--- a/docs/gearing_shiftlights.xlsx
+++ b/docs/gearing_shiftlights.xlsx
@@ -51,7 +51,7 @@
         <t>[线程批注]
 你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
 注释:
-    Source: docs/astral_engine_curve_*.json, current configured driveline. Game-exported torque is Nm and power is PS; displayed power is hp = PS * 735.49875 / 745.6998715822702. Samples retain 500 rpm spacing, peak points and the final point. Shift thresholds are recorded calibration inputs calculated from the full-resolution curves and configured rotational inertia; this workbook does not rerun that solver. 25R1 uses the 2025 game export. Rally1 uses the 2022 curve predicted from the game export and ECU delta, at measured running mass 1460 kg. RX3 remains an RX1 five-speed placeholder.</t>
+    Source: docs/astral_engine_curve_rally2.json, astral_engine_curve_wrc.json, astral_engine_curve_wrc17.json, astral_engine_curve_25r1.json, astral_engine_curve_rally1.json and astral_engine_curve_rx1.json, current configured driveline. Game-exported torque is Nm and power is PS; displayed power is hp = PS * 735.49875 / 745.6998715822702. Samples retain 500 rpm spacing, peak points and the final point. Shift thresholds are recorded calibration inputs calculated from the full-resolution curves and configured rotational inertia; this workbook does not rerun that solver. 25R1 uses the 2025 game export. Rally1 uses the 2022 measured game export, at measured running mass 1460 kg. RX3 remains an RX1 five-speed placeholder.</t>
       </text>
     </comment>
   </commentList>
@@ -1747,7 +1747,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>59.243074983029992</c:v>
+                  <c:v>59.243074983029985</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1871,7 +1871,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>113.64943522906022</c:v>
+                  <c:v>113.64943522906023</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2054,10 +2054,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>53.736953896371908</c:v>
+                  <c:v>53.667256161097754</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53.736953896371908</c:v>
+                  <c:v>53.667256161097754</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2069,10 +2069,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7710</c:v>
+                  <c:v>7700</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5509.2146719962384</c:v>
+                  <c:v>5502.0691276745829</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2178,10 +2178,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>102.01708127032111</c:v>
+                  <c:v>101.88337605240459</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>102.01708127032111</c:v>
+                  <c:v>101.88337605240459</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2193,10 +2193,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7630</c:v>
+                  <c:v>7620</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6050.3112313937754</c:v>
+                  <c:v>6042.3815967523678</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2562,7 +2562,7 @@
                   <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4141</c:v>
+                  <c:v>4202</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>4500</c:v>
@@ -2574,10 +2574,10 @@
                   <c:v>5500</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5690</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6000</c:v>
+                  <c:v>6026</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6500</c:v>
@@ -2604,49 +2604,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>781.33066149713</c:v>
+                  <c:v>781.05167032923998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>815.57037906490996</c:v>
+                  <c:v>822.79785742473996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>839.31014412132004</c:v>
+                  <c:v>839.28713128852996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>849.15980634939001</c:v>
+                  <c:v>841.83376436275</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>849.65874099113</c:v>
+                  <c:v>842.02176826692005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>846.29453700936006</c:v>
+                  <c:v>838.56059242493995</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>830.31349066587995</c:v>
+                  <c:v>812.3620969044</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>778.94554556110995</c:v>
+                  <c:v>770.95605396983001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>754.97659059928003</c:v>
+                  <c:v>714.32480746778003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>713.52169310327997</c:v>
+                  <c:v>711.26269761590004</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>650.00523948523005</c:v>
+                  <c:v>653.88859149237999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>590.16354933322998</c:v>
+                  <c:v>592.51204200030998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>529.20441413318997</c:v>
+                  <c:v>532.45096066694998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>466.5003138289</c:v>
+                  <c:v>475.48818762326999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>397.788442868</c:v>
+                  <c:v>426.90977160884</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2716,7 +2716,7 @@
                   <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4141</c:v>
+                  <c:v>4202</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>4500</c:v>
@@ -2728,10 +2728,10 @@
                   <c:v>5500</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5690</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6000</c:v>
+                  <c:v>6026</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6500</c:v>
@@ -2758,49 +2758,49 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>270.56190658493745</c:v>
+                  <c:v>270.46529655025506</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>338.90226648653652</c:v>
+                  <c:v>341.90557418382974</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>406.89494166808578</c:v>
+                  <c:v>406.883785118486</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>470.48003110172607</c:v>
+                  <c:v>466.42101130832987</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>487.35063311023652</c:v>
+                  <c:v>490.08469690958179</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>527.5040831604706</c:v>
+                  <c:v>522.68343601126708</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>575.04770302318877</c:v>
+                  <c:v>562.61516053815581</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>593.4191567035989</c:v>
+                  <c:v>587.33257287292554</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>595.02816984475828</c:v>
+                  <c:v>593.66132579742168</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>592.99387321365498</c:v>
+                  <c:v>593.67797109433252</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>585.22381167748551</c:v>
+                  <c:v>588.72013743865477</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>572.21889825237974</c:v>
+                  <c:v>574.49598210147042</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>549.764250848752</c:v>
+                  <c:v>553.13692721974292</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>516.93233833745376</c:v>
+                  <c:v>526.89186565067803</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>468.28663693613572</c:v>
+                  <c:v>502.56900321315055</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3165,7 +3165,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79.121592757076257</c:v>
+                  <c:v>79.121592757076272</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3289,7 +3289,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>122.89259852968704</c:v>
+                  <c:v>122.89259852968702</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3534,10 +3534,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>55.850536063818538</c:v>
+                  <c:v>57.526052145733104</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55.850536063818538</c:v>
+                  <c:v>57.526052145733104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3549,10 +3549,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6000</c:v>
+                  <c:v>6180</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4812.9629629629635</c:v>
+                  <c:v>4957.3518518518522</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3596,10 +3596,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>71.597851503436175</c:v>
+                  <c:v>74.266815173742557</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71.597851503436175</c:v>
+                  <c:v>74.266815173742557</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3611,10 +3611,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6170</c:v>
+                  <c:v>6400</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4952.1431319738349</c:v>
+                  <c:v>5136.7449018853404</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3658,10 +3658,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>89.928466218194515</c:v>
+                  <c:v>93.542954410244121</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>89.928466218194515</c:v>
+                  <c:v>93.542954410244121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3673,10 +3673,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6220</c:v>
+                  <c:v>6470</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5039.2138063278999</c:v>
+                  <c:v>5241.7545541706613</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3720,10 +3720,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>111.53583385525893</c:v>
+                  <c:v>115.9972672094693</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>111.53583385525893</c:v>
+                  <c:v>115.9972672094693</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3735,10 +3735,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6250</c:v>
+                  <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5110.9467455621307</c:v>
+                  <c:v>5315.3846153846152</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3782,10 +3782,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>136.61154277144155</c:v>
+                  <c:v>142.28550461178898</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>136.61154277144155</c:v>
+                  <c:v>142.28550461178898</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3797,10 +3797,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6260</c:v>
+                  <c:v>6520</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5163.820549927641</c:v>
+                  <c:v>5378.2923299565846</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6349,10 +6349,10 @@
                   <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>4320</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>4500</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4715</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>5000</c:v>
@@ -6364,7 +6364,7 @@
                   <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6060</c:v>
+                  <c:v>6075</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6500</c:v>
@@ -6388,46 +6388,46 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>375.5387979034</c:v>
+                  <c:v>375.44633689620002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>393.47429806315</c:v>
+                  <c:v>391.81465773047</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>403.52794593592</c:v>
+                  <c:v>402.07401438856999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>407.20471675444003</c:v>
+                  <c:v>408.63572203684998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>409.12826470105</c:v>
+                  <c:v>409.69872419623999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>409.34482245507002</c:v>
+                  <c:v>409.49711025478001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>407.45143542004001</c:v>
+                  <c:v>406.63916218112001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>392.98683843027999</c:v>
+                  <c:v>392.64119207404002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>367.25870170296997</c:v>
+                  <c:v>367.86271454908001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>363.72649618820998</c:v>
+                  <c:v>363.48537899789</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>335.54735400714998</c:v>
+                  <c:v>336.27624911903001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>303.45837406874</c:v>
+                  <c:v>303.09493534721997</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>268.94344000078001</c:v>
+                  <c:v>269.74304205366002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>256.53470931065999</c:v>
+                  <c:v>258.10696802923002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6497,10 +6497,10 @@
                   <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>4320</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>4500</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4715</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>5000</c:v>
@@ -6512,7 +6512,7 @@
                   <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6060</c:v>
+                  <c:v>6075</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6500</c:v>
@@ -6536,46 +6536,46 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>130.04288474058632</c:v>
+                  <c:v>130.01086702053112</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>163.50438274952646</c:v>
+                  <c:v>162.81473549805494</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>195.62909035840747</c:v>
+                  <c:v>194.92422887628476</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>225.61323130333525</c:v>
+                  <c:v>226.40608490372765</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>255.01385242165637</c:v>
+                  <c:v>245.15464866067819</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>267.33927943898806</c:v>
+                  <c:v>255.24375764631117</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>282.18740832921816</c:v>
+                  <c:v>281.62485470878664</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>299.38667675276599</c:v>
+                  <c:v>299.12335517604402</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>305.22149795764545</c:v>
+                  <c:v>305.72348117771463</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>305.30881080191813</c:v>
+                  <c:v>305.8616330691724</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>302.10572097215004</c:v>
+                  <c:v>302.76197226025005</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>294.23134768533191</c:v>
+                  <c:v>293.87895976668301</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>279.39201726972254</c:v>
+                  <c:v>280.22268423287494</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>271.79569218153762</c:v>
+                  <c:v>273.46148293497112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6940,7 +6940,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>59.722074825531699</c:v>
+                  <c:v>59.722074825531713</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7002,7 +7002,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73.386640165871825</c:v>
+                  <c:v>73.38664016587181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7064,7 +7064,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>91.474271122446098</c:v>
+                  <c:v>91.474271122446083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7188,7 +7188,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>140.76022229208189</c:v>
+                  <c:v>140.76022229208186</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7309,10 +7309,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>48.792544792101062</c:v>
+                  <c:v>49.026749007103156</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>48.792544792101062</c:v>
+                  <c:v>49.026749007103156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7324,10 +7324,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6250</c:v>
+                  <c:v>6280</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5086.2523044508816</c:v>
+                  <c:v>5110.6663155122469</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7371,10 +7371,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>61.970940584513983</c:v>
+                  <c:v>62.258731330262492</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>61.970940584513983</c:v>
+                  <c:v>62.258731330262492</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7386,10 +7386,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6460</c:v>
+                  <c:v>6490</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5182.6343042071203</c:v>
+                  <c:v>5206.7022653721688</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7433,10 +7433,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>78.321107954512669</c:v>
+                  <c:v>78.560256375747812</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>78.321107954512669</c:v>
+                  <c:v>78.560256375747812</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7448,10 +7448,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6550</c:v>
+                  <c:v>6570</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5276.462283178701</c:v>
+                  <c:v>5292.5736183945137</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7495,10 +7495,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>98.115459903837134</c:v>
+                  <c:v>98.412329676617276</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>98.115459903837134</c:v>
+                  <c:v>98.412329676617276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7510,10 +7510,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6610</c:v>
+                  <c:v>6630</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5332.3535302954424</c:v>
+                  <c:v>5348.4877315973963</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7557,10 +7557,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>121.62419207198188</c:v>
+                  <c:v>122.17619294371551</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>121.62419207198188</c:v>
+                  <c:v>122.17619294371551</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7572,10 +7572,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6610</c:v>
+                  <c:v>6640</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5399.6027312228434</c:v>
+                  <c:v>5424.1092489137181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7886,10 +7886,10 @@
                   <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4719</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>5000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5242</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>5500</c:v>
@@ -7901,7 +7901,7 @@
                   <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6589</c:v>
+                  <c:v>6619</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>7000</c:v>
@@ -7925,49 +7925,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>401.07451780446002</c:v>
+                  <c:v>401.49191489075997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>420.15432548965998</c:v>
+                  <c:v>420.79792263021</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>434.59303883507999</c:v>
+                  <c:v>435.31957112793998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>445.04598601673001</c:v>
+                  <c:v>445.08767979256999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>449.37292062704</c:v>
+                  <c:v>450.64322868988</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>450.29178004523999</c:v>
+                  <c:v>451.20326615827997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>450.42287057639999</c:v>
+                  <c:v>450.94250368996001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>450.06220861605999</c:v>
+                  <c:v>450.01398097113002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>446.99380766573</c:v>
+                  <c:v>446.55915850042999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>421.37375767764001</c:v>
+                  <c:v>420.98622755331002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>415.94463169600999</c:v>
+                  <c:v>413.80998751977</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>388.61552309927998</c:v>
+                  <c:v>388.98375720312998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>356.44475630423</c:v>
+                  <c:v>356.39069102285998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>323.93917964009</c:v>
+                  <c:v>324.80740390348001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>283.84920919076001</c:v>
+                  <c:v>285.34487111657</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8040,10 +8040,10 @@
                   <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4719</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>5000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5242</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>5500</c:v>
@@ -8055,7 +8055,7 @@
                   <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6589</c:v>
+                  <c:v>6619</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>7000</c:v>
@@ -8079,49 +8079,49 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>138.88548289129707</c:v>
+                  <c:v>139.0300206101455</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>174.59100629160596</c:v>
+                  <c:v>174.8584467666858</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>210.68935056335647</c:v>
+                  <c:v>211.04157115426511</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>246.57932202775831</c:v>
+                  <c:v>246.60242261354236</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>280.09876009619853</c:v>
+                  <c:v>280.89055616803807</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>311.85721623958699</c:v>
+                  <c:v>294.92662876437004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>327.0462886645617</c:v>
+                  <c:v>312.30788594616013</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>342.86804491412022</c:v>
+                  <c:v>342.83130395251504</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>371.48777937974825</c:v>
+                  <c:v>371.12655099033117</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>379.37841363288413</c:v>
+                  <c:v>379.02950589688623</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>379.61800764077708</c:v>
+                  <c:v>379.38933991421766</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>376.79918850102615</c:v>
+                  <c:v>377.15622599247598</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>370.29280025853808</c:v>
+                  <c:v>370.23663451593626</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>358.95932467021913</c:v>
+                  <c:v>359.92141019378801</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>334.15448324885881</c:v>
+                  <c:v>335.91521437562892</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8486,7 +8486,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>66.332219995224065</c:v>
+                  <c:v>66.332219995224079</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8548,7 +8548,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>81.523689959165253</c:v>
+                  <c:v>81.523689959165267</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8672,7 +8672,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>126.16761541299385</c:v>
+                  <c:v>126.16761541299383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8734,7 +8734,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>156.37676276540085</c:v>
+                  <c:v>156.37676276540083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8855,10 +8855,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>54.392420396083736</c:v>
+                  <c:v>54.470458301960477</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>54.392420396083736</c:v>
+                  <c:v>54.470458301960477</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8870,10 +8870,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6970</c:v>
+                  <c:v>6980</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5671.1806543385492</c:v>
+                  <c:v>5679.3172119487908</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8917,10 +8917,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>68.863540459624303</c:v>
+                  <c:v>68.959450683105686</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>68.863540459624303</c:v>
+                  <c:v>68.959450683105686</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8932,10 +8932,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7180</c:v>
+                  <c:v>7190</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5761.5734265734263</c:v>
+                  <c:v>5769.5979020979021</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9041,10 +9041,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>108.20728427773237</c:v>
+                  <c:v>108.35571676645353</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>108.20728427773237</c:v>
+                  <c:v>108.35571676645353</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9056,10 +9056,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7290</c:v>
+                  <c:v>7300</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5881.704545454546</c:v>
+                  <c:v>5889.7727272727279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9103,10 +9103,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>133.74812532993695</c:v>
+                  <c:v>133.93209799201389</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>133.74812532993695</c:v>
+                  <c:v>133.93209799201389</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9118,10 +9118,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7270</c:v>
+                  <c:v>7280</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5938.8732394366198</c:v>
+                  <c:v>5947.0422535211255</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9432,7 +9432,7 @@
                   <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4978</c:v>
+                  <c:v>4910</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>5000</c:v>
@@ -9447,10 +9447,10 @@
                   <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>6997</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>7000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7023</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>7500</c:v>
@@ -9471,49 +9471,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>392.12322294939003</c:v>
+                  <c:v>392.77292020160002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>413.34434636400999</c:v>
+                  <c:v>414.05838390473002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>426.43653820907002</c:v>
+                  <c:v>426.22417942502</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>434.66000894194002</c:v>
+                  <c:v>433.33018061939998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>438.93000290914</c:v>
+                  <c:v>439.48912900365002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>440.45937290107003</c:v>
+                  <c:v>440.77961570266001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>440.45531734092998</c:v>
+                  <c:v>440.74556683840001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>438.54886894563998</c:v>
+                  <c:v>438.74965911927001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>430.32993219679997</c:v>
+                  <c:v>430.00295381093002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>407.30321335870002</c:v>
+                  <c:v>406.35807005572002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>381.20202297351</c:v>
+                  <c:v>380.79667249825002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>379.95765344646998</c:v>
+                  <c:v>380.63334389029001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>353.21169403024999</c:v>
+                  <c:v>351.86158862310998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>321.39007141308002</c:v>
+                  <c:v>321.04792098374998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>278.85280319881002</c:v>
+                  <c:v>280.43430803348002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9586,7 +9586,7 @@
                   <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4978</c:v>
+                  <c:v>4910</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>5000</c:v>
@@ -9601,10 +9601,10 @@
                   <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>6997</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>7000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7023</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>7500</c:v>
@@ -9625,49 +9625,49 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>135.78579728859611</c:v>
+                  <c:v>136.01077671910764</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>171.76118630347156</c:v>
+                  <c:v>172.0578975954937</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>206.73510448437605</c:v>
+                  <c:v>206.63215360780916</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>240.82493424275626</c:v>
+                  <c:v>240.08813809923262</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>273.58958214998773</c:v>
+                  <c:v>273.93809119141594</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>303.7054062516201</c:v>
+                  <c:v>299.77455605322371</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>305.04480701394795</c:v>
+                  <c:v>305.24582423057882</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>334.09691019617696</c:v>
+                  <c:v>334.24987690378146</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>357.63875957757472</c:v>
+                  <c:v>357.36701425943784</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>366.71018101183154</c:v>
+                  <c:v>365.85923346133035</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>369.61110499610913</c:v>
+                  <c:v>369.05984338245162</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>369.61504422565332</c:v>
+                  <c:v>369.05971730226167</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>366.93413201704772</c:v>
+                  <c:v>365.53157438923347</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>356.13463958985204</c:v>
+                  <c:v>355.75550024898888</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>328.27258748067237</c:v>
+                  <c:v>330.13437505545949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10032,7 +10032,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>59.243074983029977</c:v>
+                  <c:v>59.243074983029992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10156,7 +10156,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>113.64943522906022</c:v>
+                  <c:v>113.64943522906024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10339,10 +10339,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>52.621790131985449</c:v>
+                  <c:v>52.412696926163001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52.621790131985449</c:v>
+                  <c:v>52.412696926163001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10354,10 +10354,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7550</c:v>
+                  <c:v>7520</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5394.885962849753</c:v>
+                  <c:v>5373.4493298847874</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10401,10 +10401,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>75.788684346823146</c:v>
+                  <c:v>75.593604078234165</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>75.788684346823146</c:v>
+                  <c:v>75.593604078234165</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10416,10 +10416,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7770</c:v>
+                  <c:v>7750</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5668.3415597235935</c:v>
+                  <c:v>5653.7512339585392</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10463,10 +10463,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>100.94743952698879</c:v>
+                  <c:v>100.54632387323919</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100.94743952698879</c:v>
+                  <c:v>100.54632387323919</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10478,10 +10478,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7550</c:v>
+                  <c:v>7520</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5986.8741542625166</c:v>
+                  <c:v>5963.0852503382948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10525,10 +10525,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>131.18215938459414</c:v>
+                  <c:v>130.84493018309135</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>131.18215938459414</c:v>
+                  <c:v>130.84493018309135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10540,10 +10540,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7780</c:v>
+                  <c:v>7760</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5947.8498293515368</c:v>
+                  <c:v>5932.5597269624577</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10853,7 +10853,7 @@
                   <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5189</c:v>
+                  <c:v>5083</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>5500</c:v>
@@ -10865,7 +10865,7 @@
                   <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6843</c:v>
+                  <c:v>6951</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>7000</c:v>
@@ -10889,49 +10889,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>392.12322294939003</c:v>
+                  <c:v>393.20032070475003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>413.34311991096001</c:v>
+                  <c:v>414.50137329109998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>427.69062033038</c:v>
+                  <c:v>428.95781702558997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>435.71238814309982</c:v>
+                  <c:v>436.57054083362999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>439.98714840701604</c:v>
+                  <c:v>442.09140264401998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>443.19385328835278</c:v>
+                  <c:v>444.45705821157998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>443.46248568368935</c:v>
+                  <c:v>444.51603790308002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>442.88615147652462</c:v>
+                  <c:v>443.41134004895002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>439.70678468527797</c:v>
+                  <c:v>439.80647992658999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>418.98807357322522</c:v>
+                  <c:v>418.75913649655001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>399.94118639818879</c:v>
+                  <c:v>393.93320137098999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>390.92736187569773</c:v>
+                  <c:v>391.17393740355999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>363.26933766308696</c:v>
+                  <c:v>362.86336707814002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>332.97769982606115</c:v>
+                  <c:v>333.47219443757001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>288.35790965028451</c:v>
+                  <c:v>289.71271466747999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11007,7 +11007,7 @@
                   <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5189</c:v>
+                  <c:v>5083</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>5500</c:v>
@@ -11019,7 +11019,7 @@
                   <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6843</c:v>
+                  <c:v>6951</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>7000</c:v>
@@ -11043,49 +11043,49 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>135.78579728860106</c:v>
+                  <c:v>136.15877845602444</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>171.76067666294219</c:v>
+                  <c:v>172.24197748721423</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>207.34307958770773</c:v>
+                  <c:v>207.95741259558852</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>241.40800870717055</c:v>
+                  <c:v>241.88347127794921</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>274.24851180418904</c:v>
+                  <c:v>275.56011509770593</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>306.94142657260284</c:v>
+                  <c:v>307.81628058583448</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>318.73689095861903</c:v>
+                  <c:v>312.96755629673748</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>337.4011547053417</c:v>
+                  <c:v>337.80125579268849</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>365.43167761979055</c:v>
+                  <c:v>365.51453237789877</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>377.23049380050577</c:v>
+                  <c:v>377.02437326407409</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>379.08311881213342</c:v>
+                  <c:v>379.28148996854014</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>379.04073296623568</c:v>
+                  <c:v>379.27981106085798</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>377.38251976561105</c:v>
+                  <c:v>376.96077703531915</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>368.97497361265437</c:v>
+                  <c:v>369.5229266327072</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>339.46223970331931</c:v>
+                  <c:v>341.05715050724183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12298,7 +12298,7 @@
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="B2" dT="2026-10-27T03:19:09.83" personId="{4B51B63F-135D-471B-AFAA-1BEB5D1B10EA}" id="{61577C78-3AE9-40FE-BEAD-1A1561E5C31C}">
-    <text>Source: docs/astral_engine_curve_*.json, current configured driveline. Game-exported torque is Nm and power is PS; displayed power is hp = PS * 735.49875 / 745.6998715822702. Samples retain 500 rpm spacing, peak points and the final point. Shift thresholds are recorded calibration inputs calculated from the full-resolution curves and configured rotational inertia; this workbook does not rerun that solver. 25R1 uses the 2025 game export. Rally1 uses the 2022 curve predicted from the game export and ECU delta, at measured running mass 1460 kg. RX3 remains an RX1 five-speed placeholder.</text>
+    <text>Source: docs/astral_engine_curve_rally2.json, astral_engine_curve_wrc.json, astral_engine_curve_wrc17.json, astral_engine_curve_25r1.json, astral_engine_curve_rally1.json and astral_engine_curve_rx1.json, current configured driveline. Game-exported torque is Nm and power is PS; displayed power is hp = PS * 735.49875 / 745.6998715822702. Samples retain 500 rpm spacing, peak points and the final point. Shift thresholds are recorded calibration inputs calculated from the full-resolution curves and configured rotational inertia; this workbook does not rerun that solver. 25R1 uses the 2025 game export. Rally1 uses the 2022 measured game export, at measured running mass 1460 kg. RX3 remains an RX1 five-speed placeholder.</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
-      <c r="I6" s="7">
+      <c r="I6" s="7" t="n">
         <v>1420.59</v>
       </c>
       <c r="J6" s="1"/>
@@ -12464,7 +12464,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="O6" s="31" t="n">
         <v>3000</v>
       </c>
       <c r="P6" s="31"/>
@@ -12488,8 +12488,8 @@
       </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="8">
-        <v>0.12343999999999999</v>
+      <c r="I7" s="8" t="n">
+        <v>0.12344</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="32" t="str">
@@ -12499,7 +12499,7 @@
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="O7" s="32" t="n">
         <v>7500</v>
       </c>
       <c r="P7" s="32"/>
@@ -12523,19 +12523,19 @@
       </c>
       <c r="G8" s="30"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="9">
-        <v>4.1333333333333337</v>
+      <c r="I8" s="9" t="n">
+        <v>4.133333333333334</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="30" t="str">
-        <f>VLOOKUP("label.lightRangeRpm",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>亮灯范围 (rpm)</v>
+        <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>普通档亮灯范围 (rpm)</v>
       </c>
       <c r="L8" s="30"/>
       <c r="M8" s="30"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="31">
-        <v>800</v>
+      <c r="O8" s="31" t="n">
+        <v>500</v>
       </c>
       <c r="P8" s="31"/>
       <c r="Q8" s="1"/>
@@ -12558,8 +12558,8 @@
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="10">
-        <v>1.0999999999999999E-2</v>
+      <c r="I9" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="32" t="str">
@@ -12586,12 +12586,17 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
+      <c r="K10" s="30" t="str">
+        <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>最高档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="31" t="n">
+        <v>250</v>
+      </c>
+      <c r="P10" s="31"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
@@ -12608,12 +12613,17 @@
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
+      <c r="K11" s="30" t="str">
+        <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>空档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="31"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -12734,10 +12744,10 @@
       <c r="B15" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="12" t="n">
         <v>3.762</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="22" t="n">
         <v>6170</v>
       </c>
       <c r="E15" s="13">
@@ -12750,7 +12760,7 @@
       </c>
       <c r="G15" s="13">
         <f>MAX(0,D15-$O$8)</f>
-        <v>5370</v>
+        <v>5670</v>
       </c>
       <c r="H15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -12760,10 +12770,10 @@
       <c r="J15" s="11">
         <v>1</v>
       </c>
-      <c r="K15" s="12">
-        <v>3.3650000000000002</v>
-      </c>
-      <c r="L15" s="22">
+      <c r="K15" s="12" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="L15" s="22" t="n">
         <v>6460</v>
       </c>
       <c r="M15" s="13">
@@ -12776,7 +12786,7 @@
       </c>
       <c r="O15" s="13">
         <f>MAX(0,L15-$O$8)</f>
-        <v>5660</v>
+        <v>5960</v>
       </c>
       <c r="P15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -12789,10 +12799,10 @@
       <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="12" t="n">
         <v>2.69</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="22" t="n">
         <v>6360</v>
       </c>
       <c r="E16" s="16">
@@ -12805,7 +12815,7 @@
       </c>
       <c r="G16" s="16">
         <f>MAX(0,D16-$O$8)</f>
-        <v>5560</v>
+        <v>5860</v>
       </c>
       <c r="H16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -12815,10 +12825,10 @@
       <c r="J16" s="15">
         <v>2</v>
       </c>
-      <c r="K16" s="12">
-        <v>2.3039999999999998</v>
-      </c>
-      <c r="L16" s="22">
+      <c r="K16" s="12" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="L16" s="22" t="n">
         <v>6210</v>
       </c>
       <c r="M16" s="16">
@@ -12831,7 +12841,7 @@
       </c>
       <c r="O16" s="16">
         <f>MAX(0,L16-$O$8)</f>
-        <v>5410</v>
+        <v>5710</v>
       </c>
       <c r="P16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -12844,10 +12854,10 @@
       <c r="B17" s="11">
         <v>3</v>
       </c>
-      <c r="C17" s="12">
-        <v>1.9610000000000001</v>
-      </c>
-      <c r="D17" s="22">
+      <c r="C17" s="12" t="n">
+        <v>1.961</v>
+      </c>
+      <c r="D17" s="22" t="n">
         <v>6290</v>
       </c>
       <c r="E17" s="13">
@@ -12860,7 +12870,7 @@
       </c>
       <c r="G17" s="13">
         <f>MAX(0,D17-$O$8)</f>
-        <v>5490</v>
+        <v>5790</v>
       </c>
       <c r="H17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -12870,10 +12880,10 @@
       <c r="J17" s="11">
         <v>3</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="12" t="n">
         <v>1.758</v>
       </c>
-      <c r="L17" s="22">
+      <c r="L17" s="22" t="n">
         <v>6150</v>
       </c>
       <c r="M17" s="13">
@@ -12886,7 +12896,7 @@
       </c>
       <c r="O17" s="13">
         <f>MAX(0,L17-$O$8)</f>
-        <v>5350</v>
+        <v>5650</v>
       </c>
       <c r="P17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -12899,10 +12909,10 @@
       <c r="B18" s="15">
         <v>4</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="12" t="n">
         <v>1.49</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="22" t="n">
         <v>6120</v>
       </c>
       <c r="E18" s="16">
@@ -12915,7 +12925,7 @@
       </c>
       <c r="G18" s="16">
         <f>MAX(0,D18-$O$8)</f>
-        <v>5320</v>
+        <v>5620</v>
       </c>
       <c r="H18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -12925,10 +12935,10 @@
       <c r="J18" s="15">
         <v>4</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="12" t="n">
         <v>1.383</v>
       </c>
-      <c r="L18" s="22">
+      <c r="L18" s="22" t="n">
         <v>6080</v>
       </c>
       <c r="M18" s="16">
@@ -12941,7 +12951,7 @@
       </c>
       <c r="O18" s="16">
         <f>MAX(0,L18-$O$8)</f>
-        <v>5280</v>
+        <v>5580</v>
       </c>
       <c r="P18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -12954,8 +12964,8 @@
       <c r="B19" s="11">
         <v>5</v>
       </c>
-      <c r="C19" s="12">
-        <v>1.1890000000000001</v>
+      <c r="C19" s="12" t="n">
+        <v>1.189</v>
       </c>
       <c r="D19" s="13">
         <f>$O$7</f>
@@ -12969,8 +12979,8 @@
         <v>186.97926921003307</v>
       </c>
       <c r="G19" s="13">
-        <f>MAX(0,D19-$O$8)</f>
-        <v>6700</v>
+        <f>MAX(0,D19-$O$10)</f>
+        <v>7250</v>
       </c>
       <c r="H19" s="11" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -12980,8 +12990,8 @@
       <c r="J19" s="11">
         <v>5</v>
       </c>
-      <c r="K19" s="12">
-        <v>1.1140000000000001</v>
+      <c r="K19" s="12" t="n">
+        <v>1.114</v>
       </c>
       <c r="L19" s="13">
         <f>$O$7</f>
@@ -12995,8 +13005,8 @@
         <v>198.95358584006709</v>
       </c>
       <c r="O19" s="13">
-        <f>MAX(0,L19-$O$8)</f>
-        <v>6700</v>
+        <f>MAX(0,L19-$O$10)</f>
+        <v>7250</v>
       </c>
       <c r="P19" s="11" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -13049,8 +13059,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="C22" s="34"/>
-      <c r="D22" s="18">
-        <v>0.32500000000000001</v>
+      <c r="D22" s="18" t="n">
+        <v>0.325</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="34" t="str">
@@ -13058,7 +13068,7 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="G22" s="34"/>
-      <c r="H22" s="19">
+      <c r="H22" s="19" t="n">
         <v>5.4748128000000005</v>
       </c>
       <c r="I22" s="1"/>
@@ -13067,8 +13077,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="K22" s="34"/>
-      <c r="L22" s="18">
-        <v>0.32400000000000001</v>
+      <c r="L22" s="18" t="n">
+        <v>0.324</v>
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="34" t="str">
@@ -13076,8 +13086,8 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="O22" s="34"/>
-      <c r="P22" s="19">
-        <v>5.7898434559999998</v>
+      <c r="P22" s="19" t="n">
+        <v>5.789843456</v>
       </c>
       <c r="Q22" s="1"/>
     </row>
@@ -13088,7 +13098,7 @@
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
       <c r="C23" s="34"/>
-      <c r="D23" s="20">
+      <c r="D23" s="20" t="n">
         <v>1.65</v>
       </c>
       <c r="E23" s="1"/>
@@ -13097,8 +13107,8 @@
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
       <c r="G23" s="34"/>
-      <c r="H23" s="21">
-        <v>7.7999999999999999E-4</v>
+      <c r="H23" s="21" t="n">
+        <v>0.00078</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="34" t="str">
@@ -14214,8 +14224,8 @@
       <c r="Q80" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B11:P11"/>
+  <mergeCells count="39">
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="E53:P53"/>
     <mergeCell ref="J13:P13"/>
@@ -14250,6 +14260,10 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="K5:P5"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="5">
@@ -14407,7 +14421,7 @@
       <c r="C6" s="30"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$37:$D$50)</f>
-        <v>305.30881080191813</v>
+        <v>305.8616330691724</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="30" t="str">
@@ -14416,7 +14430,7 @@
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
-      <c r="I6" s="7">
+      <c r="I6" s="7" t="n">
         <v>1390</v>
       </c>
       <c r="J6" s="1"/>
@@ -14427,7 +14441,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="O6" s="31" t="n">
         <v>3000</v>
       </c>
       <c r="P6" s="31"/>
@@ -14442,7 +14456,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$37:$B$50,MATCH(D6,Samples!$D$37:$D$50,0))</f>
-        <v>6060</v>
+        <v>6075</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="32" t="str">
@@ -14451,7 +14465,7 @@
       </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="8">
+      <c r="I7" s="8" t="n">
         <v>0.12171599999999999</v>
       </c>
       <c r="J7" s="1"/>
@@ -14462,7 +14476,7 @@
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="O7" s="32" t="n">
         <v>7650</v>
       </c>
       <c r="P7" s="32"/>
@@ -14477,7 +14491,7 @@
       <c r="C8" s="30"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$37:$C$50)</f>
-        <v>409.34482245507002</v>
+        <v>409.69872419623999</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="30" t="str">
@@ -14486,19 +14500,19 @@
       </c>
       <c r="G8" s="30"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="9">
-        <v>4.1333333333333337</v>
+      <c r="I8" s="9" t="n">
+        <v>4.133333333333334</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="30" t="str">
-        <f>VLOOKUP("label.lightRangeRpm",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>亮灯范围 (rpm)</v>
+        <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>普通档亮灯范围 (rpm)</v>
       </c>
       <c r="L8" s="30"/>
       <c r="M8" s="30"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="31">
-        <v>800</v>
+      <c r="O8" s="31" t="n">
+        <v>500</v>
       </c>
       <c r="P8" s="31"/>
       <c r="Q8" s="1"/>
@@ -14512,7 +14526,7 @@
       <c r="C9" s="32"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$37:$B$50,MATCH(D8,Samples!$C$37:$C$50,0))</f>
-        <v>4715</v>
+        <v>4320</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="32" t="str">
@@ -14521,8 +14535,8 @@
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="10">
-        <v>1.2E-2</v>
+      <c r="I9" s="10" t="n">
+        <v>0.012</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="32" t="str">
@@ -14549,12 +14563,17 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
+      <c r="K10" s="30" t="str">
+        <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>最高档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="31" t="n">
+        <v>250</v>
+      </c>
+      <c r="P10" s="31"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
@@ -14571,12 +14590,17 @@
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
+      <c r="K11" s="30" t="str">
+        <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>空档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="31"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -14697,23 +14721,23 @@
       <c r="B15" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="12">
-        <v>3.7970000000000002</v>
-      </c>
-      <c r="D15" s="22">
-        <v>6250</v>
+      <c r="C15" s="12" t="n">
+        <v>3.797</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>6280</v>
       </c>
       <c r="E15" s="13">
         <f>D15*C16/C15</f>
-        <v>5086.2523044508816</v>
+        <v>5110.6663155122469</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" ref="F15:F20" si="0">D15*2*PI()/60*$D$22/(C15*$I$8)*3.6</f>
-        <v>48.792544792101062</v>
+        <v>49.026749007103156</v>
       </c>
       <c r="G15" s="13">
         <f t="shared" ref="G15:G20" si="1">MAX(0,D15-$O$8)</f>
-        <v>5450</v>
+        <v>5780</v>
       </c>
       <c r="H15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14723,23 +14747,23 @@
       <c r="J15" s="11">
         <v>1</v>
       </c>
-      <c r="K15" s="12">
-        <v>3.4910000000000001</v>
-      </c>
-      <c r="L15" s="22">
-        <v>6350</v>
+      <c r="K15" s="12" t="n">
+        <v>3.491</v>
+      </c>
+      <c r="L15" s="22" t="n">
+        <v>6380</v>
       </c>
       <c r="M15" s="13">
         <f>L15*K16/K15</f>
-        <v>5091.2775708965901</v>
+        <v>5115.3308507590946</v>
       </c>
       <c r="N15" s="14">
         <f t="shared" ref="N15:N20" si="2">L15*2*PI()/60*$L$22/(K15*$I$8)*3.6</f>
-        <v>53.752612274383672</v>
+        <v>54.006561623711484</v>
       </c>
       <c r="O15" s="13">
         <f t="shared" ref="O15:O20" si="3">MAX(0,L15-$O$8)</f>
-        <v>5550</v>
+        <v>5880</v>
       </c>
       <c r="P15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14752,23 +14776,23 @@
       <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="12" t="n">
         <v>3.09</v>
       </c>
-      <c r="D16" s="22">
-        <v>6460</v>
+      <c r="D16" s="22" t="n">
+        <v>6490</v>
       </c>
       <c r="E16" s="16">
         <f>D16*C17/C16</f>
-        <v>5182.6343042071203</v>
+        <v>5206.7022653721688</v>
       </c>
       <c r="F16" s="17">
         <f t="shared" si="0"/>
-        <v>61.970940584513983</v>
+        <v>62.258731330262492</v>
       </c>
       <c r="G16" s="16">
         <f t="shared" si="1"/>
-        <v>5660</v>
+        <v>5990</v>
       </c>
       <c r="H16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14778,23 +14802,23 @@
       <c r="J16" s="15">
         <v>2</v>
       </c>
-      <c r="K16" s="12">
-        <v>2.7989999999999999</v>
-      </c>
-      <c r="L16" s="22">
-        <v>6510</v>
+      <c r="K16" s="12" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="L16" s="22" t="n">
+        <v>6540</v>
       </c>
       <c r="M16" s="16">
         <f>L16*K17/K16</f>
-        <v>5221.4898177920686</v>
+        <v>5245.5519828510187</v>
       </c>
       <c r="N16" s="17">
         <f t="shared" si="2"/>
-        <v>68.731178183359987</v>
+        <v>69.047911723375464</v>
       </c>
       <c r="O16" s="16">
         <f t="shared" si="3"/>
-        <v>5710</v>
+        <v>6040</v>
       </c>
       <c r="P16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14807,23 +14831,23 @@
       <c r="B17" s="11">
         <v>3</v>
       </c>
-      <c r="C17" s="12">
-        <v>2.4790000000000001</v>
-      </c>
-      <c r="D17" s="22">
-        <v>6550</v>
+      <c r="C17" s="12" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>6570</v>
       </c>
       <c r="E17" s="13">
         <f>D17*C18/C17</f>
-        <v>5276.462283178701</v>
+        <v>5292.5736183945137</v>
       </c>
       <c r="F17" s="14">
         <f t="shared" si="0"/>
-        <v>78.321107954512669</v>
+        <v>78.560256375747812</v>
       </c>
       <c r="G17" s="13">
         <f t="shared" si="1"/>
-        <v>5750</v>
+        <v>6070</v>
       </c>
       <c r="H17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14833,23 +14857,23 @@
       <c r="J17" s="11">
         <v>3</v>
       </c>
-      <c r="K17" s="12">
-        <v>2.2450000000000001</v>
-      </c>
-      <c r="L17" s="22">
-        <v>6560</v>
+      <c r="K17" s="12" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="L17" s="22" t="n">
+        <v>6590</v>
       </c>
       <c r="M17" s="13">
         <f>L17*K18/K17</f>
-        <v>5315.2071269487742</v>
+        <v>5339.5144766146987</v>
       </c>
       <c r="N17" s="14">
         <f t="shared" si="2"/>
-        <v>86.350169131134436</v>
+        <v>86.745063197282889</v>
       </c>
       <c r="O17" s="13">
         <f t="shared" si="3"/>
-        <v>5760</v>
+        <v>6090</v>
       </c>
       <c r="P17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14862,23 +14886,23 @@
       <c r="B18" s="15">
         <v>4</v>
       </c>
-      <c r="C18" s="12">
-        <v>1.9970000000000001</v>
-      </c>
-      <c r="D18" s="22">
-        <v>6610</v>
+      <c r="C18" s="12" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>6630</v>
       </c>
       <c r="E18" s="16">
         <f>D18*C19/C18</f>
-        <v>5332.3535302954424</v>
+        <v>5348.4877315973963</v>
       </c>
       <c r="F18" s="17">
         <f t="shared" si="0"/>
-        <v>98.115459903837134</v>
+        <v>98.412329676617276</v>
       </c>
       <c r="G18" s="16">
         <f t="shared" si="1"/>
-        <v>5810</v>
+        <v>6130</v>
       </c>
       <c r="H18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14888,23 +14912,23 @@
       <c r="J18" s="15">
         <v>4</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="12" t="n">
         <v>1.819</v>
       </c>
-      <c r="L18" s="22">
-        <v>6580</v>
+      <c r="L18" s="22" t="n">
+        <v>6610</v>
       </c>
       <c r="M18" s="16">
         <f>L18*K19/K18</f>
-        <v>5382.6498075865857</v>
+        <v>5407.1907641561302</v>
       </c>
       <c r="N18" s="17">
         <f t="shared" si="2"/>
-        <v>106.89783094286183</v>
+        <v>107.38520707178067</v>
       </c>
       <c r="O18" s="16">
         <f t="shared" si="3"/>
-        <v>5780</v>
+        <v>6110</v>
       </c>
       <c r="P18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14917,23 +14941,23 @@
       <c r="B19" s="11">
         <v>5</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="12" t="n">
         <v>1.611</v>
       </c>
-      <c r="D19" s="22">
-        <v>6610</v>
+      <c r="D19" s="22" t="n">
+        <v>6640</v>
       </c>
       <c r="E19" s="13">
         <f>D19*C20/C19</f>
-        <v>5399.6027312228434</v>
+        <v>5424.1092489137181</v>
       </c>
       <c r="F19" s="14">
         <f t="shared" si="0"/>
-        <v>121.62419207198188</v>
+        <v>122.17619294371551</v>
       </c>
       <c r="G19" s="13">
         <f t="shared" si="1"/>
-        <v>5810</v>
+        <v>6140</v>
       </c>
       <c r="H19" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14943,23 +14967,23 @@
       <c r="J19" s="11">
         <v>5</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="12" t="n">
         <v>1.488</v>
       </c>
-      <c r="L19" s="22">
-        <v>6590</v>
+      <c r="L19" s="22" t="n">
+        <v>6610</v>
       </c>
       <c r="M19" s="13">
         <f>L19*K20/K19</f>
-        <v>5434.0927419354839</v>
+        <v>5450.5846774193551</v>
       </c>
       <c r="N19" s="14">
         <f t="shared" si="2"/>
-        <v>130.87544817063178</v>
+        <v>131.27264224702222</v>
       </c>
       <c r="O19" s="13">
         <f t="shared" si="3"/>
-        <v>5790</v>
+        <v>6110</v>
       </c>
       <c r="P19" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14972,8 +14996,8 @@
       <c r="B20" s="15">
         <v>6</v>
       </c>
-      <c r="C20" s="12">
-        <v>1.3160000000000001</v>
+      <c r="C20" s="12" t="n">
+        <v>1.316</v>
       </c>
       <c r="D20" s="16">
         <f>$O$7</f>
@@ -14987,8 +15011,8 @@
         <v>172.31361558703946</v>
       </c>
       <c r="G20" s="16">
-        <f t="shared" si="1"/>
-        <v>6850</v>
+        <f>MAX(0,D20-$O$10)</f>
+        <v>7400</v>
       </c>
       <c r="H20" s="15" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -14998,8 +15022,8 @@
       <c r="J20" s="15">
         <v>6</v>
       </c>
-      <c r="K20" s="12">
-        <v>1.2270000000000001</v>
+      <c r="K20" s="12" t="n">
+        <v>1.227</v>
       </c>
       <c r="L20" s="16">
         <f>$O$7</f>
@@ -15013,8 +15037,8 @@
         <v>184.24366790411688</v>
       </c>
       <c r="O20" s="16">
-        <f t="shared" si="3"/>
-        <v>6850</v>
+        <f>MAX(0,L20-$O$10)</f>
+        <v>7400</v>
       </c>
       <c r="P20" s="15" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -15048,8 +15072,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="C22" s="34"/>
-      <c r="D22" s="18">
-        <v>0.32500000000000001</v>
+      <c r="D22" s="18" t="n">
+        <v>0.325</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="34" t="str">
@@ -15057,7 +15081,7 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="G22" s="34"/>
-      <c r="H22" s="19">
+      <c r="H22" s="19" t="n">
         <v>5.4748128000000005</v>
       </c>
       <c r="I22" s="1"/>
@@ -15066,8 +15090,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="K22" s="34"/>
-      <c r="L22" s="18">
-        <v>0.32400000000000001</v>
+      <c r="L22" s="18" t="n">
+        <v>0.324</v>
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="34" t="str">
@@ -15075,8 +15099,8 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="O22" s="34"/>
-      <c r="P22" s="19">
-        <v>5.7898434559999998</v>
+      <c r="P22" s="19" t="n">
+        <v>5.789843456</v>
       </c>
       <c r="Q22" s="1"/>
     </row>
@@ -15087,7 +15111,7 @@
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
       <c r="C23" s="34"/>
-      <c r="D23" s="20">
+      <c r="D23" s="20" t="n">
         <v>1.85</v>
       </c>
       <c r="E23" s="1"/>
@@ -15096,8 +15120,8 @@
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
       <c r="G23" s="34"/>
-      <c r="H23" s="21">
-        <v>9.7999999999999997E-4</v>
+      <c r="H23" s="21" t="n">
+        <v>0.00098</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="34" t="str">
@@ -16213,7 +16237,7 @@
       <c r="Q80" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="37">
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="E53:P53"/>
     <mergeCell ref="J13:P13"/>
@@ -16230,7 +16254,7 @@
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="K9:N9"/>
     <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B11:P11"/>
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="K7:N7"/>
@@ -16247,6 +16271,10 @@
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="O6:P6"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -16401,7 +16429,7 @@
       <c r="C6" s="30"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$67:$D$81)</f>
-        <v>379.61800764077708</v>
+        <v>379.38933991421766</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="30" t="str">
@@ -16410,7 +16438,7 @@
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
-      <c r="I6" s="7">
+      <c r="I6" s="7" t="n">
         <v>1391.01</v>
       </c>
       <c r="J6" s="1"/>
@@ -16421,7 +16449,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="O6" s="31" t="n">
         <v>3000</v>
       </c>
       <c r="P6" s="31"/>
@@ -16436,7 +16464,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$67:$B$81,MATCH(D6,Samples!$D$67:$D$81,0))</f>
-        <v>6589</v>
+        <v>6619</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="32" t="str">
@@ -16445,7 +16473,7 @@
       </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="8">
+      <c r="I7" s="8" t="n">
         <v>0.12171599999999999</v>
       </c>
       <c r="J7" s="1"/>
@@ -16456,7 +16484,7 @@
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="O7" s="32" t="n">
         <v>8500</v>
       </c>
       <c r="P7" s="32"/>
@@ -16471,7 +16499,7 @@
       <c r="C8" s="30"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$67:$C$81)</f>
-        <v>450.42287057639999</v>
+        <v>451.20326615827997</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="30" t="str">
@@ -16480,19 +16508,19 @@
       </c>
       <c r="G8" s="30"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="9">
-        <v>4.4666666666666668</v>
+      <c r="I8" s="9" t="n">
+        <v>4.466666666666667</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="30" t="str">
-        <f>VLOOKUP("label.lightRangeRpm",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>亮灯范围 (rpm)</v>
+        <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>普通档亮灯范围 (rpm)</v>
       </c>
       <c r="L8" s="30"/>
       <c r="M8" s="30"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="31">
-        <v>800</v>
+      <c r="O8" s="31" t="n">
+        <v>500</v>
       </c>
       <c r="P8" s="31"/>
       <c r="Q8" s="1"/>
@@ -16506,7 +16534,7 @@
       <c r="C9" s="32"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$67:$B$81,MATCH(D8,Samples!$C$67:$C$81,0))</f>
-        <v>5242</v>
+        <v>4719</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="32" t="str">
@@ -16515,8 +16543,8 @@
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="10">
-        <v>1.2E-2</v>
+      <c r="I9" s="10" t="n">
+        <v>0.012</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="32" t="str">
@@ -16543,12 +16571,17 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
+      <c r="K10" s="30" t="str">
+        <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>最高档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="31" t="n">
+        <v>250</v>
+      </c>
+      <c r="P10" s="31"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
@@ -16565,12 +16598,17 @@
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
+      <c r="K11" s="30" t="str">
+        <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>空档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="31"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -16691,23 +16729,23 @@
       <c r="B15" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="12">
-        <v>3.5150000000000001</v>
-      </c>
-      <c r="D15" s="22">
-        <v>6970</v>
+      <c r="C15" s="12" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>6980</v>
       </c>
       <c r="E15" s="13">
         <f>D15*C16/C15</f>
-        <v>5671.1806543385492</v>
+        <v>5679.3172119487908</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" ref="F15:F20" si="0">D15*2*PI()/60*$D$22/(C15*$I$8)*3.6</f>
-        <v>54.392420396083736</v>
+        <v>54.470458301960477</v>
       </c>
       <c r="G15" s="13">
         <f t="shared" ref="G15:G20" si="1">MAX(0,D15-$O$8)</f>
-        <v>6170</v>
+        <v>6480</v>
       </c>
       <c r="H15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16717,23 +16755,23 @@
       <c r="J15" s="11">
         <v>1</v>
       </c>
-      <c r="K15" s="12">
-        <v>3.2349999999999999</v>
-      </c>
-      <c r="L15" s="22">
-        <v>7080</v>
+      <c r="K15" s="12" t="n">
+        <v>3.235</v>
+      </c>
+      <c r="L15" s="22" t="n">
+        <v>7090</v>
       </c>
       <c r="M15" s="13">
         <f>L15*K16/K15</f>
-        <v>5679.3199381761988</v>
+        <v>5687.3415765069567</v>
       </c>
       <c r="N15" s="14">
         <f t="shared" ref="N15:N20" si="2">L15*2*PI()/60*$L$22/(K15*$I$8)*3.6</f>
-        <v>59.848264070040173</v>
+        <v>59.93279551646679</v>
       </c>
       <c r="O15" s="13">
         <f t="shared" ref="O15:O20" si="3">MAX(0,L15-$O$8)</f>
-        <v>6280</v>
+        <v>6590</v>
       </c>
       <c r="P15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16746,23 +16784,23 @@
       <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="12" t="n">
         <v>2.86</v>
       </c>
-      <c r="D16" s="22">
-        <v>7180</v>
+      <c r="D16" s="22" t="n">
+        <v>7190</v>
       </c>
       <c r="E16" s="16">
         <f>D16*C17/C16</f>
-        <v>5761.5734265734263</v>
+        <v>5769.5979020979021</v>
       </c>
       <c r="F16" s="17">
         <f t="shared" si="0"/>
-        <v>68.863540459624303</v>
+        <v>68.959450683105686</v>
       </c>
       <c r="G16" s="16">
         <f t="shared" si="1"/>
-        <v>6380</v>
+        <v>6690</v>
       </c>
       <c r="H16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16772,10 +16810,10 @@
       <c r="J16" s="15">
         <v>2</v>
       </c>
-      <c r="K16" s="12">
-        <v>2.5950000000000002</v>
-      </c>
-      <c r="L16" s="22">
+      <c r="K16" s="12" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="L16" s="22" t="n">
         <v>7220</v>
       </c>
       <c r="M16" s="16">
@@ -16788,7 +16826,7 @@
       </c>
       <c r="O16" s="16">
         <f t="shared" si="3"/>
-        <v>6420</v>
+        <v>6720</v>
       </c>
       <c r="P16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16801,10 +16839,10 @@
       <c r="B17" s="11">
         <v>3</v>
       </c>
-      <c r="C17" s="12">
-        <v>2.2949999999999999</v>
-      </c>
-      <c r="D17" s="22">
+      <c r="C17" s="12" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="D17" s="22" t="n">
         <v>7250</v>
       </c>
       <c r="E17" s="13">
@@ -16817,7 +16855,7 @@
       </c>
       <c r="G17" s="13">
         <f t="shared" si="1"/>
-        <v>6450</v>
+        <v>6750</v>
       </c>
       <c r="H17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16827,23 +16865,23 @@
       <c r="J17" s="11">
         <v>3</v>
       </c>
-      <c r="K17" s="12">
-        <v>2.0830000000000002</v>
-      </c>
-      <c r="L17" s="22">
-        <v>7240</v>
+      <c r="K17" s="12" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="L17" s="22" t="n">
+        <v>7250</v>
       </c>
       <c r="M17" s="13">
         <f>L17*K18/K17</f>
-        <v>5863.6005760921744</v>
+        <v>5871.6994719155064</v>
       </c>
       <c r="N17" s="14">
         <f t="shared" si="2"/>
-        <v>95.047758969573351</v>
+        <v>95.179040404614213</v>
       </c>
       <c r="O17" s="13">
         <f t="shared" si="3"/>
-        <v>6440</v>
+        <v>6750</v>
       </c>
       <c r="P17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16856,23 +16894,23 @@
       <c r="B18" s="15">
         <v>4</v>
       </c>
-      <c r="C18" s="12">
-        <v>1.8480000000000001</v>
-      </c>
-      <c r="D18" s="22">
-        <v>7290</v>
+      <c r="C18" s="12" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>7300</v>
       </c>
       <c r="E18" s="16">
         <f>D18*C19/C18</f>
-        <v>5881.704545454546</v>
+        <v>5889.7727272727279</v>
       </c>
       <c r="F18" s="17">
         <f t="shared" si="0"/>
-        <v>108.20728427773237</v>
+        <v>108.35571676645353</v>
       </c>
       <c r="G18" s="16">
         <f t="shared" si="1"/>
-        <v>6490</v>
+        <v>6800</v>
       </c>
       <c r="H18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16882,23 +16920,23 @@
       <c r="J18" s="15">
         <v>4</v>
       </c>
-      <c r="K18" s="12">
-        <v>1.6870000000000001</v>
-      </c>
-      <c r="L18" s="22">
-        <v>7240</v>
+      <c r="K18" s="12" t="n">
+        <v>1.687</v>
+      </c>
+      <c r="L18" s="22" t="n">
+        <v>7250</v>
       </c>
       <c r="M18" s="16">
         <f>L18*K19/K18</f>
-        <v>5922.4659158269105</v>
+        <v>5930.6461173681091</v>
       </c>
       <c r="N18" s="17">
         <f t="shared" si="2"/>
-        <v>117.35891045265043</v>
+        <v>117.52100839526462</v>
       </c>
       <c r="O18" s="16">
         <f t="shared" si="3"/>
-        <v>6440</v>
+        <v>6750</v>
       </c>
       <c r="P18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16911,23 +16949,23 @@
       <c r="B19" s="11">
         <v>5</v>
       </c>
-      <c r="C19" s="12">
-        <v>1.4910000000000001</v>
-      </c>
-      <c r="D19" s="22">
-        <v>7270</v>
+      <c r="C19" s="12" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>7280</v>
       </c>
       <c r="E19" s="13">
         <f>D19*C20/C19</f>
-        <v>5938.8732394366198</v>
+        <v>5947.0422535211255</v>
       </c>
       <c r="F19" s="14">
         <f t="shared" si="0"/>
-        <v>133.74812532993695</v>
+        <v>133.93209799201389</v>
       </c>
       <c r="G19" s="13">
         <f t="shared" si="1"/>
-        <v>6470</v>
+        <v>6780</v>
       </c>
       <c r="H19" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16937,23 +16975,23 @@
       <c r="J19" s="11">
         <v>5</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="12" t="n">
         <v>1.38</v>
       </c>
-      <c r="L19" s="22">
-        <v>7240</v>
+      <c r="L19" s="22" t="n">
+        <v>7250</v>
       </c>
       <c r="M19" s="13">
         <f>L19*K20/K19</f>
-        <v>5970.376811594203</v>
+        <v>5978.6231884057979</v>
       </c>
       <c r="N19" s="14">
         <f t="shared" si="2"/>
-        <v>143.4670158939285</v>
+        <v>143.66517475566044</v>
       </c>
       <c r="O19" s="13">
         <f t="shared" si="3"/>
-        <v>6440</v>
+        <v>6750</v>
       </c>
       <c r="P19" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16966,7 +17004,7 @@
       <c r="B20" s="15">
         <v>6</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="12" t="n">
         <v>1.218</v>
       </c>
       <c r="D20" s="16">
@@ -16981,8 +17019,8 @@
         <v>191.4267268335079</v>
       </c>
       <c r="G20" s="16">
-        <f t="shared" si="1"/>
-        <v>7700</v>
+        <f>MAX(0,D20-$O$10)</f>
+        <v>8250</v>
       </c>
       <c r="H20" s="15" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -16992,8 +17030,8 @@
       <c r="J20" s="15">
         <v>6</v>
       </c>
-      <c r="K20" s="12">
-        <v>1.1379999999999999</v>
+      <c r="K20" s="12" t="n">
+        <v>1.138</v>
       </c>
       <c r="L20" s="16">
         <f>$O$7</f>
@@ -17007,8 +17045,8 @@
         <v>204.25337856904392</v>
       </c>
       <c r="O20" s="16">
-        <f t="shared" si="3"/>
-        <v>7700</v>
+        <f>MAX(0,L20-$O$10)</f>
+        <v>8250</v>
       </c>
       <c r="P20" s="15" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -17042,8 +17080,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="C22" s="34"/>
-      <c r="D22" s="18">
-        <v>0.32500000000000001</v>
+      <c r="D22" s="18" t="n">
+        <v>0.325</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="34" t="str">
@@ -17051,7 +17089,7 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="G22" s="34"/>
-      <c r="H22" s="19">
+      <c r="H22" s="19" t="n">
         <v>5.4748128000000005</v>
       </c>
       <c r="I22" s="1"/>
@@ -17060,8 +17098,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="K22" s="34"/>
-      <c r="L22" s="18">
-        <v>0.32400000000000001</v>
+      <c r="L22" s="18" t="n">
+        <v>0.324</v>
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="34" t="str">
@@ -17069,8 +17107,8 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="O22" s="34"/>
-      <c r="P22" s="19">
-        <v>5.7898434559999998</v>
+      <c r="P22" s="19" t="n">
+        <v>5.789843456</v>
       </c>
       <c r="Q22" s="1"/>
     </row>
@@ -17081,7 +17119,7 @@
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
       <c r="C23" s="34"/>
-      <c r="D23" s="20">
+      <c r="D23" s="20" t="n">
         <v>1.85</v>
       </c>
       <c r="E23" s="1"/>
@@ -17090,8 +17128,8 @@
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
       <c r="G23" s="34"/>
-      <c r="H23" s="21">
-        <v>9.7999999999999997E-4</v>
+      <c r="H23" s="21" t="n">
+        <v>0.00098</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="34" t="str">
@@ -18207,7 +18245,7 @@
       <c r="Q80" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="37">
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="E53:P53"/>
     <mergeCell ref="J13:P13"/>
@@ -18224,7 +18262,7 @@
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="K9:N9"/>
     <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B11:P11"/>
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="K7:N7"/>
@@ -18241,6 +18279,10 @@
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="O6:P6"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -18395,7 +18437,7 @@
       <c r="C6" s="30"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$97:$D$111)</f>
-        <v>369.61504422565332</v>
+        <v>369.05984338245162</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="30" t="str">
@@ -18404,7 +18446,7 @@
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
-      <c r="I6" s="7">
+      <c r="I6" s="7" t="n">
         <v>1380</v>
       </c>
       <c r="J6" s="1"/>
@@ -18415,7 +18457,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="O6" s="31" t="n">
         <v>3000</v>
       </c>
       <c r="P6" s="31"/>
@@ -18430,7 +18472,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$97:$B$111,MATCH(D6,Samples!$D$97:$D$111,0))</f>
-        <v>7023</v>
+        <v>6997</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="32" t="str">
@@ -18439,7 +18481,7 @@
       </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="8">
+      <c r="I7" s="8" t="n">
         <v>0.12171599999999999</v>
       </c>
       <c r="J7" s="1"/>
@@ -18450,7 +18492,7 @@
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="O7" s="32" t="n">
         <v>8500</v>
       </c>
       <c r="P7" s="32"/>
@@ -18465,7 +18507,7 @@
       <c r="C8" s="30"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$97:$C$111)</f>
-        <v>440.45937290107003</v>
+        <v>440.77961570266001</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="30" t="str">
@@ -18474,19 +18516,19 @@
       </c>
       <c r="G8" s="30"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="9">
-        <v>4.1333333333333337</v>
+      <c r="I8" s="9" t="n">
+        <v>4.133333333333334</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="30" t="str">
-        <f>VLOOKUP("label.lightRangeRpm",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>亮灯范围 (rpm)</v>
+        <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>普通档亮灯范围 (rpm)</v>
       </c>
       <c r="L8" s="30"/>
       <c r="M8" s="30"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="31">
-        <v>800</v>
+      <c r="O8" s="31" t="n">
+        <v>500</v>
       </c>
       <c r="P8" s="31"/>
       <c r="Q8" s="1"/>
@@ -18500,7 +18542,7 @@
       <c r="C9" s="32"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$97:$B$111,MATCH(D8,Samples!$C$97:$C$111,0))</f>
-        <v>4978</v>
+        <v>4910</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="32" t="str">
@@ -18509,8 +18551,8 @@
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="10">
-        <v>1.0999999999999999E-2</v>
+      <c r="I9" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="32" t="str">
@@ -18537,12 +18579,17 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
+      <c r="K10" s="30" t="str">
+        <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>最高档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="31" t="n">
+        <v>250</v>
+      </c>
+      <c r="P10" s="31"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
@@ -18559,12 +18606,17 @@
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
+      <c r="K11" s="30" t="str">
+        <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>空档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="31"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -18685,23 +18737,23 @@
       <c r="B15" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="12">
-        <v>4.2530000000000001</v>
-      </c>
-      <c r="D15" s="22">
-        <v>7550</v>
+      <c r="C15" s="12" t="n">
+        <v>4.253</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>7520</v>
       </c>
       <c r="E15" s="13">
         <f>D15*C16/C15</f>
-        <v>5394.885962849753</v>
+        <v>5373.4493298847874</v>
       </c>
       <c r="F15" s="14">
         <f>D15*2*PI()/60*$D$22/(C15*$I$8)*3.6</f>
-        <v>52.621790131985449</v>
+        <v>52.412696926163001</v>
       </c>
       <c r="G15" s="13">
         <f>MAX(0,D15-$O$8)</f>
-        <v>6750</v>
+        <v>7020</v>
       </c>
       <c r="H15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -18711,23 +18763,23 @@
       <c r="J15" s="11">
         <v>1</v>
       </c>
-      <c r="K15" s="12">
-        <v>3.6890000000000001</v>
-      </c>
-      <c r="L15" s="22">
-        <v>7860</v>
+      <c r="K15" s="12" t="n">
+        <v>3.689</v>
+      </c>
+      <c r="L15" s="22" t="n">
+        <v>7850</v>
       </c>
       <c r="M15" s="13">
         <f>L15*K16/K15</f>
-        <v>5382.043914339929</v>
+        <v>5375.1965302249928</v>
       </c>
       <c r="N15" s="14">
         <f>L15*2*PI()/60*$L$22/(K15*$I$8)*3.6</f>
-        <v>62.96360552124554</v>
+        <v>62.883499152897897</v>
       </c>
       <c r="O15" s="13">
         <f>MAX(0,L15-$O$8)</f>
-        <v>7060</v>
+        <v>7350</v>
       </c>
       <c r="P15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -18740,23 +18792,23 @@
       <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C16" s="12">
-        <v>3.0390000000000001</v>
-      </c>
-      <c r="D16" s="22">
-        <v>7770</v>
+      <c r="C16" s="12" t="n">
+        <v>3.039</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>7750</v>
       </c>
       <c r="E16" s="16">
         <f>D16*C17/C16</f>
-        <v>5668.3415597235935</v>
+        <v>5653.7512339585392</v>
       </c>
       <c r="F16" s="17">
         <f>D16*2*PI()/60*$D$22/(C16*$I$8)*3.6</f>
-        <v>75.788684346823146</v>
+        <v>75.593604078234165</v>
       </c>
       <c r="G16" s="16">
         <f>MAX(0,D16-$O$8)</f>
-        <v>6970</v>
+        <v>7250</v>
       </c>
       <c r="H16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -18766,23 +18818,23 @@
       <c r="J16" s="15">
         <v>2</v>
       </c>
-      <c r="K16" s="12">
-        <v>2.5259999999999998</v>
-      </c>
-      <c r="L16" s="22">
-        <v>7750</v>
+      <c r="K16" s="12" t="n">
+        <v>2.526</v>
+      </c>
+      <c r="L16" s="22" t="n">
+        <v>7730</v>
       </c>
       <c r="M16" s="16">
         <f>L16*K17/K16</f>
-        <v>5807.8978622327795</v>
+        <v>5792.9097387173397</v>
       </c>
       <c r="N16" s="17">
         <f>L16*2*PI()/60*$L$22/(K16*$I$8)*3.6</f>
-        <v>90.665916249681686</v>
+        <v>90.431939691618012</v>
       </c>
       <c r="O16" s="16">
         <f>MAX(0,L16-$O$8)</f>
-        <v>6950</v>
+        <v>7230</v>
       </c>
       <c r="P16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -18795,23 +18847,23 @@
       <c r="B17" s="11">
         <v>3</v>
       </c>
-      <c r="C17" s="12">
-        <v>2.2170000000000001</v>
-      </c>
-      <c r="D17" s="22">
-        <v>7550</v>
+      <c r="C17" s="12" t="n">
+        <v>2.217</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>7520</v>
       </c>
       <c r="E17" s="13">
         <f>D17*C18/C17</f>
-        <v>5986.8741542625166</v>
+        <v>5963.0852503382948</v>
       </c>
       <c r="F17" s="14">
         <f>D17*2*PI()/60*$D$22/(C17*$I$8)*3.6</f>
-        <v>100.94743952698879</v>
+        <v>100.54632387323919</v>
       </c>
       <c r="G17" s="13">
         <f>MAX(0,D17-$O$8)</f>
-        <v>6750</v>
+        <v>7020</v>
       </c>
       <c r="H17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -18821,23 +18873,23 @@
       <c r="J17" s="11">
         <v>3</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="12" t="n">
         <v>1.893</v>
       </c>
-      <c r="L17" s="22">
-        <v>7560</v>
+      <c r="L17" s="22" t="n">
+        <v>7540</v>
       </c>
       <c r="M17" s="13">
         <f>L17*K18/K17</f>
-        <v>6054.3898573692559</v>
+        <v>6038.3729529846796</v>
       </c>
       <c r="N17" s="14">
         <f>L17*2*PI()/60*$L$22/(K17*$I$8)*3.6</f>
-        <v>118.01762756621311</v>
+        <v>117.70541162027075</v>
       </c>
       <c r="O17" s="13">
         <f>MAX(0,L17-$O$8)</f>
-        <v>6760</v>
+        <v>7040</v>
       </c>
       <c r="P17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -18850,23 +18902,23 @@
       <c r="B18" s="15">
         <v>4</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="12" t="n">
         <v>1.758</v>
       </c>
-      <c r="D18" s="22">
-        <v>7780</v>
+      <c r="D18" s="22" t="n">
+        <v>7760</v>
       </c>
       <c r="E18" s="16">
         <f>D18*C19/C18</f>
-        <v>5947.8498293515368</v>
+        <v>5932.5597269624577</v>
       </c>
       <c r="F18" s="17">
         <f>D18*2*PI()/60*$D$22/(C18*$I$8)*3.6</f>
-        <v>131.18215938459414</v>
+        <v>130.84493018309135</v>
       </c>
       <c r="G18" s="16">
         <f>MAX(0,D18-$O$8)</f>
-        <v>6980</v>
+        <v>7260</v>
       </c>
       <c r="H18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -18876,23 +18928,23 @@
       <c r="J18" s="15">
         <v>4</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="12" t="n">
         <v>1.516</v>
       </c>
-      <c r="L18" s="22">
-        <v>7600</v>
+      <c r="L18" s="22" t="n">
+        <v>7570</v>
       </c>
       <c r="M18" s="16">
         <f>L18*K19/K18</f>
-        <v>6126.1213720316618</v>
+        <v>6101.9393139841686</v>
       </c>
       <c r="N18" s="17">
         <f>L18*2*PI()/60*$L$22/(K18*$I$8)*3.6</f>
-        <v>148.14605445526337</v>
+        <v>147.56126739820309</v>
       </c>
       <c r="O18" s="16">
         <f>MAX(0,L18-$O$8)</f>
-        <v>6800</v>
+        <v>7070</v>
       </c>
       <c r="P18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -18905,8 +18957,8 @@
       <c r="B19" s="11">
         <v>5</v>
       </c>
-      <c r="C19" s="12">
-        <v>1.3440000000000001</v>
+      <c r="C19" s="12" t="n">
+        <v>1.344</v>
       </c>
       <c r="D19" s="13">
         <f>$O$7</f>
@@ -18920,8 +18972,8 @@
         <v>187.47083177293638</v>
       </c>
       <c r="G19" s="13">
-        <f>MAX(0,D19-$O$8)</f>
-        <v>7700</v>
+        <f>MAX(0,D19-$O$10)</f>
+        <v>8250</v>
       </c>
       <c r="H19" s="11" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -18931,7 +18983,7 @@
       <c r="J19" s="11">
         <v>5</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="12" t="n">
         <v>1.222</v>
       </c>
       <c r="L19" s="13">
@@ -18946,8 +18998,8 @@
         <v>205.55281007306004</v>
       </c>
       <c r="O19" s="13">
-        <f>MAX(0,L19-$O$8)</f>
-        <v>7700</v>
+        <f>MAX(0,L19-$O$10)</f>
+        <v>8250</v>
       </c>
       <c r="P19" s="11" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -19000,8 +19052,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="C22" s="34"/>
-      <c r="D22" s="18">
-        <v>0.32500000000000001</v>
+      <c r="D22" s="18" t="n">
+        <v>0.325</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="34" t="str">
@@ -19009,7 +19061,7 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="G22" s="34"/>
-      <c r="H22" s="19">
+      <c r="H22" s="19" t="n">
         <v>5.4748128000000005</v>
       </c>
       <c r="I22" s="1"/>
@@ -19018,8 +19070,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="K22" s="34"/>
-      <c r="L22" s="18">
-        <v>0.32400000000000001</v>
+      <c r="L22" s="18" t="n">
+        <v>0.324</v>
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="34" t="str">
@@ -19027,8 +19079,8 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="O22" s="34"/>
-      <c r="P22" s="19">
-        <v>5.7898434559999998</v>
+      <c r="P22" s="19" t="n">
+        <v>5.789843456</v>
       </c>
       <c r="Q22" s="1"/>
     </row>
@@ -19039,7 +19091,7 @@
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
       <c r="C23" s="34"/>
-      <c r="D23" s="20">
+      <c r="D23" s="20" t="n">
         <v>1.65</v>
       </c>
       <c r="E23" s="1"/>
@@ -19048,8 +19100,8 @@
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
       <c r="G23" s="34"/>
-      <c r="H23" s="21">
-        <v>7.7999999999999999E-4</v>
+      <c r="H23" s="21" t="n">
+        <v>0.00078</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="34" t="str">
@@ -20165,10 +20217,10 @@
       <c r="Q80" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="38">
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="E53:P53"/>
-    <mergeCell ref="B11:P11"/>
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="F22:G22"/>
@@ -20200,6 +20252,10 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="K5:P5"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -20283,7 +20339,7 @@
       <c r="A3" s="1"/>
       <c r="B3" s="35" t="str">
         <f>VLOOKUP("note.rally1Calibration",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>2022 预测曲线</v>
+        <v>2022 实测曲线</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -20357,7 +20413,7 @@
       <c r="C6" s="30"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$437:$D$451)</f>
-        <v>379.08311881213342</v>
+        <v>379.28148996854014</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="30" t="str">
@@ -20366,7 +20422,7 @@
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
-      <c r="I6" s="7">
+      <c r="I6" s="7" t="n">
         <v>1460</v>
       </c>
       <c r="J6" s="1"/>
@@ -20377,7 +20433,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="O6" s="31" t="n">
         <v>3000</v>
       </c>
       <c r="P6" s="31"/>
@@ -20392,7 +20448,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$437:$B$451,MATCH(D6,Samples!$D$437:$D$451,0))</f>
-        <v>6843</v>
+        <v>6951</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="32" t="str">
@@ -20401,7 +20457,7 @@
       </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="8">
+      <c r="I7" s="8" t="n">
         <v>0.12171599999999999</v>
       </c>
       <c r="J7" s="1"/>
@@ -20412,7 +20468,7 @@
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="O7" s="32" t="n">
         <v>8500</v>
       </c>
       <c r="P7" s="32"/>
@@ -20427,7 +20483,7 @@
       <c r="C8" s="30"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$437:$C$451)</f>
-        <v>443.46248568368935</v>
+        <v>444.51603790308002</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="30" t="str">
@@ -20436,19 +20492,19 @@
       </c>
       <c r="G8" s="30"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="9">
-        <v>4.1333333333333337</v>
+      <c r="I8" s="9" t="n">
+        <v>4.133333333333334</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="30" t="str">
-        <f>VLOOKUP("label.lightRangeRpm",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>亮灯范围 (rpm)</v>
+        <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>普通档亮灯范围 (rpm)</v>
       </c>
       <c r="L8" s="30"/>
       <c r="M8" s="30"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="31">
-        <v>800</v>
+      <c r="O8" s="31" t="n">
+        <v>500</v>
       </c>
       <c r="P8" s="31"/>
       <c r="Q8" s="1"/>
@@ -20462,7 +20518,7 @@
       <c r="C9" s="32"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$437:$B$451,MATCH(D8,Samples!$C$437:$C$451,0))</f>
-        <v>5189</v>
+        <v>5083</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="32" t="str">
@@ -20471,8 +20527,8 @@
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="10">
-        <v>1.0999999999999999E-2</v>
+      <c r="I9" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="32" t="str">
@@ -20499,12 +20555,17 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
+      <c r="K10" s="30" t="str">
+        <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>最高档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="31" t="n">
+        <v>250</v>
+      </c>
+      <c r="P10" s="31"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
@@ -20521,12 +20582,17 @@
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
+      <c r="K11" s="30" t="str">
+        <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>空档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="31"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -20647,23 +20713,23 @@
       <c r="B15" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="12">
-        <v>4.2530000000000001</v>
-      </c>
-      <c r="D15" s="22">
-        <v>7710</v>
+      <c r="C15" s="12" t="n">
+        <v>4.253</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>7700</v>
       </c>
       <c r="E15" s="13">
         <f>D15*C16/C15</f>
-        <v>5509.2146719962384</v>
+        <v>5502.0691276745829</v>
       </c>
       <c r="F15" s="14">
         <f>D15*2*PI()/60*$D$22/(C15*$I$8)*3.6</f>
-        <v>53.736953896371908</v>
+        <v>53.667256161097754</v>
       </c>
       <c r="G15" s="13">
         <f>MAX(0,D15-$O$8)</f>
-        <v>6910</v>
+        <v>7200</v>
       </c>
       <c r="H15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -20673,10 +20739,10 @@
       <c r="J15" s="11">
         <v>1</v>
       </c>
-      <c r="K15" s="12">
-        <v>3.6890000000000001</v>
-      </c>
-      <c r="L15" s="22">
+      <c r="K15" s="12" t="n">
+        <v>3.689</v>
+      </c>
+      <c r="L15" s="22" t="n">
         <v>8010</v>
       </c>
       <c r="M15" s="13">
@@ -20689,7 +20755,7 @@
       </c>
       <c r="O15" s="13">
         <f>MAX(0,L15-$O$8)</f>
-        <v>7210</v>
+        <v>7510</v>
       </c>
       <c r="P15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -20702,10 +20768,10 @@
       <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C16" s="12">
-        <v>3.0390000000000001</v>
-      </c>
-      <c r="D16" s="22">
+      <c r="C16" s="12" t="n">
+        <v>3.039</v>
+      </c>
+      <c r="D16" s="22" t="n">
         <v>7890</v>
       </c>
       <c r="E16" s="16">
@@ -20718,7 +20784,7 @@
       </c>
       <c r="G16" s="16">
         <f>MAX(0,D16-$O$8)</f>
-        <v>7090</v>
+        <v>7390</v>
       </c>
       <c r="H16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -20728,10 +20794,10 @@
       <c r="J16" s="15">
         <v>2</v>
       </c>
-      <c r="K16" s="12">
-        <v>2.5259999999999998</v>
-      </c>
-      <c r="L16" s="22">
+      <c r="K16" s="12" t="n">
+        <v>2.526</v>
+      </c>
+      <c r="L16" s="22" t="n">
         <v>7850</v>
       </c>
       <c r="M16" s="16">
@@ -20744,7 +20810,7 @@
       </c>
       <c r="O16" s="16">
         <f>MAX(0,L16-$O$8)</f>
-        <v>7050</v>
+        <v>7350</v>
       </c>
       <c r="P16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -20757,23 +20823,23 @@
       <c r="B17" s="11">
         <v>3</v>
       </c>
-      <c r="C17" s="12">
-        <v>2.2170000000000001</v>
-      </c>
-      <c r="D17" s="22">
-        <v>7630</v>
+      <c r="C17" s="12" t="n">
+        <v>2.217</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>7620</v>
       </c>
       <c r="E17" s="13">
         <f>D17*C18/C17</f>
-        <v>6050.3112313937754</v>
+        <v>6042.3815967523678</v>
       </c>
       <c r="F17" s="14">
         <f>D17*2*PI()/60*$D$22/(C17*$I$8)*3.6</f>
-        <v>102.01708127032111</v>
+        <v>101.88337605240459</v>
       </c>
       <c r="G17" s="13">
         <f>MAX(0,D17-$O$8)</f>
-        <v>6830</v>
+        <v>7120</v>
       </c>
       <c r="H17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -20783,23 +20849,23 @@
       <c r="J17" s="11">
         <v>3</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="12" t="n">
         <v>1.893</v>
       </c>
-      <c r="L17" s="22">
-        <v>7640</v>
+      <c r="L17" s="22" t="n">
+        <v>7630</v>
       </c>
       <c r="M17" s="13">
         <f>L17*K18/K17</f>
-        <v>6118.4574749075537</v>
+        <v>6110.4490227152664</v>
       </c>
       <c r="N17" s="14">
         <f>L17*2*PI()/60*$L$22/(K17*$I$8)*3.6</f>
-        <v>119.26649134998256</v>
+        <v>119.11038337701139</v>
       </c>
       <c r="O17" s="13">
         <f>MAX(0,L17-$O$8)</f>
-        <v>6840</v>
+        <v>7130</v>
       </c>
       <c r="P17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -20812,10 +20878,10 @@
       <c r="B18" s="15">
         <v>4</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="12" t="n">
         <v>1.758</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="22" t="n">
         <v>7870</v>
       </c>
       <c r="E18" s="16">
@@ -20828,7 +20894,7 @@
       </c>
       <c r="G18" s="16">
         <f>MAX(0,D18-$O$8)</f>
-        <v>7070</v>
+        <v>7370</v>
       </c>
       <c r="H18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -20838,10 +20904,10 @@
       <c r="J18" s="15">
         <v>4</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="12" t="n">
         <v>1.516</v>
       </c>
-      <c r="L18" s="22">
+      <c r="L18" s="22" t="n">
         <v>7670</v>
       </c>
       <c r="M18" s="16">
@@ -20854,7 +20920,7 @@
       </c>
       <c r="O18" s="16">
         <f>MAX(0,L18-$O$8)</f>
-        <v>6870</v>
+        <v>7170</v>
       </c>
       <c r="P18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -20867,8 +20933,8 @@
       <c r="B19" s="11">
         <v>5</v>
       </c>
-      <c r="C19" s="12">
-        <v>1.3440000000000001</v>
+      <c r="C19" s="12" t="n">
+        <v>1.344</v>
       </c>
       <c r="D19" s="13">
         <f>$O$7</f>
@@ -20882,8 +20948,8 @@
         <v>187.47083177293638</v>
       </c>
       <c r="G19" s="13">
-        <f>MAX(0,D19-$O$8)</f>
-        <v>7700</v>
+        <f>MAX(0,D19-$O$10)</f>
+        <v>8250</v>
       </c>
       <c r="H19" s="11" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -20893,7 +20959,7 @@
       <c r="J19" s="11">
         <v>5</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="12" t="n">
         <v>1.222</v>
       </c>
       <c r="L19" s="13">
@@ -20908,8 +20974,8 @@
         <v>205.55281007306004</v>
       </c>
       <c r="O19" s="13">
-        <f>MAX(0,L19-$O$8)</f>
-        <v>7700</v>
+        <f>MAX(0,L19-$O$10)</f>
+        <v>8250</v>
       </c>
       <c r="P19" s="11" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -20962,8 +21028,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="C22" s="34"/>
-      <c r="D22" s="18">
-        <v>0.32500000000000001</v>
+      <c r="D22" s="18" t="n">
+        <v>0.325</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="34" t="str">
@@ -20971,7 +21037,7 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="G22" s="34"/>
-      <c r="H22" s="19">
+      <c r="H22" s="19" t="n">
         <v>5.4748128000000005</v>
       </c>
       <c r="I22" s="1"/>
@@ -20980,8 +21046,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="K22" s="34"/>
-      <c r="L22" s="18">
-        <v>0.32400000000000001</v>
+      <c r="L22" s="18" t="n">
+        <v>0.324</v>
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="34" t="str">
@@ -20989,8 +21055,8 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="O22" s="34"/>
-      <c r="P22" s="19">
-        <v>5.7898434559999998</v>
+      <c r="P22" s="19" t="n">
+        <v>5.789843456</v>
       </c>
       <c r="Q22" s="1"/>
     </row>
@@ -21001,7 +21067,7 @@
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
       <c r="C23" s="34"/>
-      <c r="D23" s="20">
+      <c r="D23" s="20" t="n">
         <v>1.65</v>
       </c>
       <c r="E23" s="1"/>
@@ -21010,8 +21076,8 @@
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
       <c r="G23" s="34"/>
-      <c r="H23" s="21">
-        <v>7.7999999999999999E-4</v>
+      <c r="H23" s="21" t="n">
+        <v>0.00078</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="34" t="str">
@@ -22127,10 +22193,10 @@
       <c r="Q80" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="38">
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="E53:P53"/>
-    <mergeCell ref="B11:P11"/>
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="F22:G22"/>
@@ -22162,6 +22228,10 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="K5:P5"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -22316,7 +22386,7 @@
       <c r="C6" s="30"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$127:$D$141)</f>
-        <v>595.02816984475828</v>
+        <v>593.67797109433252</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="30" t="str">
@@ -22325,7 +22395,7 @@
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
-      <c r="I6" s="7">
+      <c r="I6" s="7" t="n">
         <v>1306</v>
       </c>
       <c r="J6" s="1"/>
@@ -22336,7 +22406,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="O6" s="31" t="n">
         <v>3000</v>
       </c>
       <c r="P6" s="31"/>
@@ -22351,7 +22421,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$127:$B$141,MATCH(D6,Samples!$D$127:$D$141,0))</f>
-        <v>5690</v>
+        <v>6026</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="32" t="str">
@@ -22360,7 +22430,7 @@
       </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="8">
+      <c r="I7" s="8" t="n">
         <v>0.128</v>
       </c>
       <c r="J7" s="1"/>
@@ -22371,7 +22441,7 @@
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="O7" s="32" t="n">
         <v>8500</v>
       </c>
       <c r="P7" s="32"/>
@@ -22386,7 +22456,7 @@
       <c r="C8" s="30"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$127:$C$141)</f>
-        <v>849.65874099113</v>
+        <v>842.02176826692005</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="30" t="str">
@@ -22395,19 +22465,19 @@
       </c>
       <c r="G8" s="30"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="9">
+      <c r="I8" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="30" t="str">
-        <f>VLOOKUP("label.lightRangeRpm",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>亮灯范围 (rpm)</v>
+        <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>普通档亮灯范围 (rpm)</v>
       </c>
       <c r="L8" s="30"/>
       <c r="M8" s="30"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="31">
-        <v>800</v>
+      <c r="O8" s="31" t="n">
+        <v>500</v>
       </c>
       <c r="P8" s="31"/>
       <c r="Q8" s="1"/>
@@ -22421,7 +22491,7 @@
       <c r="C9" s="32"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$127:$B$141,MATCH(D8,Samples!$C$127:$C$141,0))</f>
-        <v>4141</v>
+        <v>4202</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="32" t="str">
@@ -22430,8 +22500,8 @@
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="10">
-        <v>1.2E-2</v>
+      <c r="I9" s="10" t="n">
+        <v>0.012</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="32" t="str">
@@ -22458,12 +22528,17 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
+      <c r="K10" s="30" t="str">
+        <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>最高档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="31" t="n">
+        <v>250</v>
+      </c>
+      <c r="P10" s="31"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
@@ -22480,12 +22555,17 @@
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
+      <c r="K11" s="30" t="str">
+        <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
+        <v>空档亮灯范围 (rpm)</v>
+      </c>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="31"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -22578,23 +22658,23 @@
       <c r="B15" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="12" t="n">
         <v>3.24</v>
       </c>
-      <c r="D15" s="22">
-        <v>6000</v>
+      <c r="D15" s="22" t="n">
+        <v>6180</v>
       </c>
       <c r="E15" s="13">
         <f>D15*C16/C15</f>
-        <v>4812.9629629629635</v>
+        <v>4957.3518518518522</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" ref="F15:F20" si="0">D15*2*PI()/60*$D$22/(C15*$I$8)*3.6</f>
-        <v>55.850536063818538</v>
+        <v>57.526052145733104</v>
       </c>
       <c r="G15" s="13">
         <f t="shared" ref="G15:G20" si="1">MAX(0,D15-$O$8)</f>
-        <v>5200</v>
+        <v>5680</v>
       </c>
       <c r="H15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -22615,23 +22695,23 @@
       <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C16" s="12">
-        <v>2.5990000000000002</v>
-      </c>
-      <c r="D16" s="22">
-        <v>6170</v>
+      <c r="C16" s="12" t="n">
+        <v>2.599</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>6400</v>
       </c>
       <c r="E16" s="16">
         <f>D16*C17/C16</f>
-        <v>4952.1431319738349</v>
+        <v>5136.7449018853404</v>
       </c>
       <c r="F16" s="17">
         <f t="shared" si="0"/>
-        <v>71.597851503436175</v>
+        <v>74.266815173742557</v>
       </c>
       <c r="G16" s="16">
         <f t="shared" si="1"/>
-        <v>5370</v>
+        <v>5900</v>
       </c>
       <c r="H16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -22652,23 +22732,23 @@
       <c r="B17" s="11">
         <v>3</v>
       </c>
-      <c r="C17" s="12">
-        <v>2.0859999999999999</v>
-      </c>
-      <c r="D17" s="22">
-        <v>6220</v>
+      <c r="C17" s="12" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>6470</v>
       </c>
       <c r="E17" s="13">
         <f>D17*C18/C17</f>
-        <v>5039.2138063278999</v>
+        <v>5241.7545541706613</v>
       </c>
       <c r="F17" s="14">
         <f t="shared" si="0"/>
-        <v>89.928466218194515</v>
+        <v>93.542954410244121</v>
       </c>
       <c r="G17" s="13">
         <f t="shared" si="1"/>
-        <v>5420</v>
+        <v>5970</v>
       </c>
       <c r="H17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -22689,23 +22769,23 @@
       <c r="B18" s="15">
         <v>4</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="12" t="n">
         <v>1.69</v>
       </c>
-      <c r="D18" s="22">
-        <v>6250</v>
+      <c r="D18" s="22" t="n">
+        <v>6500</v>
       </c>
       <c r="E18" s="16">
         <f>D18*C19/C18</f>
-        <v>5110.9467455621307</v>
+        <v>5315.3846153846152</v>
       </c>
       <c r="F18" s="17">
         <f t="shared" si="0"/>
-        <v>111.53583385525893</v>
+        <v>115.9972672094693</v>
       </c>
       <c r="G18" s="16">
         <f t="shared" si="1"/>
-        <v>5450</v>
+        <v>6000</v>
       </c>
       <c r="H18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -22726,23 +22806,23 @@
       <c r="B19" s="11">
         <v>5</v>
       </c>
-      <c r="C19" s="12">
-        <v>1.3819999999999999</v>
-      </c>
-      <c r="D19" s="22">
-        <v>6260</v>
+      <c r="C19" s="12" t="n">
+        <v>1.382</v>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>6520</v>
       </c>
       <c r="E19" s="13">
         <f>D19*C20/C19</f>
-        <v>5163.820549927641</v>
+        <v>5378.2923299565846</v>
       </c>
       <c r="F19" s="14">
         <f t="shared" si="0"/>
-        <v>136.61154277144155</v>
+        <v>142.28550461178898</v>
       </c>
       <c r="G19" s="13">
         <f t="shared" si="1"/>
-        <v>5460</v>
+        <v>6020</v>
       </c>
       <c r="H19" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -22763,8 +22843,8 @@
       <c r="B20" s="15">
         <v>6</v>
       </c>
-      <c r="C20" s="12">
-        <v>1.1399999999999999</v>
+      <c r="C20" s="12" t="n">
+        <v>1.14</v>
       </c>
       <c r="D20" s="16">
         <f>$O$7</f>
@@ -22778,8 +22858,8 @@
         <v>224.87189520432207</v>
       </c>
       <c r="G20" s="16">
-        <f t="shared" si="1"/>
-        <v>7700</v>
+        <f>MAX(0,D20-$O$10)</f>
+        <v>8250</v>
       </c>
       <c r="H20" s="15" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -22821,7 +22901,7 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="C22" s="34"/>
-      <c r="D22" s="18">
+      <c r="D22" s="18" t="n">
         <v>0.32</v>
       </c>
       <c r="E22" s="1"/>
@@ -22830,8 +22910,8 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="G22" s="34"/>
-      <c r="H22" s="19">
-        <v>5.2788544000000002</v>
+      <c r="H22" s="19" t="n">
+        <v>5.2788544</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -22850,7 +22930,7 @@
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
       <c r="C23" s="34"/>
-      <c r="D23" s="20">
+      <c r="D23" s="20" t="n">
         <v>1.85</v>
       </c>
       <c r="E23" s="1"/>
@@ -22859,8 +22939,8 @@
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
       <c r="G23" s="34"/>
-      <c r="H23" s="21">
-        <v>9.7999999999999997E-4</v>
+      <c r="H23" s="21" t="n">
+        <v>0.00098</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -23964,7 +24044,7 @@
       <c r="Q80" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="32">
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="E53:P53"/>
     <mergeCell ref="B13:H13"/>
@@ -23976,7 +24056,7 @@
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="K9:N9"/>
     <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B11:P11"/>
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="K7:N7"/>
@@ -23993,6 +24073,10 @@
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="O6:P6"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -25837,7 +25921,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6CD1CB5-45E7-4848-9CC2-99BB8DB20462}">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -26777,15 +26861,15 @@
       <c r="A63" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="B63" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="C63" s="24" t="s">
-        <v>235</v>
+      <c r="B63" s="24" t="str">
+        <v>2022 measured curve</v>
+      </c>
+      <c r="C63" s="24" t="str">
+        <v>2022 实测曲线</v>
       </c>
       <c r="D63" s="24" t="str">
         <f>IF(Rally2!$E$1="English",B63,C63)</f>
-        <v>2022 预测曲线</v>
+        <v>2022 实测曲线</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -26966,6 +27050,51 @@
       <c r="D75" s="24" t="str">
         <f>IF(Rally2!$E$1="English",B75,C75)</f>
         <v>25R1 · 档位图</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="24" t="str">
+        <v>label.topGearLightRangeRpm</v>
+      </c>
+      <c r="B76" s="24" t="str">
+        <v>Top-gear light range (rpm)</v>
+      </c>
+      <c r="C76" s="24" t="str">
+        <v>最高档亮灯范围 (rpm)</v>
+      </c>
+      <c r="D76" s="24" t="str">
+        <f>IF(Rally2!$E$1="English",B76,C76)</f>
+        <v>最高档亮灯范围 (rpm)</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="24" t="str">
+        <v>label.neutralLightRangeRpm</v>
+      </c>
+      <c r="B77" s="24" t="str">
+        <v>Neutral light range (rpm)</v>
+      </c>
+      <c r="C77" s="24" t="str">
+        <v>空档亮灯范围 (rpm)</v>
+      </c>
+      <c r="D77" s="24" t="str">
+        <f>IF(Rally2!$E$1="English",B77,C77)</f>
+        <v>空档亮灯范围 (rpm)</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="24" t="str">
+        <v>label.normalGearLightRangeRpm</v>
+      </c>
+      <c r="B78" s="24" t="str">
+        <v>Normal-gear light range (rpm)</v>
+      </c>
+      <c r="C78" s="24" t="str">
+        <v>普通档亮灯范围 (rpm)</v>
+      </c>
+      <c r="D78" s="24" t="str">
+        <f>IF(Rally2!$E$1="English",B78,C78)</f>
+        <v>普通档亮灯范围 (rpm)</v>
       </c>
     </row>
   </sheetData>
@@ -27095,14 +27224,14 @@
     </row>
     <row r="7" spans="1:13" ht="22.5" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="1">
+      <c r="B7" s="1" t="n">
         <v>2500</v>
       </c>
-      <c r="C7" s="3">
-        <v>393.18990963689998</v>
+      <c r="C7" s="3" t="n">
+        <v>393.1899096369</v>
       </c>
       <c r="D7" s="4">
-        <f>138.04359997421*735.49875/745.69987158227</f>
+        <f>138.04359997421*735.49875/745.6998715822702</f>
         <v>136.15517327513714</v>
       </c>
       <c r="E7" s="1"/>
@@ -27117,14 +27246,14 @@
     </row>
     <row r="8" spans="1:13" ht="22.5" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="1">
+      <c r="B8" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="C8" s="3">
-        <v>409.57588844470001</v>
+      <c r="C8" s="3" t="n">
+        <v>409.5758884447</v>
       </c>
       <c r="D8" s="4">
-        <f>172.55579164507*735.49875/745.69987158227</f>
+        <f>172.55579164507*735.49875/745.6998715822702</f>
         <v>170.19524060117456</v>
       </c>
       <c r="E8" s="1"/>
@@ -27139,14 +27268,14 @@
     </row>
     <row r="9" spans="1:13" ht="22.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="1">
+      <c r="B9" s="1" t="n">
         <v>3500</v>
       </c>
-      <c r="C9" s="3">
-        <v>421.65444683919998</v>
+      <c r="C9" s="3" t="n">
+        <v>421.6544468392</v>
       </c>
       <c r="D9" s="4">
-        <f>207.25195358344*735.49875/745.69987158227</f>
+        <f>207.25195358344*735.49875/745.6998715822702</f>
         <v>204.41676149445436</v>
       </c>
       <c r="E9" s="1"/>
@@ -27161,14 +27290,14 @@
     </row>
     <row r="10" spans="1:13" ht="22.5" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="1">
+      <c r="B10" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="C10" s="3">
-        <v>425.29867261765003</v>
+      <c r="C10" s="3" t="n">
+        <v>425.29867261765</v>
       </c>
       <c r="D10" s="4">
-        <f>238.90647605524*735.49875/745.69987158227</f>
+        <f>238.90647605524*735.49875/745.6998715822702</f>
         <v>235.63825233426769</v>
       </c>
       <c r="E10" s="1"/>
@@ -27183,14 +27312,14 @@
     </row>
     <row r="11" spans="1:13" ht="22.5" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="1">
+      <c r="B11" s="1" t="n">
         <v>4157</v>
       </c>
-      <c r="C11" s="3">
-        <v>425.46588144156999</v>
+      <c r="C11" s="3" t="n">
+        <v>425.46588144157</v>
       </c>
       <c r="D11" s="4">
-        <f>248.38116946764*735.49875/745.69987158227</f>
+        <f>248.38116946764*735.49875/745.6998715822702</f>
         <v>244.98333260988446</v>
       </c>
       <c r="E11" s="1"/>
@@ -27205,14 +27334,14 @@
     </row>
     <row r="12" spans="1:13" ht="22.5" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="1">
+      <c r="B12" s="1" t="n">
         <v>4500</v>
       </c>
-      <c r="C12" s="3">
-        <v>423.16781828923001</v>
+      <c r="C12" s="3" t="n">
+        <v>423.16781828923</v>
       </c>
       <c r="D12" s="4">
-        <f>267.42318069882*735.49875/745.69987158227</f>
+        <f>267.42318069882*735.49875/745.6998715822702</f>
         <v>263.76485047215976</v>
       </c>
       <c r="E12" s="1"/>
@@ -27227,14 +27356,14 @@
     </row>
     <row r="13" spans="1:13" ht="22.5" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="1">
+      <c r="B13" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="C13" s="3">
-        <v>409.08667914096998</v>
+      <c r="C13" s="3" t="n">
+        <v>409.08667914097</v>
       </c>
       <c r="D13" s="4">
-        <f>287.24947668298*735.49875/745.69987158227</f>
+        <f>287.24947668298*735.49875/745.6998715822702</f>
         <v>283.31992412738026</v>
       </c>
       <c r="E13" s="1"/>
@@ -27249,14 +27378,14 @@
     </row>
     <row r="14" spans="1:13" ht="22.5" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="1">
+      <c r="B14" s="1" t="n">
         <v>5275</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="3" t="n">
         <v>391.3253872784</v>
       </c>
       <c r="D14" s="4">
-        <f>289.89077243111*735.49875/745.69987158227</f>
+        <f>289.89077243111*735.49875/745.6998715822702</f>
         <v>285.92508713620288</v>
       </c>
       <c r="E14" s="1"/>
@@ -27271,14 +27400,14 @@
     </row>
     <row r="15" spans="1:13" ht="22.5" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="1">
+      <c r="B15" s="1" t="n">
         <v>5500</v>
       </c>
-      <c r="C15" s="3">
-        <v>374.92208099622002</v>
+      <c r="C15" s="3" t="n">
+        <v>374.92208099622</v>
       </c>
       <c r="D15" s="4">
-        <f>289.58603337593*735.49875/745.69987158227</f>
+        <f>289.58603337593*735.49875/745.6998715822702</f>
         <v>285.62451688977723</v>
       </c>
       <c r="E15" s="1"/>
@@ -27293,14 +27422,14 @@
     </row>
     <row r="16" spans="1:13" ht="22.5" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="1">
+      <c r="B16" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="C16" s="3">
-        <v>341.53645220662997</v>
+      <c r="C16" s="3" t="n">
+        <v>341.53645220663</v>
       </c>
       <c r="D16" s="4">
-        <f>287.78106597026*735.49875/745.69987158227</f>
+        <f>287.78106597026*735.49875/745.6998715822702</f>
         <v>283.84424131075082</v>
       </c>
       <c r="E16" s="1"/>
@@ -27315,14 +27444,14 @@
     </row>
     <row r="17" spans="1:13" ht="22.5" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1">
+      <c r="B17" s="1" t="n">
         <v>6500</v>
       </c>
-      <c r="C17" s="3">
-        <v>312.76661205507997</v>
+      <c r="C17" s="3" t="n">
+        <v>312.76661205508</v>
       </c>
       <c r="D17" s="4">
-        <f>285.50100817999*735.49875/745.69987158227</f>
+        <f>285.50100817999*735.49875/745.6998715822702</f>
         <v>281.5953745500351</v>
       </c>
       <c r="E17" s="1"/>
@@ -27337,14 +27466,14 @@
     </row>
     <row r="18" spans="1:13" ht="22.5" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1">
+      <c r="B18" s="1" t="n">
         <v>7000</v>
       </c>
-      <c r="C18" s="3">
-        <v>286.00976855711002</v>
+      <c r="C18" s="3" t="n">
+        <v>286.00976855711</v>
       </c>
       <c r="D18" s="4">
-        <f>281.1595310888*735.49875/745.69987158227</f>
+        <f>281.1595310888*735.49875/745.6998715822702</f>
         <v>277.31328855885954</v>
       </c>
       <c r="E18" s="1"/>
@@ -27359,14 +27488,14 @@
     </row>
     <row r="19" spans="1:13" ht="22.5" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1">
+      <c r="B19" s="1" t="n">
         <v>7499</v>
       </c>
-      <c r="C19" s="3">
-        <v>259.39155855516998</v>
+      <c r="C19" s="3" t="n">
+        <v>259.39155855517</v>
       </c>
       <c r="D19" s="4">
-        <f>273.17005871031*735.49875/745.69987158227</f>
+        <f>273.17005871031*735.49875/745.6998715822702</f>
         <v>269.43311159829449</v>
       </c>
       <c r="E19" s="1"/>
@@ -27646,15 +27775,15 @@
     </row>
     <row r="37" spans="1:13" ht="22.5" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="1">
+      <c r="B37" s="1" t="n">
         <v>2500</v>
       </c>
-      <c r="C37" s="3">
-        <v>375.5387979034</v>
+      <c r="C37" s="3" t="n">
+        <v>375.4463368962</v>
       </c>
       <c r="D37" s="4">
-        <f>131.84653604271*735.49875/745.69987158227</f>
-        <v>130.04288474058632</v>
+        <f>131.81407424759*735.49875/745.6998715822702</f>
+        <v>130.01086702053112</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -27668,15 +27797,15 @@
     </row>
     <row r="38" spans="1:13" ht="22.5" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="1">
+      <c r="B38" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="C38" s="3">
-        <v>393.47429806315</v>
+      <c r="C38" s="3" t="n">
+        <v>391.81465773047</v>
       </c>
       <c r="D38" s="4">
-        <f>165.77213383362*735.49875/745.69987158227</f>
-        <v>163.50438274952646</v>
+        <f>165.07292140551*735.49875/745.6998715822702</f>
+        <v>162.81473549805494</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -27690,15 +27819,15 @@
     </row>
     <row r="39" spans="1:13" ht="22.5" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="1">
+      <c r="B39" s="1" t="n">
         <v>3500</v>
       </c>
-      <c r="C39" s="3">
-        <v>403.52794593592</v>
+      <c r="C39" s="3" t="n">
+        <v>402.07401438857</v>
       </c>
       <c r="D39" s="4">
-        <f>198.34240038888*735.49875/745.69987158227</f>
-        <v>195.62909035840747</v>
+        <f>197.62776271383*735.49875/745.6998715822702</f>
+        <v>194.92422887628476</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -27712,15 +27841,15 @@
     </row>
     <row r="40" spans="1:13" ht="22.5" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="1">
+      <c r="B40" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="C40" s="3">
-        <v>407.20471675444003</v>
+      <c r="C40" s="3" t="n">
+        <v>408.63572203685</v>
       </c>
       <c r="D40" s="4">
-        <f>228.74241133674*735.49875/745.69987158227</f>
-        <v>225.61323130333525</v>
+        <f>229.5462615513*735.49875/745.6998715822702</f>
+        <v>226.40608490372765</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -27734,15 +27863,15 @@
     </row>
     <row r="41" spans="1:13" ht="22.5" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="1">
-        <v>4500</v>
-      </c>
-      <c r="C41" s="3">
-        <v>409.12826470105</v>
+      <c r="B41" s="1" t="n">
+        <v>4320</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>409.69872419624</v>
       </c>
       <c r="D41" s="4">
-        <f>258.55080923323*735.49875/745.69987158227</f>
-        <v>255.01385242165637</v>
+        <f>248.55486161474*735.49875/745.6998715822702</f>
+        <v>245.15464866067819</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -27756,15 +27885,15 @@
     </row>
     <row r="42" spans="1:13" ht="22.5" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="1">
-        <v>4715</v>
-      </c>
-      <c r="C42" s="3">
-        <v>409.34482245507002</v>
+      <c r="B42" s="1" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>409.49711025478</v>
       </c>
       <c r="D42" s="4">
-        <f>271.0471857995*735.49875/745.69987158227</f>
-        <v>267.33927943898806</v>
+        <f>258.78390316643*735.49875/745.6998715822702</f>
+        <v>255.24375764631117</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -27778,15 +27907,15 @@
     </row>
     <row r="43" spans="1:13" ht="22.5" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="1">
+      <c r="B43" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="C43" s="3">
-        <v>407.45143542004001</v>
+      <c r="C43" s="3" t="n">
+        <v>406.63916218112</v>
       </c>
       <c r="D43" s="4">
-        <f>286.10125326961*735.49875/745.69987158227</f>
-        <v>282.18740832921816</v>
+        <f>285.53089721868*735.49875/745.6998715822702</f>
+        <v>281.62485470878664</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -27800,15 +27929,15 @@
     </row>
     <row r="44" spans="1:13" ht="22.5" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="1">
+      <c r="B44" s="1" t="n">
         <v>5500</v>
       </c>
-      <c r="C44" s="3">
-        <v>392.98683843027999</v>
+      <c r="C44" s="3" t="n">
+        <v>392.64119207404</v>
       </c>
       <c r="D44" s="4">
-        <f>303.53906979173*735.49875/745.69987158227</f>
-        <v>299.38667675276599</v>
+        <f>303.27209603284*735.49875/745.6998715822702</f>
+        <v>299.12335517604402</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -27822,15 +27951,15 @@
     </row>
     <row r="45" spans="1:13" ht="22.5" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="1">
+      <c r="B45" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="C45" s="3">
-        <v>367.25870170296997</v>
+      <c r="C45" s="3" t="n">
+        <v>367.86271454908</v>
       </c>
       <c r="D45" s="4">
-        <f>309.45481801453*735.49875/745.69987158227</f>
-        <v>305.22149795764545</v>
+        <f>309.96376357391*735.49875/745.6998715822702</f>
+        <v>305.72348117771463</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -27844,15 +27973,15 @@
     </row>
     <row r="46" spans="1:13" ht="22.5" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="1">
-        <v>6060</v>
-      </c>
-      <c r="C46" s="3">
-        <v>363.72649618820998</v>
+      <c r="B46" s="1" t="n">
+        <v>6075</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>363.48537899789</v>
       </c>
       <c r="D46" s="4">
-        <f>309.54334185874*735.49875/745.69987158227</f>
-        <v>305.30881080191813</v>
+        <f>310.10383158588*735.49875/745.6998715822702</f>
+        <v>305.8616330691724</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -27866,15 +27995,15 @@
     </row>
     <row r="47" spans="1:13" ht="22.5" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="1">
+      <c r="B47" s="1" t="n">
         <v>6500</v>
       </c>
-      <c r="C47" s="3">
-        <v>335.54735400714998</v>
+      <c r="C47" s="3" t="n">
+        <v>336.27624911903</v>
       </c>
       <c r="D47" s="4">
-        <f>306.29582624471*735.49875/745.69987158227</f>
-        <v>302.10572097215004</v>
+        <f>306.96117951861*735.49875/745.6998715822702</f>
+        <v>302.76197226025005</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -27888,15 +28017,15 @@
     </row>
     <row r="48" spans="1:13" ht="22.5" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="1">
+      <c r="B48" s="1" t="n">
         <v>7000</v>
       </c>
-      <c r="C48" s="3">
-        <v>303.45837406874</v>
+      <c r="C48" s="3" t="n">
+        <v>303.09493534722</v>
       </c>
       <c r="D48" s="4">
-        <f>298.31223803498*735.49875/745.69987158227</f>
-        <v>294.23134768533191</v>
+        <f>297.9549626138*735.49875/745.6998715822702</f>
+        <v>293.87895976668301</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -27910,15 +28039,15 @@
     </row>
     <row r="49" spans="1:13" ht="22.5" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="1">
+      <c r="B49" s="1" t="n">
         <v>7500</v>
       </c>
-      <c r="C49" s="3">
-        <v>268.94344000078001</v>
+      <c r="C49" s="3" t="n">
+        <v>269.74304205366</v>
       </c>
       <c r="D49" s="4">
-        <f>283.26709107139*735.49875/745.69987158227</f>
-        <v>279.39201726972254</v>
+        <f>284.1092791074*735.49875/745.6998715822702</f>
+        <v>280.22268423287494</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -27932,15 +28061,15 @@
     </row>
     <row r="50" spans="1:13" ht="22.5" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="1">
+      <c r="B50" s="1" t="n">
         <v>7649</v>
       </c>
-      <c r="C50" s="3">
-        <v>256.53470931065999</v>
+      <c r="C50" s="3" t="n">
+        <v>258.10696802923</v>
       </c>
       <c r="D50" s="4">
-        <f>275.56540749578*735.49875/745.69987158227</f>
-        <v>271.79569218153762</v>
+        <f>277.25430220963*735.49875/745.6998715822702</f>
+        <v>273.46148293497112</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -28204,15 +28333,15 @@
     </row>
     <row r="67" spans="1:13" ht="22.5" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="1">
+      <c r="B67" s="1" t="n">
         <v>2500</v>
       </c>
-      <c r="C67" s="3">
-        <v>401.07451780446002</v>
+      <c r="C67" s="3" t="n">
+        <v>401.49191489076</v>
       </c>
       <c r="D67" s="4">
-        <f>140.81177807125*735.49875/745.69987158227</f>
-        <v>138.88548289129707</v>
+        <f>140.9583204799*735.49875/745.6998715822702</f>
+        <v>139.0300206101455</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -28226,15 +28355,15 @@
     </row>
     <row r="68" spans="1:13" ht="22.5" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="1">
+      <c r="B68" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="C68" s="3">
-        <v>420.15432548965998</v>
+      <c r="C68" s="3" t="n">
+        <v>420.79792263021</v>
       </c>
       <c r="D68" s="4">
-        <f>177.01252513491*735.49875/745.69987158227</f>
-        <v>174.59100629160596</v>
+        <f>177.2836749199*735.49875/745.6998715822702</f>
+        <v>174.8584467666858</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
@@ -28248,15 +28377,15 @@
     </row>
     <row r="69" spans="1:13" ht="22.5" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="1">
+      <c r="B69" s="1" t="n">
         <v>3500</v>
       </c>
-      <c r="C69" s="3">
-        <v>434.59303883507999</v>
+      <c r="C69" s="3" t="n">
+        <v>435.31957112794</v>
       </c>
       <c r="D69" s="4">
-        <f>213.61154136407*735.49875/745.69987158227</f>
-        <v>210.68935056335647</v>
+        <f>213.96864713673*735.49875/745.6998715822702</f>
+        <v>211.04157115426511</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -28270,15 +28399,15 @@
     </row>
     <row r="70" spans="1:13" ht="22.5" customHeight="1">
       <c r="A70" s="1"/>
-      <c r="B70" s="1">
+      <c r="B70" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="C70" s="3">
-        <v>445.04598601673001</v>
+      <c r="C70" s="3" t="n">
+        <v>445.08767979257</v>
       </c>
       <c r="D70" s="4">
-        <f>249.99929472476*735.49875/745.69987158227</f>
-        <v>246.57932202775831</v>
+        <f>250.02271570794*735.49875/745.6998715822702</f>
+        <v>246.60242261354236</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
@@ -28292,15 +28421,15 @@
     </row>
     <row r="71" spans="1:13" ht="22.5" customHeight="1">
       <c r="A71" s="1"/>
-      <c r="B71" s="1">
+      <c r="B71" s="1" t="n">
         <v>4500</v>
       </c>
-      <c r="C71" s="3">
-        <v>449.37292062704</v>
+      <c r="C71" s="3" t="n">
+        <v>450.64322868988</v>
       </c>
       <c r="D71" s="4">
-        <f>283.98363618441*735.49875/745.69987158227</f>
-        <v>280.09876009619853</v>
+        <f>284.78641420285*735.49875/745.6998715822702</f>
+        <v>280.89055616803807</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
@@ -28314,15 +28443,15 @@
     </row>
     <row r="72" spans="1:13" ht="22.5" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="1">
-        <v>5000</v>
-      </c>
-      <c r="C72" s="3">
-        <v>450.29178004523999</v>
+      <c r="B72" s="1" t="n">
+        <v>4719</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>451.20326615828</v>
       </c>
       <c r="D72" s="4">
-        <f>316.18257148889*735.49875/745.69987158227</f>
-        <v>311.85721623958699</v>
+        <f>299.01716242996*735.49875/745.6998715822702</f>
+        <v>294.92662876437004</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
@@ -28336,15 +28465,15 @@
     </row>
     <row r="73" spans="1:13" ht="22.5" customHeight="1">
       <c r="A73" s="1"/>
-      <c r="B73" s="1">
-        <v>5242</v>
-      </c>
-      <c r="C73" s="3">
-        <v>450.42287057639999</v>
+      <c r="B73" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>450.94250368996</v>
       </c>
       <c r="D73" s="4">
-        <f>331.5823112665*735.49875/745.69987158227</f>
-        <v>327.0462886645617</v>
+        <f>316.63949183351*735.49875/745.6998715822702</f>
+        <v>312.30788594616013</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -28358,15 +28487,15 @@
     </row>
     <row r="74" spans="1:13" ht="22.5" customHeight="1">
       <c r="A74" s="1"/>
-      <c r="B74" s="1">
+      <c r="B74" s="1" t="n">
         <v>5500</v>
       </c>
-      <c r="C74" s="3">
-        <v>450.06220861605999</v>
+      <c r="C74" s="3" t="n">
+        <v>450.01398097113</v>
       </c>
       <c r="D74" s="4">
-        <f>347.62350998166*735.49875/745.69987158227</f>
-        <v>342.86804491412022</v>
+        <f>347.58625943521*735.49875/745.6998715822702</f>
+        <v>342.83130395251504</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -28380,15 +28509,15 @@
     </row>
     <row r="75" spans="1:13" ht="22.5" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="1">
+      <c r="B75" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="C75" s="3">
-        <v>446.99380766573</v>
+      <c r="C75" s="3" t="n">
+        <v>446.55915850043</v>
       </c>
       <c r="D75" s="4">
-        <f>376.64019058885*735.49875/745.69987158227</f>
-        <v>371.48777937974825</v>
+        <f>376.27395208253*735.49875/745.6998715822702</f>
+        <v>371.12655099033117</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -28402,15 +28531,15 @@
     </row>
     <row r="76" spans="1:13" ht="22.5" customHeight="1">
       <c r="A76" s="1"/>
-      <c r="B76" s="1">
+      <c r="B76" s="1" t="n">
         <v>6500</v>
       </c>
-      <c r="C76" s="3">
-        <v>421.37375767764001</v>
+      <c r="C76" s="3" t="n">
+        <v>420.98622755331</v>
       </c>
       <c r="D76" s="4">
-        <f>384.64026529906*735.49875/745.69987158227</f>
-        <v>379.37841363288413</v>
+        <f>384.2865183295*735.49875/745.6998715822702</f>
+        <v>379.02950589688623</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
@@ -28424,15 +28553,15 @@
     </row>
     <row r="77" spans="1:13" ht="22.5" customHeight="1">
       <c r="A77" s="1"/>
-      <c r="B77" s="1">
-        <v>6589</v>
-      </c>
-      <c r="C77" s="3">
-        <v>415.94463169600999</v>
+      <c r="B77" s="1" t="n">
+        <v>6619</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>413.80998751977</v>
       </c>
       <c r="D77" s="4">
-        <f>384.88318239568*735.49875/745.69987158227</f>
-        <v>379.61800764077708</v>
+        <f>384.65134312426*735.49875/745.6998715822702</f>
+        <v>379.38933991421766</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -28446,15 +28575,15 @@
     </row>
     <row r="78" spans="1:13" ht="22.5" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="1">
+      <c r="B78" s="1" t="n">
         <v>7000</v>
       </c>
-      <c r="C78" s="3">
-        <v>388.61552309927998</v>
+      <c r="C78" s="3" t="n">
+        <v>388.98375720313</v>
       </c>
       <c r="D78" s="4">
-        <f>382.02526717757*735.49875/745.69987158227</f>
-        <v>376.79918850102615</v>
+        <f>382.38725665957*735.49875/745.6998715822702</f>
+        <v>377.15622599247598</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
@@ -28468,15 +28597,15 @@
     </row>
     <row r="79" spans="1:13" ht="22.5" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="1">
+      <c r="B79" s="1" t="n">
         <v>7500</v>
       </c>
-      <c r="C79" s="3">
-        <v>356.44475630423</v>
+      <c r="C79" s="3" t="n">
+        <v>356.39069102286</v>
       </c>
       <c r="D79" s="4">
-        <f>375.42863750704*735.49875/745.69987158227</f>
-        <v>370.29280025853808</v>
+        <f>375.37169276438*735.49875/745.6998715822702</f>
+        <v>370.23663451593626</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
@@ -28490,15 +28619,15 @@
     </row>
     <row r="80" spans="1:13" ht="22.5" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="1">
+      <c r="B80" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="C80" s="3">
-        <v>323.93917964009</v>
+      <c r="C80" s="3" t="n">
+        <v>324.80740390348</v>
       </c>
       <c r="D80" s="4">
-        <f>363.93797040422*735.49875/745.69987158227</f>
-        <v>358.95932467021913</v>
+        <f>364.91339973211*735.49875/745.6998715822702</f>
+        <v>359.92141019378801</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -28512,15 +28641,15 @@
     </row>
     <row r="81" spans="1:13" ht="22.5" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="1">
+      <c r="B81" s="1" t="n">
         <v>8499</v>
       </c>
-      <c r="C81" s="3">
-        <v>283.84920919076001</v>
+      <c r="C81" s="3" t="n">
+        <v>285.34487111657</v>
       </c>
       <c r="D81" s="4">
-        <f>338.78909413145*735.49875/745.69987158227</f>
-        <v>334.15448324885881</v>
+        <f>340.57424600985*735.49875/745.6998715822702</f>
+        <v>335.91521437562892</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
@@ -28769,15 +28898,15 @@
     </row>
     <row r="97" spans="1:13" ht="22.5" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="1">
+      <c r="B97" s="1" t="n">
         <v>2500</v>
       </c>
-      <c r="C97" s="3">
-        <v>392.12322294939003</v>
+      <c r="C97" s="3" t="n">
+        <v>392.7729202016</v>
       </c>
       <c r="D97" s="4">
-        <f>137.66910086632*735.49875/745.69987158227</f>
-        <v>135.78579728859611</v>
+        <f>137.89720068626*735.49875/745.6998715822702</f>
+        <v>136.01077671910764</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -28791,15 +28920,15 @@
     </row>
     <row r="98" spans="1:13" ht="22.5" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="B98" s="1">
+      <c r="B98" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="C98" s="3">
-        <v>413.34434636400999</v>
+      <c r="C98" s="3" t="n">
+        <v>414.05838390473</v>
       </c>
       <c r="D98" s="4">
-        <f>174.14345649033*735.49875/745.69987158227</f>
-        <v>171.76118630347156</v>
+        <f>174.4442830687*735.49875/745.6998715822702</f>
+        <v>172.0578975954937</v>
       </c>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
@@ -28813,15 +28942,15 @@
     </row>
     <row r="99" spans="1:13" ht="22.5" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="1">
+      <c r="B99" s="1" t="n">
         <v>3500</v>
       </c>
-      <c r="C99" s="3">
-        <v>426.43653820907002</v>
+      <c r="C99" s="3" t="n">
+        <v>426.22417942502</v>
       </c>
       <c r="D99" s="4">
-        <f>209.60245121497*735.49875/745.69987158227</f>
-        <v>206.73510448437605</v>
+        <f>209.49807244419*735.49875/745.6998715822702</f>
+        <v>206.63215360780916</v>
       </c>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
@@ -28835,15 +28964,15 @@
     </row>
     <row r="100" spans="1:13" ht="22.5" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="B100" s="1">
+      <c r="B100" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="C100" s="3">
-        <v>434.66000894194002</v>
+      <c r="C100" s="3" t="n">
+        <v>433.3301806194</v>
       </c>
       <c r="D100" s="4">
-        <f>244.16509550646*735.49875/745.69987158227</f>
-        <v>240.82493424275626</v>
+        <f>243.41808024694*735.49875/745.6998715822702</f>
+        <v>240.08813809923262</v>
       </c>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
@@ -28857,15 +28986,15 @@
     </row>
     <row r="101" spans="1:13" ht="22.5" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="1">
+      <c r="B101" s="1" t="n">
         <v>4500</v>
       </c>
-      <c r="C101" s="3">
-        <v>438.93000290914</v>
+      <c r="C101" s="3" t="n">
+        <v>439.48912900365</v>
       </c>
       <c r="D101" s="4">
-        <f>277.3841781179*735.49875/745.69987158227</f>
-        <v>273.58958214998773</v>
+        <f>277.73752086313*735.49875/745.6998715822702</f>
+        <v>273.93809119141594</v>
       </c>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
@@ -28879,15 +29008,15 @@
     </row>
     <row r="102" spans="1:13" ht="22.5" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="1">
-        <v>4978</v>
-      </c>
-      <c r="C102" s="3">
-        <v>440.45937290107003</v>
+      <c r="B102" s="1" t="n">
+        <v>4910</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>440.77961570266</v>
       </c>
       <c r="D102" s="4">
-        <f>307.91769862379*735.49875/745.69987158227</f>
-        <v>303.7054062516201</v>
+        <f>303.93232884831*735.49875/745.6998715822702</f>
+        <v>299.77455605322371</v>
       </c>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
@@ -28901,15 +29030,15 @@
     </row>
     <row r="103" spans="1:13" ht="22.5" customHeight="1">
       <c r="A103" s="1"/>
-      <c r="B103" s="1">
+      <c r="B103" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="C103" s="3">
-        <v>440.45531734092998</v>
+      <c r="C103" s="3" t="n">
+        <v>440.7455668384</v>
       </c>
       <c r="D103" s="4">
-        <f>309.27567642656*735.49875/745.69987158227</f>
-        <v>305.04480701394795</v>
+        <f>309.47948168473*735.49875/745.6998715822702</f>
+        <v>305.24582423057882</v>
       </c>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
@@ -28923,15 +29052,15 @@
     </row>
     <row r="104" spans="1:13" ht="22.5" customHeight="1">
       <c r="A104" s="1"/>
-      <c r="B104" s="1">
+      <c r="B104" s="1" t="n">
         <v>5500</v>
       </c>
-      <c r="C104" s="3">
-        <v>438.54886894563998</v>
+      <c r="C104" s="3" t="n">
+        <v>438.74965911927</v>
       </c>
       <c r="D104" s="4">
-        <f>338.73072255979*735.49875/745.69987158227</f>
-        <v>334.09691019617696</v>
+        <f>338.88581086445*735.49875/745.6998715822702</f>
+        <v>334.24987690378146</v>
       </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
@@ -28945,15 +29074,15 @@
     </row>
     <row r="105" spans="1:13" ht="22.5" customHeight="1">
       <c r="A105" s="1"/>
-      <c r="B105" s="1">
+      <c r="B105" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="C105" s="3">
-        <v>430.32993219679997</v>
+      <c r="C105" s="3" t="n">
+        <v>430.00295381093</v>
       </c>
       <c r="D105" s="4">
-        <f>362.59908951557*735.49875/745.69987158227</f>
-        <v>357.63875957757472</v>
+        <f>362.32357518079*735.49875/745.6998715822702</f>
+        <v>357.36701425943784</v>
       </c>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
@@ -28967,15 +29096,15 @@
     </row>
     <row r="106" spans="1:13" ht="22.5" customHeight="1">
       <c r="A106" s="1"/>
-      <c r="B106" s="1">
+      <c r="B106" s="1" t="n">
         <v>6500</v>
       </c>
-      <c r="C106" s="3">
-        <v>407.30321335870002</v>
+      <c r="C106" s="3" t="n">
+        <v>406.35807005572</v>
       </c>
       <c r="D106" s="4">
-        <f>371.79632853004*735.49875/745.69987158227</f>
-        <v>366.71018101183154</v>
+        <f>370.93357862172*735.49875/745.6998715822702</f>
+        <v>365.85923346133035</v>
       </c>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
@@ -28989,15 +29118,15 @@
     </row>
     <row r="107" spans="1:13" ht="22.5" customHeight="1">
       <c r="A107" s="1"/>
-      <c r="B107" s="1">
-        <v>7000</v>
-      </c>
-      <c r="C107" s="3">
-        <v>381.20202297351</v>
+      <c r="B107" s="1" t="n">
+        <v>6997</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>380.79667249825</v>
       </c>
       <c r="D107" s="4">
-        <f>374.7374873594*735.49875/745.69987158227</f>
-        <v>369.61110499610913</v>
+        <f>374.1785799316*735.49875/745.6998715822702</f>
+        <v>369.05984338245162</v>
       </c>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
@@ -29011,15 +29140,15 @@
     </row>
     <row r="108" spans="1:13" ht="22.5" customHeight="1">
       <c r="A108" s="1"/>
-      <c r="B108" s="1">
-        <v>7023</v>
-      </c>
-      <c r="C108" s="3">
-        <v>379.95765344646998</v>
+      <c r="B108" s="1" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>380.63334389029</v>
       </c>
       <c r="D108" s="4">
-        <f>374.74148122474*735.49875/745.69987158227</f>
-        <v>369.61504422565332</v>
+        <f>374.17845210272*735.49875/745.6998715822702</f>
+        <v>369.05971730226167</v>
       </c>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
@@ -29033,15 +29162,15 @@
     </row>
     <row r="109" spans="1:13" ht="22.5" customHeight="1">
       <c r="A109" s="1"/>
-      <c r="B109" s="1">
+      <c r="B109" s="1" t="n">
         <v>7500</v>
       </c>
-      <c r="C109" s="3">
-        <v>353.21169403024999</v>
+      <c r="C109" s="3" t="n">
+        <v>351.86158862311</v>
       </c>
       <c r="D109" s="4">
-        <f>372.02338566077*735.49875/745.69987158227</f>
-        <v>366.93413201704772</v>
+        <f>370.60137502792*735.49875/745.6998715822702</f>
+        <v>365.53157438923347</v>
       </c>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
@@ -29055,15 +29184,15 @@
     </row>
     <row r="110" spans="1:13" ht="22.5" customHeight="1">
       <c r="A110" s="1"/>
-      <c r="B110" s="1">
+      <c r="B110" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="C110" s="3">
-        <v>321.39007141308002</v>
+      <c r="C110" s="3" t="n">
+        <v>321.04792098375</v>
       </c>
       <c r="D110" s="4">
-        <f>361.07410788686*735.49875/745.69987158227</f>
-        <v>356.13463958985204</v>
+        <f>360.68971001019*735.49875/745.6998715822702</f>
+        <v>355.75550024898888</v>
       </c>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
@@ -29077,15 +29206,15 @@
     </row>
     <row r="111" spans="1:13" ht="22.5" customHeight="1">
       <c r="A111" s="1"/>
-      <c r="B111" s="1">
+      <c r="B111" s="1" t="n">
         <v>8499</v>
       </c>
-      <c r="C111" s="3">
-        <v>278.85280319881002</v>
+      <c r="C111" s="3" t="n">
+        <v>280.43430803348</v>
       </c>
       <c r="D111" s="4">
-        <f>332.8256184369*735.49875/745.69987158227</f>
-        <v>328.27258748067237</v>
+        <f>334.71322838244*735.49875/745.6998715822702</f>
+        <v>330.13437505545949</v>
       </c>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -29334,15 +29463,15 @@
     </row>
     <row r="127" spans="1:13" ht="22.5" customHeight="1">
       <c r="A127" s="1"/>
-      <c r="B127" s="1">
+      <c r="B127" s="1" t="n">
         <v>2500</v>
       </c>
-      <c r="C127" s="3">
-        <v>781.33066149713</v>
+      <c r="C127" s="3" t="n">
+        <v>781.05167032924</v>
       </c>
       <c r="D127" s="4">
-        <f>274.31450970575*735.49875/745.69987158227</f>
-        <v>270.56190658493745</v>
+        <f>274.21655972221*735.49875/745.6998715822702</f>
+        <v>270.46529655025506</v>
       </c>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
@@ -29356,15 +29485,15 @@
     </row>
     <row r="128" spans="1:13" ht="22.5" customHeight="1">
       <c r="A128" s="1"/>
-      <c r="B128" s="1">
+      <c r="B128" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="C128" s="3">
-        <v>815.57037906490996</v>
+      <c r="C128" s="3" t="n">
+        <v>822.79785742474</v>
       </c>
       <c r="D128" s="4">
-        <f>343.60272753414*735.49875/745.69987158227</f>
-        <v>338.90226648653652</v>
+        <f>346.64769010436*735.49875/745.6998715822702</f>
+        <v>341.90557418382974</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -29378,15 +29507,15 @@
     </row>
     <row r="129" spans="1:13" ht="22.5" customHeight="1">
       <c r="A129" s="1"/>
-      <c r="B129" s="1">
+      <c r="B129" s="1" t="n">
         <v>3500</v>
       </c>
-      <c r="C129" s="3">
-        <v>839.31014412132004</v>
+      <c r="C129" s="3" t="n">
+        <v>839.28713128853</v>
       </c>
       <c r="D129" s="4">
-        <f>412.53843837174*735.49875/745.69987158227</f>
-        <v>406.89494166808578</v>
+        <f>412.52712708453*735.49875/745.6998715822702</f>
+        <v>406.883785118486</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -29400,15 +29529,15 @@
     </row>
     <row r="130" spans="1:13" ht="22.5" customHeight="1">
       <c r="A130" s="1"/>
-      <c r="B130" s="1">
+      <c r="B130" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="C130" s="3">
-        <v>849.15980634939001</v>
+      <c r="C130" s="3" t="n">
+        <v>841.83376436275</v>
       </c>
       <c r="D130" s="4">
-        <f>477.00543172178*735.49875/745.69987158227</f>
-        <v>470.48003110172607</v>
+        <f>472.8901146819*735.49875/745.6998715822702</f>
+        <v>466.42101130832987</v>
       </c>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
@@ -29422,15 +29551,15 @@
     </row>
     <row r="131" spans="1:13" ht="22.5" customHeight="1">
       <c r="A131" s="1"/>
-      <c r="B131" s="1">
-        <v>4141</v>
-      </c>
-      <c r="C131" s="3">
-        <v>849.65874099113</v>
+      <c r="B131" s="1" t="n">
+        <v>4202</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>842.02176826692</v>
       </c>
       <c r="D131" s="4">
-        <f>494.11002333565*735.49875/745.69987158227</f>
-        <v>487.35063311023652</v>
+        <f>496.88200768514*735.49875/745.6998715822702</f>
+        <v>490.08469690958179</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -29444,15 +29573,15 @@
     </row>
     <row r="132" spans="1:13" ht="22.5" customHeight="1">
       <c r="A132" s="1"/>
-      <c r="B132" s="1">
+      <c r="B132" s="1" t="n">
         <v>4500</v>
       </c>
-      <c r="C132" s="3">
-        <v>846.29453700936006</v>
+      <c r="C132" s="3" t="n">
+        <v>838.56059242494</v>
       </c>
       <c r="D132" s="4">
-        <f>534.8203883037*735.49875/745.69987158227</f>
-        <v>527.5040831604706</v>
+        <f>529.93288039141*735.49875/745.6998715822702</f>
+        <v>522.68343601126708</v>
       </c>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
@@ -29466,15 +29595,15 @@
     </row>
     <row r="133" spans="1:13" ht="22.5" customHeight="1">
       <c r="A133" s="1"/>
-      <c r="B133" s="1">
+      <c r="B133" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="C133" s="3">
-        <v>830.31349066587995</v>
+      <c r="C133" s="3" t="n">
+        <v>812.3620969044</v>
       </c>
       <c r="D133" s="4">
-        <f>583.02342226696*735.49875/745.69987158227</f>
-        <v>575.04770302318877</v>
+        <f>570.41844457729*735.49875/745.6998715822702</f>
+        <v>562.61516053815581</v>
       </c>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
@@ -29488,15 +29617,15 @@
     </row>
     <row r="134" spans="1:13" ht="22.5" customHeight="1">
       <c r="A134" s="1"/>
-      <c r="B134" s="1">
+      <c r="B134" s="1" t="n">
         <v>5500</v>
       </c>
-      <c r="C134" s="3">
-        <v>778.94554556110995</v>
+      <c r="C134" s="3" t="n">
+        <v>770.95605396983</v>
       </c>
       <c r="D134" s="4">
-        <f>601.64968186327*735.49875/745.69987158227</f>
-        <v>593.4191567035989</v>
+        <f>595.47867915129*735.49875/745.6998715822702</f>
+        <v>587.33257287292554</v>
       </c>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
@@ -29510,15 +29639,15 @@
     </row>
     <row r="135" spans="1:13" ht="22.5" customHeight="1">
       <c r="A135" s="1"/>
-      <c r="B135" s="1">
-        <v>5690</v>
-      </c>
-      <c r="C135" s="3">
-        <v>754.97659059928003</v>
+      <c r="B135" s="1" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>714.32480746778</v>
       </c>
       <c r="D135" s="4">
-        <f>603.28101147836*735.49875/745.69987158227</f>
-        <v>595.02816984475828</v>
+        <f>601.8952097614*735.49875/745.6998715822702</f>
+        <v>593.66132579742168</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
@@ -29532,15 +29661,15 @@
     </row>
     <row r="136" spans="1:13" ht="22.5" customHeight="1">
       <c r="A136" s="1"/>
-      <c r="B136" s="1">
-        <v>6000</v>
-      </c>
-      <c r="C136" s="3">
-        <v>713.52169310327997</v>
+      <c r="B136" s="1" t="n">
+        <v>6026</v>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>711.2626976159</v>
       </c>
       <c r="D136" s="4">
-        <f>601.21849983361*735.49875/745.69987158227</f>
-        <v>592.99387321365498</v>
+        <f>601.91208592301*735.49875/745.6998715822702</f>
+        <v>593.67797109433252</v>
       </c>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
@@ -29554,15 +29683,15 @@
     </row>
     <row r="137" spans="1:13" ht="22.5" customHeight="1">
       <c r="A137" s="1"/>
-      <c r="B137" s="1">
+      <c r="B137" s="1" t="n">
         <v>6500</v>
       </c>
-      <c r="C137" s="3">
-        <v>650.00523948523005</v>
+      <c r="C137" s="3" t="n">
+        <v>653.88859149238</v>
       </c>
       <c r="D137" s="4">
-        <f>593.34067014361*735.49875/745.69987158227</f>
-        <v>585.22381167748551</v>
+        <f>596.8854887733*735.49875/745.6998715822702</f>
+        <v>588.72013743865477</v>
       </c>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
@@ -29576,15 +29705,15 @@
     </row>
     <row r="138" spans="1:13" ht="22.5" customHeight="1">
       <c r="A138" s="1"/>
-      <c r="B138" s="1">
+      <c r="B138" s="1" t="n">
         <v>7000</v>
       </c>
-      <c r="C138" s="3">
-        <v>590.16354933322998</v>
+      <c r="C138" s="3" t="n">
+        <v>592.51204200031</v>
       </c>
       <c r="D138" s="4">
-        <f>580.15538292043*735.49875/745.69987158227</f>
-        <v>572.21889825237974</v>
+        <f>582.46404916065*735.49875/745.6998715822702</f>
+        <v>574.49598210147042</v>
       </c>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
@@ -29598,15 +29727,15 @@
     </row>
     <row r="139" spans="1:13" ht="22.5" customHeight="1">
       <c r="A139" s="1"/>
-      <c r="B139" s="1">
+      <c r="B139" s="1" t="n">
         <v>7500</v>
       </c>
-      <c r="C139" s="3">
-        <v>529.20441413318997</v>
+      <c r="C139" s="3" t="n">
+        <v>532.45096066695</v>
       </c>
       <c r="D139" s="4">
-        <f>557.3892970701*735.49875/745.69987158227</f>
-        <v>549.764250848752</v>
+        <f>560.80875133394*735.49875/745.6998715822702</f>
+        <v>553.13692721974292</v>
       </c>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
@@ -29620,15 +29749,15 @@
     </row>
     <row r="140" spans="1:13" ht="22.5" customHeight="1">
       <c r="A140" s="1"/>
-      <c r="B140" s="1">
+      <c r="B140" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="C140" s="3">
-        <v>466.5003138289</v>
+      <c r="C140" s="3" t="n">
+        <v>475.48818762327</v>
       </c>
       <c r="D140" s="4">
-        <f>524.10201691704*735.49875/745.69987158227</f>
-        <v>516.93233833745376</v>
+        <f>534.19967954188*735.49875/745.6998715822702</f>
+        <v>526.89186565067803</v>
       </c>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
@@ -29642,15 +29771,15 @@
     </row>
     <row r="141" spans="1:13" ht="22.5" customHeight="1">
       <c r="A141" s="1"/>
-      <c r="B141" s="1">
+      <c r="B141" s="1" t="n">
         <v>8499</v>
       </c>
-      <c r="C141" s="3">
-        <v>397.788442868</v>
+      <c r="C141" s="3" t="n">
+        <v>426.90977160884</v>
       </c>
       <c r="D141" s="4">
-        <f>474.78161591297*735.49875/745.69987158227</f>
-        <v>468.28663693613572</v>
+        <f>509.53946714019*735.49875/745.6998715822702</f>
+        <v>502.56900321315055</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
@@ -31525,19 +31654,19 @@
       </c>
       <c r="D240" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!D15,'WRC16'!L15)</f>
-        <v>6250</v>
+        <v>6280</v>
       </c>
       <c r="E240" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!F15,'WRC16'!N15)</f>
-        <v>48.792544792101062</v>
+        <v>49.026749007103156</v>
       </c>
       <c r="F240" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!E15,'WRC16'!M15)</f>
-        <v>5086.2523044508816</v>
+        <v>5110.6663155122469</v>
       </c>
       <c r="G240" s="20">
         <f>E240*'WRC16'!$O$7/D240</f>
-        <v>59.722074825531699</v>
+        <v>59.722074825531713</v>
       </c>
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
@@ -31557,19 +31686,19 @@
       </c>
       <c r="D241" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!D16,'WRC16'!L16)</f>
-        <v>6460</v>
+        <v>6490</v>
       </c>
       <c r="E241" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!F16,'WRC16'!N16)</f>
-        <v>61.970940584513983</v>
+        <v>62.258731330262492</v>
       </c>
       <c r="F241" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!E16,'WRC16'!M16)</f>
-        <v>5182.6343042071203</v>
+        <v>5206.7022653721688</v>
       </c>
       <c r="G241" s="20">
         <f>E241*'WRC16'!$O$7/D241</f>
-        <v>73.386640165871825</v>
+        <v>73.38664016587181</v>
       </c>
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
@@ -31589,19 +31718,19 @@
       </c>
       <c r="D242" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!D17,'WRC16'!L17)</f>
-        <v>6550</v>
+        <v>6570</v>
       </c>
       <c r="E242" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!F17,'WRC16'!N17)</f>
-        <v>78.321107954512669</v>
+        <v>78.560256375747812</v>
       </c>
       <c r="F242" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!E17,'WRC16'!M17)</f>
-        <v>5276.462283178701</v>
+        <v>5292.5736183945137</v>
       </c>
       <c r="G242" s="20">
         <f>E242*'WRC16'!$O$7/D242</f>
-        <v>91.474271122446098</v>
+        <v>91.474271122446083</v>
       </c>
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
@@ -31621,15 +31750,15 @@
       </c>
       <c r="D243" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!D18,'WRC16'!L18)</f>
-        <v>6610</v>
+        <v>6630</v>
       </c>
       <c r="E243" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!F18,'WRC16'!N18)</f>
-        <v>98.115459903837134</v>
+        <v>98.412329676617276</v>
       </c>
       <c r="F243" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!E18,'WRC16'!M18)</f>
-        <v>5332.3535302954424</v>
+        <v>5348.4877315973963</v>
       </c>
       <c r="G243" s="20">
         <f>E243*'WRC16'!$O$7/D243</f>
@@ -31653,19 +31782,19 @@
       </c>
       <c r="D244" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!D19,'WRC16'!L19)</f>
-        <v>6610</v>
+        <v>6640</v>
       </c>
       <c r="E244" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!F19,'WRC16'!N19)</f>
-        <v>121.62419207198188</v>
+        <v>122.17619294371551</v>
       </c>
       <c r="F244" s="20">
         <f>IF('WRC16'!$D$53=1,'WRC16'!E19,'WRC16'!M19)</f>
-        <v>5399.6027312228434</v>
+        <v>5424.1092489137181</v>
       </c>
       <c r="G244" s="20">
         <f>E244*'WRC16'!$O$7/D244</f>
-        <v>140.76022229208189</v>
+        <v>140.76022229208186</v>
       </c>
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
@@ -31839,7 +31968,7 @@
       <c r="A251" s="1"/>
       <c r="B251" s="1">
         <f>G240</f>
-        <v>59.722074825531699</v>
+        <v>59.722074825531713</v>
       </c>
       <c r="C251" s="1">
         <f>'WRC16'!$O$7</f>
@@ -31847,7 +31976,7 @@
       </c>
       <c r="D251" s="1">
         <f>G241</f>
-        <v>73.386640165871825</v>
+        <v>73.38664016587181</v>
       </c>
       <c r="E251" s="1">
         <f>'WRC16'!$O$7</f>
@@ -31855,7 +31984,7 @@
       </c>
       <c r="F251" s="1">
         <f>G242</f>
-        <v>91.474271122446098</v>
+        <v>91.474271122446083</v>
       </c>
       <c r="G251" s="1">
         <f>'WRC16'!$O$7</f>
@@ -31871,7 +32000,7 @@
       </c>
       <c r="J251" s="1">
         <f>G244</f>
-        <v>140.76022229208189</v>
+        <v>140.76022229208186</v>
       </c>
       <c r="K251" s="1">
         <f>'WRC16'!$O$7</f>
@@ -31970,43 +32099,43 @@
       <c r="A256" s="1"/>
       <c r="B256" s="1">
         <f>E240</f>
-        <v>48.792544792101062</v>
+        <v>49.026749007103156</v>
       </c>
       <c r="C256" s="1">
         <f>D240</f>
-        <v>6250</v>
+        <v>6280</v>
       </c>
       <c r="D256" s="1">
         <f>E241</f>
-        <v>61.970940584513983</v>
+        <v>62.258731330262492</v>
       </c>
       <c r="E256" s="1">
         <f>D241</f>
-        <v>6460</v>
+        <v>6490</v>
       </c>
       <c r="F256" s="1">
         <f>E242</f>
-        <v>78.321107954512669</v>
+        <v>78.560256375747812</v>
       </c>
       <c r="G256" s="1">
         <f>D242</f>
-        <v>6550</v>
+        <v>6570</v>
       </c>
       <c r="H256" s="1">
         <f>E243</f>
-        <v>98.115459903837134</v>
+        <v>98.412329676617276</v>
       </c>
       <c r="I256" s="1">
         <f>D243</f>
-        <v>6610</v>
+        <v>6630</v>
       </c>
       <c r="J256" s="1">
         <f>E244</f>
-        <v>121.62419207198188</v>
+        <v>122.17619294371551</v>
       </c>
       <c r="K256" s="1">
         <f>D244</f>
-        <v>6610</v>
+        <v>6640</v>
       </c>
       <c r="L256" s="1"/>
       <c r="M256" s="1"/>
@@ -32015,43 +32144,43 @@
       <c r="A257" s="1"/>
       <c r="B257" s="1">
         <f>E240</f>
-        <v>48.792544792101062</v>
+        <v>49.026749007103156</v>
       </c>
       <c r="C257" s="1">
         <f>F240</f>
-        <v>5086.2523044508816</v>
+        <v>5110.6663155122469</v>
       </c>
       <c r="D257" s="1">
         <f>E241</f>
-        <v>61.970940584513983</v>
+        <v>62.258731330262492</v>
       </c>
       <c r="E257" s="1">
         <f>F241</f>
-        <v>5182.6343042071203</v>
+        <v>5206.7022653721688</v>
       </c>
       <c r="F257" s="1">
         <f>E242</f>
-        <v>78.321107954512669</v>
+        <v>78.560256375747812</v>
       </c>
       <c r="G257" s="1">
         <f>F242</f>
-        <v>5276.462283178701</v>
+        <v>5292.5736183945137</v>
       </c>
       <c r="H257" s="1">
         <f>E243</f>
-        <v>98.115459903837134</v>
+        <v>98.412329676617276</v>
       </c>
       <c r="I257" s="1">
         <f>F243</f>
-        <v>5332.3535302954424</v>
+        <v>5348.4877315973963</v>
       </c>
       <c r="J257" s="1">
         <f>E244</f>
-        <v>121.62419207198188</v>
+        <v>122.17619294371551</v>
       </c>
       <c r="K257" s="1">
         <f>F244</f>
-        <v>5399.6027312228434</v>
+        <v>5424.1092489137181</v>
       </c>
       <c r="L257" s="1"/>
       <c r="M257" s="1"/>
@@ -32388,19 +32517,19 @@
       </c>
       <c r="D278" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!D15,'WRC17'!L15)</f>
-        <v>6970</v>
+        <v>6980</v>
       </c>
       <c r="E278" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!F15,'WRC17'!N15)</f>
-        <v>54.392420396083736</v>
+        <v>54.470458301960477</v>
       </c>
       <c r="F278" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!E15,'WRC17'!M15)</f>
-        <v>5671.1806543385492</v>
+        <v>5679.3172119487908</v>
       </c>
       <c r="G278" s="20">
         <f>E278*'WRC17'!$O$7/D278</f>
-        <v>66.332219995224065</v>
+        <v>66.332219995224079</v>
       </c>
       <c r="H278" s="1"/>
       <c r="I278" s="1"/>
@@ -32420,19 +32549,19 @@
       </c>
       <c r="D279" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!D16,'WRC17'!L16)</f>
-        <v>7180</v>
+        <v>7190</v>
       </c>
       <c r="E279" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!F16,'WRC17'!N16)</f>
-        <v>68.863540459624303</v>
+        <v>68.959450683105686</v>
       </c>
       <c r="F279" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!E16,'WRC17'!M16)</f>
-        <v>5761.5734265734263</v>
+        <v>5769.5979020979021</v>
       </c>
       <c r="G279" s="20">
         <f>E279*'WRC17'!$O$7/D279</f>
-        <v>81.523689959165253</v>
+        <v>81.523689959165267</v>
       </c>
       <c r="H279" s="1"/>
       <c r="I279" s="1"/>
@@ -32484,19 +32613,19 @@
       </c>
       <c r="D281" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!D18,'WRC17'!L18)</f>
-        <v>7290</v>
+        <v>7300</v>
       </c>
       <c r="E281" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!F18,'WRC17'!N18)</f>
-        <v>108.20728427773237</v>
+        <v>108.35571676645353</v>
       </c>
       <c r="F281" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!E18,'WRC17'!M18)</f>
-        <v>5881.704545454546</v>
+        <v>5889.7727272727279</v>
       </c>
       <c r="G281" s="20">
         <f>E281*'WRC17'!$O$7/D281</f>
-        <v>126.16761541299385</v>
+        <v>126.16761541299383</v>
       </c>
       <c r="H281" s="1"/>
       <c r="I281" s="1"/>
@@ -32516,19 +32645,19 @@
       </c>
       <c r="D282" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!D19,'WRC17'!L19)</f>
-        <v>7270</v>
+        <v>7280</v>
       </c>
       <c r="E282" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!F19,'WRC17'!N19)</f>
-        <v>133.74812532993695</v>
+        <v>133.93209799201389</v>
       </c>
       <c r="F282" s="20">
         <f>IF('WRC17'!$D$53=1,'WRC17'!E19,'WRC17'!M19)</f>
-        <v>5938.8732394366198</v>
+        <v>5947.0422535211255</v>
       </c>
       <c r="G282" s="20">
         <f>E282*'WRC17'!$O$7/D282</f>
-        <v>156.37676276540085</v>
+        <v>156.37676276540083</v>
       </c>
       <c r="H282" s="1"/>
       <c r="I282" s="1"/>
@@ -32702,7 +32831,7 @@
       <c r="A289" s="1"/>
       <c r="B289" s="1">
         <f>G278</f>
-        <v>66.332219995224065</v>
+        <v>66.332219995224079</v>
       </c>
       <c r="C289" s="1">
         <f>'WRC17'!$O$7</f>
@@ -32710,7 +32839,7 @@
       </c>
       <c r="D289" s="1">
         <f>G279</f>
-        <v>81.523689959165253</v>
+        <v>81.523689959165267</v>
       </c>
       <c r="E289" s="1">
         <f>'WRC17'!$O$7</f>
@@ -32726,7 +32855,7 @@
       </c>
       <c r="H289" s="1">
         <f>G281</f>
-        <v>126.16761541299385</v>
+        <v>126.16761541299383</v>
       </c>
       <c r="I289" s="1">
         <f>'WRC17'!$O$7</f>
@@ -32734,7 +32863,7 @@
       </c>
       <c r="J289" s="1">
         <f>G282</f>
-        <v>156.37676276540085</v>
+        <v>156.37676276540083</v>
       </c>
       <c r="K289" s="1">
         <f>'WRC17'!$O$7</f>
@@ -32833,19 +32962,19 @@
       <c r="A294" s="1"/>
       <c r="B294" s="1">
         <f>E278</f>
-        <v>54.392420396083736</v>
+        <v>54.470458301960477</v>
       </c>
       <c r="C294" s="1">
         <f>D278</f>
-        <v>6970</v>
+        <v>6980</v>
       </c>
       <c r="D294" s="1">
         <f>E279</f>
-        <v>68.863540459624303</v>
+        <v>68.959450683105686</v>
       </c>
       <c r="E294" s="1">
         <f>D279</f>
-        <v>7180</v>
+        <v>7190</v>
       </c>
       <c r="F294" s="1">
         <f>E280</f>
@@ -32857,19 +32986,19 @@
       </c>
       <c r="H294" s="1">
         <f>E281</f>
-        <v>108.20728427773237</v>
+        <v>108.35571676645353</v>
       </c>
       <c r="I294" s="1">
         <f>D281</f>
-        <v>7290</v>
+        <v>7300</v>
       </c>
       <c r="J294" s="1">
         <f>E282</f>
-        <v>133.74812532993695</v>
+        <v>133.93209799201389</v>
       </c>
       <c r="K294" s="1">
         <f>D282</f>
-        <v>7270</v>
+        <v>7280</v>
       </c>
       <c r="L294" s="1"/>
       <c r="M294" s="1"/>
@@ -32878,19 +33007,19 @@
       <c r="A295" s="1"/>
       <c r="B295" s="1">
         <f>E278</f>
-        <v>54.392420396083736</v>
+        <v>54.470458301960477</v>
       </c>
       <c r="C295" s="1">
         <f>F278</f>
-        <v>5671.1806543385492</v>
+        <v>5679.3172119487908</v>
       </c>
       <c r="D295" s="1">
         <f>E279</f>
-        <v>68.863540459624303</v>
+        <v>68.959450683105686</v>
       </c>
       <c r="E295" s="1">
         <f>F279</f>
-        <v>5761.5734265734263</v>
+        <v>5769.5979020979021</v>
       </c>
       <c r="F295" s="1">
         <f>E280</f>
@@ -32902,19 +33031,19 @@
       </c>
       <c r="H295" s="1">
         <f>E281</f>
-        <v>108.20728427773237</v>
+        <v>108.35571676645353</v>
       </c>
       <c r="I295" s="1">
         <f>F281</f>
-        <v>5881.704545454546</v>
+        <v>5889.7727272727279</v>
       </c>
       <c r="J295" s="1">
         <f>E282</f>
-        <v>133.74812532993695</v>
+        <v>133.93209799201389</v>
       </c>
       <c r="K295" s="1">
         <f>F282</f>
-        <v>5938.8732394366198</v>
+        <v>5947.0422535211255</v>
       </c>
       <c r="L295" s="1"/>
       <c r="M295" s="1"/>
@@ -33251,19 +33380,19 @@
       </c>
       <c r="D316" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!D15,'25R1'!L15)</f>
-        <v>7550</v>
+        <v>7520</v>
       </c>
       <c r="E316" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!F15,'25R1'!N15)</f>
-        <v>52.621790131985449</v>
+        <v>52.412696926163001</v>
       </c>
       <c r="F316" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!E15,'25R1'!M15)</f>
-        <v>5394.885962849753</v>
+        <v>5373.4493298847874</v>
       </c>
       <c r="G316" s="20">
         <f>E316*'25R1'!$O$7/D316</f>
-        <v>59.243074983029977</v>
+        <v>59.243074983029992</v>
       </c>
       <c r="H316" s="1"/>
       <c r="I316" s="1"/>
@@ -33283,15 +33412,15 @@
       </c>
       <c r="D317" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!D16,'25R1'!L16)</f>
-        <v>7770</v>
+        <v>7750</v>
       </c>
       <c r="E317" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!F16,'25R1'!N16)</f>
-        <v>75.788684346823146</v>
+        <v>75.593604078234165</v>
       </c>
       <c r="F317" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!E16,'25R1'!M16)</f>
-        <v>5668.3415597235935</v>
+        <v>5653.7512339585392</v>
       </c>
       <c r="G317" s="20">
         <f>E317*'25R1'!$O$7/D317</f>
@@ -33315,19 +33444,19 @@
       </c>
       <c r="D318" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!D17,'25R1'!L17)</f>
-        <v>7550</v>
+        <v>7520</v>
       </c>
       <c r="E318" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!F17,'25R1'!N17)</f>
-        <v>100.94743952698879</v>
+        <v>100.54632387323919</v>
       </c>
       <c r="F318" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!E17,'25R1'!M17)</f>
-        <v>5986.8741542625166</v>
+        <v>5963.0852503382948</v>
       </c>
       <c r="G318" s="20">
         <f>E318*'25R1'!$O$7/D318</f>
-        <v>113.64943522906022</v>
+        <v>113.64943522906024</v>
       </c>
       <c r="H318" s="1"/>
       <c r="I318" s="1"/>
@@ -33347,15 +33476,15 @@
       </c>
       <c r="D319" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!D18,'25R1'!L18)</f>
-        <v>7780</v>
+        <v>7760</v>
       </c>
       <c r="E319" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!F18,'25R1'!N18)</f>
-        <v>131.18215938459414</v>
+        <v>130.84493018309135</v>
       </c>
       <c r="F319" s="20">
         <f>IF('25R1'!$D$53=1,'25R1'!E18,'25R1'!M18)</f>
-        <v>5947.8498293515368</v>
+        <v>5932.5597269624577</v>
       </c>
       <c r="G319" s="20">
         <f>E319*'25R1'!$O$7/D319</f>
@@ -33539,7 +33668,7 @@
       <c r="A327" s="1"/>
       <c r="B327" s="1">
         <f>G316</f>
-        <v>59.243074983029977</v>
+        <v>59.243074983029992</v>
       </c>
       <c r="C327" s="1">
         <f>'25R1'!$O$7</f>
@@ -33555,7 +33684,7 @@
       </c>
       <c r="F327" s="1">
         <f>G318</f>
-        <v>113.64943522906022</v>
+        <v>113.64943522906024</v>
       </c>
       <c r="G327" s="1">
         <f>'25R1'!$O$7</f>
@@ -33660,35 +33789,35 @@
       <c r="A332" s="1"/>
       <c r="B332" s="1">
         <f>E316</f>
-        <v>52.621790131985449</v>
+        <v>52.412696926163001</v>
       </c>
       <c r="C332" s="1">
         <f>D316</f>
-        <v>7550</v>
+        <v>7520</v>
       </c>
       <c r="D332" s="1">
         <f>E317</f>
-        <v>75.788684346823146</v>
+        <v>75.593604078234165</v>
       </c>
       <c r="E332" s="1">
         <f>D317</f>
-        <v>7770</v>
+        <v>7750</v>
       </c>
       <c r="F332" s="1">
         <f>E318</f>
-        <v>100.94743952698879</v>
+        <v>100.54632387323919</v>
       </c>
       <c r="G332" s="1">
         <f>D318</f>
-        <v>7550</v>
+        <v>7520</v>
       </c>
       <c r="H332" s="1">
         <f>E319</f>
-        <v>131.18215938459414</v>
+        <v>130.84493018309135</v>
       </c>
       <c r="I332" s="1">
         <f>D319</f>
-        <v>7780</v>
+        <v>7760</v>
       </c>
       <c r="J332" s="1"/>
       <c r="K332" s="1"/>
@@ -33699,35 +33828,35 @@
       <c r="A333" s="1"/>
       <c r="B333" s="1">
         <f>E316</f>
-        <v>52.621790131985449</v>
+        <v>52.412696926163001</v>
       </c>
       <c r="C333" s="1">
         <f>F316</f>
-        <v>5394.885962849753</v>
+        <v>5373.4493298847874</v>
       </c>
       <c r="D333" s="1">
         <f>E317</f>
-        <v>75.788684346823146</v>
+        <v>75.593604078234165</v>
       </c>
       <c r="E333" s="1">
         <f>F317</f>
-        <v>5668.3415597235935</v>
+        <v>5653.7512339585392</v>
       </c>
       <c r="F333" s="1">
         <f>E318</f>
-        <v>100.94743952698879</v>
+        <v>100.54632387323919</v>
       </c>
       <c r="G333" s="1">
         <f>F318</f>
-        <v>5986.8741542625166</v>
+        <v>5963.0852503382948</v>
       </c>
       <c r="H333" s="1">
         <f>E319</f>
-        <v>131.18215938459414</v>
+        <v>130.84493018309135</v>
       </c>
       <c r="I333" s="1">
         <f>F319</f>
-        <v>5947.8498293515368</v>
+        <v>5932.5597269624577</v>
       </c>
       <c r="J333" s="1"/>
       <c r="K333" s="1"/>
@@ -34066,19 +34195,19 @@
       </c>
       <c r="D354" s="20">
         <f>'RX1'!D15</f>
-        <v>6000</v>
+        <v>6180</v>
       </c>
       <c r="E354" s="20">
         <f>'RX1'!F15</f>
-        <v>55.850536063818538</v>
+        <v>57.526052145733104</v>
       </c>
       <c r="F354" s="20">
         <f>'RX1'!E15</f>
-        <v>4812.9629629629635</v>
+        <v>4957.3518518518522</v>
       </c>
       <c r="G354" s="20">
         <f>E354*'RX1'!$O$7/D354</f>
-        <v>79.121592757076257</v>
+        <v>79.121592757076272</v>
       </c>
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
@@ -34098,15 +34227,15 @@
       </c>
       <c r="D355" s="20">
         <f>'RX1'!D16</f>
-        <v>6170</v>
+        <v>6400</v>
       </c>
       <c r="E355" s="20">
         <f>'RX1'!F16</f>
-        <v>71.597851503436175</v>
+        <v>74.266815173742557</v>
       </c>
       <c r="F355" s="20">
         <f>'RX1'!E16</f>
-        <v>4952.1431319738349</v>
+        <v>5136.7449018853404</v>
       </c>
       <c r="G355" s="20">
         <f>E355*'RX1'!$O$7/D355</f>
@@ -34130,19 +34259,19 @@
       </c>
       <c r="D356" s="20">
         <f>'RX1'!D17</f>
-        <v>6220</v>
+        <v>6470</v>
       </c>
       <c r="E356" s="20">
         <f>'RX1'!F17</f>
-        <v>89.928466218194515</v>
+        <v>93.542954410244121</v>
       </c>
       <c r="F356" s="20">
         <f>'RX1'!E17</f>
-        <v>5039.2138063278999</v>
+        <v>5241.7545541706613</v>
       </c>
       <c r="G356" s="20">
         <f>E356*'RX1'!$O$7/D356</f>
-        <v>122.89259852968704</v>
+        <v>122.89259852968702</v>
       </c>
       <c r="H356" s="1"/>
       <c r="I356" s="1"/>
@@ -34162,15 +34291,15 @@
       </c>
       <c r="D357" s="20">
         <f>'RX1'!D18</f>
-        <v>6250</v>
+        <v>6500</v>
       </c>
       <c r="E357" s="20">
         <f>'RX1'!F18</f>
-        <v>111.53583385525893</v>
+        <v>115.9972672094693</v>
       </c>
       <c r="F357" s="20">
         <f>'RX1'!E18</f>
-        <v>5110.9467455621307</v>
+        <v>5315.3846153846152</v>
       </c>
       <c r="G357" s="20">
         <f>E357*'RX1'!$O$7/D357</f>
@@ -34194,15 +34323,15 @@
       </c>
       <c r="D358" s="20">
         <f>'RX1'!D19</f>
-        <v>6260</v>
+        <v>6520</v>
       </c>
       <c r="E358" s="20">
         <f>'RX1'!F19</f>
-        <v>136.61154277144155</v>
+        <v>142.28550461178898</v>
       </c>
       <c r="F358" s="20">
         <f>'RX1'!E19</f>
-        <v>5163.820549927641</v>
+        <v>5378.2923299565846</v>
       </c>
       <c r="G358" s="20">
         <f>E358*'RX1'!$O$7/D358</f>
@@ -34380,7 +34509,7 @@
       <c r="A365" s="1"/>
       <c r="B365" s="1">
         <f>G354</f>
-        <v>79.121592757076257</v>
+        <v>79.121592757076272</v>
       </c>
       <c r="C365" s="1">
         <f>'RX1'!$O$7</f>
@@ -34396,7 +34525,7 @@
       </c>
       <c r="F365" s="1">
         <f>G356</f>
-        <v>122.89259852968704</v>
+        <v>122.89259852968702</v>
       </c>
       <c r="G365" s="1">
         <f>'RX1'!$O$7</f>
@@ -34511,43 +34640,43 @@
       <c r="A370" s="1"/>
       <c r="B370" s="1">
         <f>E354</f>
-        <v>55.850536063818538</v>
+        <v>57.526052145733104</v>
       </c>
       <c r="C370" s="1">
         <f>D354</f>
-        <v>6000</v>
+        <v>6180</v>
       </c>
       <c r="D370" s="1">
         <f>E355</f>
-        <v>71.597851503436175</v>
+        <v>74.266815173742557</v>
       </c>
       <c r="E370" s="1">
         <f>D355</f>
-        <v>6170</v>
+        <v>6400</v>
       </c>
       <c r="F370" s="1">
         <f>E356</f>
-        <v>89.928466218194515</v>
+        <v>93.542954410244121</v>
       </c>
       <c r="G370" s="1">
         <f>D356</f>
-        <v>6220</v>
+        <v>6470</v>
       </c>
       <c r="H370" s="1">
         <f>E357</f>
-        <v>111.53583385525893</v>
+        <v>115.9972672094693</v>
       </c>
       <c r="I370" s="1">
         <f>D357</f>
-        <v>6250</v>
+        <v>6500</v>
       </c>
       <c r="J370" s="1">
         <f>E358</f>
-        <v>136.61154277144155</v>
+        <v>142.28550461178898</v>
       </c>
       <c r="K370" s="1">
         <f>D358</f>
-        <v>6260</v>
+        <v>6520</v>
       </c>
       <c r="L370" s="1"/>
       <c r="M370" s="1"/>
@@ -34556,43 +34685,43 @@
       <c r="A371" s="1"/>
       <c r="B371" s="1">
         <f>E354</f>
-        <v>55.850536063818538</v>
+        <v>57.526052145733104</v>
       </c>
       <c r="C371" s="1">
         <f>F354</f>
-        <v>4812.9629629629635</v>
+        <v>4957.3518518518522</v>
       </c>
       <c r="D371" s="1">
         <f>E355</f>
-        <v>71.597851503436175</v>
+        <v>74.266815173742557</v>
       </c>
       <c r="E371" s="1">
         <f>F355</f>
-        <v>4952.1431319738349</v>
+        <v>5136.7449018853404</v>
       </c>
       <c r="F371" s="1">
         <f>E356</f>
-        <v>89.928466218194515</v>
+        <v>93.542954410244121</v>
       </c>
       <c r="G371" s="1">
         <f>F356</f>
-        <v>5039.2138063278999</v>
+        <v>5241.7545541706613</v>
       </c>
       <c r="H371" s="1">
         <f>E357</f>
-        <v>111.53583385525893</v>
+        <v>115.9972672094693</v>
       </c>
       <c r="I371" s="1">
         <f>F357</f>
-        <v>5110.9467455621307</v>
+        <v>5315.3846153846152</v>
       </c>
       <c r="J371" s="1">
         <f>E358</f>
-        <v>136.61154277144155</v>
+        <v>142.28550461178898</v>
       </c>
       <c r="K371" s="1">
         <f>F358</f>
-        <v>5163.820549927641</v>
+        <v>5378.2923299565846</v>
       </c>
       <c r="L371" s="1"/>
       <c r="M371" s="1"/>
@@ -35769,15 +35898,15 @@
     </row>
     <row r="437" spans="1:13" ht="22.5" customHeight="1">
       <c r="A437" s="1"/>
-      <c r="B437" s="1">
+      <c r="B437" s="1" t="n">
         <v>2500</v>
       </c>
-      <c r="C437" s="3">
-        <v>392.12322294939003</v>
+      <c r="C437" s="3" t="n">
+        <v>393.20032070475</v>
       </c>
       <c r="D437" s="4">
-        <f>137.669100866325*735.49875/745.69987158227</f>
-        <v>135.78579728860106</v>
+        <f>138.04725515775*735.49875/745.6998715822702</f>
+        <v>136.15877845602444</v>
       </c>
       <c r="E437" s="1"/>
       <c r="F437" s="1"/>
@@ -35791,15 +35920,15 @@
     </row>
     <row r="438" spans="1:13" ht="22.5" customHeight="1">
       <c r="A438" s="1"/>
-      <c r="B438" s="1">
+      <c r="B438" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="C438" s="3">
-        <v>413.34311991096001</v>
+      <c r="C438" s="3" t="n">
+        <v>414.5013732911</v>
       </c>
       <c r="D438" s="4">
-        <f>174.142939781257*735.49875/745.69987158227</f>
-        <v>171.76067666294219</v>
+        <f>174.63091608693*735.49875/745.6998715822702</f>
+        <v>172.24197748721423</v>
       </c>
       <c r="E438" s="1"/>
       <c r="F438" s="1"/>
@@ -35813,15 +35942,15 @@
     </row>
     <row r="439" spans="1:13" ht="22.5" customHeight="1">
       <c r="A439" s="1"/>
-      <c r="B439" s="1">
+      <c r="B439" s="1" t="n">
         <v>3500</v>
       </c>
-      <c r="C439" s="3">
-        <v>427.69062033038</v>
+      <c r="C439" s="3" t="n">
+        <v>428.95781702559</v>
       </c>
       <c r="D439" s="4">
-        <f>210.218858729571*735.49875/745.69987158227</f>
-        <v>207.34307958770773</v>
+        <f>210.84171233073*735.49875/745.6998715822702</f>
+        <v>207.95741259558852</v>
       </c>
       <c r="E439" s="1"/>
       <c r="F439" s="1"/>
@@ -35835,15 +35964,15 @@
     </row>
     <row r="440" spans="1:13" ht="22.5" customHeight="1">
       <c r="A440" s="1"/>
-      <c r="B440" s="1">
+      <c r="B440" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="C440" s="3">
-        <v>435.71238814309982</v>
+      <c r="C440" s="3" t="n">
+        <v>436.57054083363</v>
       </c>
       <c r="D440" s="4">
-        <f>244.756257018613*735.49875/745.69987158227</f>
-        <v>241.40800870717055</v>
+        <f>245.23831409617*735.49875/745.6998715822702</f>
+        <v>241.88347127794921</v>
       </c>
       <c r="E440" s="1"/>
       <c r="F440" s="1"/>
@@ -35857,15 +35986,15 @@
     </row>
     <row r="441" spans="1:13" ht="22.5" customHeight="1">
       <c r="A441" s="1"/>
-      <c r="B441" s="1">
+      <c r="B441" s="1" t="n">
         <v>4500</v>
       </c>
-      <c r="C441" s="3">
-        <v>439.98714840701604</v>
+      <c r="C441" s="3" t="n">
+        <v>442.09140264402</v>
       </c>
       <c r="D441" s="4">
-        <f>278.052246905943*735.49875/745.69987158227</f>
-        <v>274.24851180418904</v>
+        <f>279.38204169831*735.49875/745.6998715822702</f>
+        <v>275.56011509770593</v>
       </c>
       <c r="E441" s="1"/>
       <c r="F441" s="1"/>
@@ -35879,15 +36008,15 @@
     </row>
     <row r="442" spans="1:13" ht="22.5" customHeight="1">
       <c r="A442" s="1"/>
-      <c r="B442" s="1">
+      <c r="B442" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="C442" s="3">
-        <v>443.19385328835278</v>
+      <c r="C442" s="3" t="n">
+        <v>444.45705821158</v>
       </c>
       <c r="D442" s="4">
-        <f>311.19860146393*735.49875/745.69987158227</f>
-        <v>306.94142657260284</v>
+        <f>312.08558940962*735.49875/745.6998715822702</f>
+        <v>307.81628058583448</v>
       </c>
       <c r="E442" s="1"/>
       <c r="F442" s="1"/>
@@ -35901,15 +36030,15 @@
     </row>
     <row r="443" spans="1:13" ht="22.5" customHeight="1">
       <c r="A443" s="1"/>
-      <c r="B443" s="1">
-        <v>5189</v>
-      </c>
-      <c r="C443" s="3">
-        <v>443.46248568368935</v>
+      <c r="B443" s="1" t="n">
+        <v>5083</v>
+      </c>
+      <c r="C443" s="3" t="n">
+        <v>444.51603790308</v>
       </c>
       <c r="D443" s="4">
-        <f>323.157664994501*735.49875/745.69987158227</f>
-        <v>318.73689095861903</v>
+        <f>317.30831159114*735.49875/745.6998715822702</f>
+        <v>312.96755629673748</v>
       </c>
       <c r="E443" s="1"/>
       <c r="F443" s="1"/>
@@ -35923,15 +36052,15 @@
     </row>
     <row r="444" spans="1:13" ht="22.5" customHeight="1">
       <c r="A444" s="1"/>
-      <c r="B444" s="1">
+      <c r="B444" s="1" t="n">
         <v>5500</v>
       </c>
-      <c r="C444" s="3">
-        <v>442.88615147652462</v>
+      <c r="C444" s="3" t="n">
+        <v>443.41134004895</v>
       </c>
       <c r="D444" s="4">
-        <f>342.080795834776*735.49875/745.69987158227</f>
-        <v>337.4011547053417</v>
+        <f>342.48644619034*735.49875/745.6998715822702</f>
+        <v>337.80125579268849</v>
       </c>
       <c r="E444" s="1"/>
       <c r="F444" s="1"/>
@@ -35945,15 +36074,15 @@
     </row>
     <row r="445" spans="1:13" ht="22.5" customHeight="1">
       <c r="A445" s="1"/>
-      <c r="B445" s="1">
+      <c r="B445" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="C445" s="3">
-        <v>439.70678468527797</v>
+      <c r="C445" s="3" t="n">
+        <v>439.80647992659</v>
       </c>
       <c r="D445" s="4">
-        <f>370.500092723708*735.49875/745.69987158227</f>
-        <v>365.43167761979055</v>
+        <f>370.58409664959*735.49875/745.6998715822702</f>
+        <v>365.51453237789877</v>
       </c>
       <c r="E445" s="1"/>
       <c r="F445" s="1"/>
@@ -35967,15 +36096,15 @@
     </row>
     <row r="446" spans="1:13" ht="22.5" customHeight="1">
       <c r="A446" s="1"/>
-      <c r="B446" s="1">
+      <c r="B446" s="1" t="n">
         <v>6500</v>
       </c>
-      <c r="C446" s="3">
-        <v>418.98807357322522</v>
+      <c r="C446" s="3" t="n">
+        <v>418.75913649655</v>
       </c>
       <c r="D446" s="4">
-        <f>382.462554537249*735.49875/745.69987158227</f>
-        <v>377.23049380050577</v>
+        <f>382.25357517794*735.49875/745.6998715822702</f>
+        <v>377.02437326407409</v>
       </c>
       <c r="E446" s="1"/>
       <c r="F446" s="1"/>
@@ -35989,15 +36118,15 @@
     </row>
     <row r="447" spans="1:13" ht="22.5" customHeight="1">
       <c r="A447" s="1"/>
-      <c r="B447" s="1">
-        <v>6843</v>
-      </c>
-      <c r="C447" s="3">
-        <v>399.94118639818879</v>
+      <c r="B447" s="1" t="n">
+        <v>6951</v>
+      </c>
+      <c r="C447" s="3" t="n">
+        <v>393.93320137099</v>
       </c>
       <c r="D447" s="4">
-        <f>384.340874837944*735.49875/745.69987158227</f>
-        <v>379.08311881213342</v>
+        <f>384.54199733592*735.49875/745.6998715822702</f>
+        <v>379.28148996854014</v>
       </c>
       <c r="E447" s="1"/>
       <c r="F447" s="1"/>
@@ -36011,15 +36140,15 @@
     </row>
     <row r="448" spans="1:13" ht="22.5" customHeight="1">
       <c r="A448" s="1"/>
-      <c r="B448" s="1">
+      <c r="B448" s="1" t="n">
         <v>7000</v>
       </c>
-      <c r="C448" s="3">
-        <v>390.92736187569773</v>
+      <c r="C448" s="3" t="n">
+        <v>391.17393740356</v>
       </c>
       <c r="D448" s="4">
-        <f>384.297901114545*735.49875/745.69987158227</f>
-        <v>379.04073296623568</v>
+        <f>384.54029514235*735.49875/745.6998715822702</f>
+        <v>379.27981106085798</v>
       </c>
       <c r="E448" s="1"/>
       <c r="F448" s="1"/>
@@ -36033,15 +36162,15 @@
     </row>
     <row r="449" spans="1:13" ht="22.5" customHeight="1">
       <c r="A449" s="1"/>
-      <c r="B449" s="1">
+      <c r="B449" s="1" t="n">
         <v>7500</v>
       </c>
-      <c r="C449" s="3">
-        <v>363.26933766308696</v>
+      <c r="C449" s="3" t="n">
+        <v>362.86336707814</v>
       </c>
       <c r="D449" s="4">
-        <f>382.616689051626*735.49875/745.69987158227</f>
-        <v>377.38251976561105</v>
+        <f>382.18909689077*735.49875/745.6998715822702</f>
+        <v>376.96077703531915</v>
       </c>
       <c r="E449" s="1"/>
       <c r="F449" s="1"/>
@@ -36055,15 +36184,15 @@
     </row>
     <row r="450" spans="1:13" ht="22.5" customHeight="1">
       <c r="A450" s="1"/>
-      <c r="B450" s="1">
+      <c r="B450" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="C450" s="3">
-        <v>332.97769982606115</v>
+      <c r="C450" s="3" t="n">
+        <v>333.47219443757</v>
       </c>
       <c r="D450" s="4">
-        <f>374.092533046491*735.49875/745.69987158227</f>
-        <v>368.97497361265437</v>
+        <f>374.6480859916*735.49875/745.6998715822702</f>
+        <v>369.5229266327072</v>
       </c>
       <c r="E450" s="1"/>
       <c r="F450" s="1"/>
@@ -36077,15 +36206,15 @@
     </row>
     <row r="451" spans="1:13" ht="22.5" customHeight="1">
       <c r="A451" s="1"/>
-      <c r="B451" s="1">
+      <c r="B451" s="1" t="n">
         <v>8499</v>
       </c>
-      <c r="C451" s="3">
-        <v>288.35790965028451</v>
+      <c r="C451" s="3" t="n">
+        <v>289.71271466748</v>
       </c>
       <c r="D451" s="4">
-        <f>344.170467392086*735.49875/745.69987158227</f>
-        <v>339.46223970331931</v>
+        <f>345.78749907524*735.49875/745.6998715822702</f>
+        <v>341.05715050724183</v>
       </c>
       <c r="E451" s="1"/>
       <c r="F451" s="1"/>
@@ -36159,19 +36288,19 @@
       </c>
       <c r="D476" s="20">
         <f>IF(Rally1!$D$53=1,Rally1!D15,Rally1!L15)</f>
-        <v>7710</v>
+        <v>7700</v>
       </c>
       <c r="E476" s="20">
         <f>IF(Rally1!$D$53=1,Rally1!F15,Rally1!N15)</f>
-        <v>53.736953896371908</v>
+        <v>53.667256161097754</v>
       </c>
       <c r="F476" s="20">
         <f>IF(Rally1!$D$53=1,Rally1!E15,Rally1!M15)</f>
-        <v>5509.2146719962384</v>
+        <v>5502.0691276745829</v>
       </c>
       <c r="G476" s="20">
         <f>E476*Rally1!$O$7/D476</f>
-        <v>59.243074983029992</v>
+        <v>59.243074983029985</v>
       </c>
       <c r="H476" s="1"/>
       <c r="I476" s="1"/>
@@ -36223,19 +36352,19 @@
       </c>
       <c r="D478" s="20">
         <f>IF(Rally1!$D$53=1,Rally1!D17,Rally1!L17)</f>
-        <v>7630</v>
+        <v>7620</v>
       </c>
       <c r="E478" s="20">
         <f>IF(Rally1!$D$53=1,Rally1!F17,Rally1!N17)</f>
-        <v>102.01708127032111</v>
+        <v>101.88337605240459</v>
       </c>
       <c r="F478" s="20">
         <f>IF(Rally1!$D$53=1,Rally1!E17,Rally1!M17)</f>
-        <v>6050.3112313937754</v>
+        <v>6042.3815967523678</v>
       </c>
       <c r="G478" s="20">
         <f>E478*Rally1!$O$7/D478</f>
-        <v>113.64943522906022</v>
+        <v>113.64943522906023</v>
       </c>
       <c r="H478" s="1"/>
       <c r="I478" s="1"/>
@@ -36447,7 +36576,7 @@
       <c r="A487" s="1"/>
       <c r="B487" s="1">
         <f>G476</f>
-        <v>59.243074983029992</v>
+        <v>59.243074983029985</v>
       </c>
       <c r="C487" s="1">
         <f>Rally1!$O$7</f>
@@ -36463,7 +36592,7 @@
       </c>
       <c r="F487" s="1">
         <f>G478</f>
-        <v>113.64943522906022</v>
+        <v>113.64943522906023</v>
       </c>
       <c r="G487" s="1">
         <f>Rally1!$O$7</f>
@@ -36568,11 +36697,11 @@
       <c r="A492" s="1"/>
       <c r="B492" s="1">
         <f>E476</f>
-        <v>53.736953896371908</v>
+        <v>53.667256161097754</v>
       </c>
       <c r="C492" s="1">
         <f>D476</f>
-        <v>7710</v>
+        <v>7700</v>
       </c>
       <c r="D492" s="1">
         <f>E477</f>
@@ -36584,11 +36713,11 @@
       </c>
       <c r="F492" s="1">
         <f>E478</f>
-        <v>102.01708127032111</v>
+        <v>101.88337605240459</v>
       </c>
       <c r="G492" s="1">
         <f>D478</f>
-        <v>7630</v>
+        <v>7620</v>
       </c>
       <c r="H492" s="1">
         <f>E479</f>
@@ -36607,11 +36736,11 @@
       <c r="A493" s="1"/>
       <c r="B493" s="1">
         <f>E476</f>
-        <v>53.736953896371908</v>
+        <v>53.667256161097754</v>
       </c>
       <c r="C493" s="1">
         <f>F476</f>
-        <v>5509.2146719962384</v>
+        <v>5502.0691276745829</v>
       </c>
       <c r="D493" s="1">
         <f>E477</f>
@@ -36623,11 +36752,11 @@
       </c>
       <c r="F493" s="1">
         <f>E478</f>
-        <v>102.01708127032111</v>
+        <v>101.88337605240459</v>
       </c>
       <c r="G493" s="1">
         <f>F478</f>
-        <v>6050.3112313937754</v>
+        <v>6042.3815967523678</v>
       </c>
       <c r="H493" s="1">
         <f>E479</f>

--- a/docs/gearing_shiftlights.xlsx
+++ b/docs/gearing_shiftlights.xlsx
@@ -51,7 +51,7 @@
         <t>[线程批注]
 你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
 注释:
-    Source: docs/astral_engine_curve_rally2.json, astral_engine_curve_wrc.json, astral_engine_curve_wrc17.json, astral_engine_curve_25r1.json, astral_engine_curve_rally1.json and astral_engine_curve_rx1.json, current configured driveline. Game-exported torque is Nm and power is PS; displayed power is hp = PS * 735.49875 / 745.6998715822702. Samples retain 500 rpm spacing, peak points and the final point. Shift thresholds are recorded calibration inputs calculated from the full-resolution curves and configured rotational inertia; this workbook does not rerun that solver. 25R1 uses the 2025 game export. Rally1 uses the 2022 measured game export, at measured running mass 1460 kg. RX3 remains an RX1 five-speed placeholder.</t>
+    Source: docs/astral_engine_curve_rally2.json, astral_engine_curve_wrc.json, astral_engine_curve_wrc17.json, astral_engine_curve_25r1.json, astral_engine_curve_rally1.json astral_engine_curve_rx1.json and astral_engine_curve_rx3.json, current configured driveline. Game-exported torque is Nm and power is PS; displayed power is hp = PS * 735.49875 / 745.6998715822702. Samples retain 500 rpm spacing, peak points and the final point. Shift thresholds are recorded calibration inputs calculated from the full-resolution curves and configured rotational inertia; this workbook does not rerun that solver. 25R1 uses the 2025 game export. Rally1 uses the 2022 measured game export, at measured running mass 1460 kg. RX3 uses its measured NA curve and five-speed driveline, at measured running mass 1009 kg.</t>
       </text>
     </comment>
   </commentList>
@@ -4108,34 +4108,34 @@
                   <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4141</c:v>
+                  <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5000</c:v>
+                  <c:v>5500</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5500</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5690</c:v>
+                  <c:v>6292</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6000</c:v>
+                  <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6500</c:v>
+                  <c:v>7000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7000</c:v>
+                  <c:v>7500</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7500</c:v>
+                  <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8000</c:v>
+                  <c:v>8355</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>8499</c:v>
@@ -4150,49 +4150,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>781.33066149713</c:v>
+                  <c:v>151.83930704375001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>815.57037906490996</c:v>
+                  <c:v>159.23716845249999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>839.31014412132004</c:v>
+                  <c:v>165.63502986124999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>849.15980634939001</c:v>
+                  <c:v>172.03289126999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>849.65874099113</c:v>
+                  <c:v>181.43075267875</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>846.29453700936006</c:v>
+                  <c:v>191.8286140875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>830.31349066587995</c:v>
+                  <c:v>200.22647549625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>778.94554556110995</c:v>
+                  <c:v>203.62433690500001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>754.97659059928003</c:v>
+                  <c:v>204.07922467170999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>713.52169310327997</c:v>
+                  <c:v>204.02219831375001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>650.00523948523005</c:v>
+                  <c:v>203.42005972250001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>590.16354933322998</c:v>
+                  <c:v>201.81792113124999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>529.20441413318997</c:v>
+                  <c:v>199.21578253999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>466.5003138289</c:v>
+                  <c:v>193.99604814021001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>397.788442868</c:v>
+                  <c:v>189.65178627393001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4262,34 +4262,34 @@
                   <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4141</c:v>
+                  <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4500</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5000</c:v>
+                  <c:v>5500</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5500</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5690</c:v>
+                  <c:v>6292</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6000</c:v>
+                  <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6500</c:v>
+                  <c:v>7000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7000</c:v>
+                  <c:v>7500</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7500</c:v>
+                  <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8000</c:v>
+                  <c:v>8355</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>8499</c:v>
@@ -4304,49 +4304,49 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>270.56190658493745</c:v>
+                  <c:v>52.579444827590663</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>338.90226648653652</c:v>
+                  <c:v>66.169442494129825</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>406.89494166808578</c:v>
+                  <c:v>80.299346178095874</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>470.48003110172607</c:v>
+                  <c:v>95.315439367283247</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>487.35063311023652</c:v>
+                  <c:v>113.08765289578997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>527.5040831604706</c:v>
+                  <c:v>132.85416309046971</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>575.04770302318877</c:v>
+                  <c:v>152.537269024539</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>593.4191567035989</c:v>
+                  <c:v>169.22818940051559</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>595.02816984475828</c:v>
+                  <c:v>177.86040792876196</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>592.99387321365498</c:v>
+                  <c:v>183.68874789156061</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>585.22381167748551</c:v>
+                  <c:v>197.23482175127756</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>572.21889825237974</c:v>
+                  <c:v>209.65864088701659</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>549.764250848752</c:v>
+                  <c:v>220.75243520607853</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>516.93233833745376</c:v>
+                  <c:v>224.50763333936891</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>468.28663693613572</c:v>
+                  <c:v>223.26288954709636</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4373,7 +4373,7 @@
         <c:axId val="48672768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="900"/>
+          <c:max val="250"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -4505,7 +4505,7 @@
         <c:axId val="1509330127"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="900"/>
+          <c:max val="250"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -4711,7 +4711,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79.121592757076257</c:v>
+                  <c:v>55.267551244682615</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4773,7 +4773,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>98.635613902626829</c:v>
+                  <c:v>75.79980443374329</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4835,7 +4835,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>122.89259852968704</c:v>
+                  <c:v>101.97002577194077</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4897,7 +4897,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>151.68873404315215</c:v>
+                  <c:v>134.13548022231774</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4959,7 +4959,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>185.49490631905005</c:v>
+                  <c:v>168.1002465673491</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5018,10 +5018,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>55.850536063818538</c:v>
+                  <c:v>55.267551244682615</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55.850536063818538</c:v>
+                  <c:v>55.267551244682615</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5033,10 +5033,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6000</c:v>
+                  <c:v>8500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4812.9629629629635</c:v>
+                  <c:v>6197.564612326044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5080,10 +5080,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>71.597851503436175</c:v>
+                  <c:v>75.79980443374329</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71.597851503436175</c:v>
+                  <c:v>75.79980443374329</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5095,10 +5095,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6170</c:v>
+                  <c:v>8500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4952.1431319738349</c:v>
+                  <c:v>6318.5071574642125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5142,10 +5142,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>89.928466218194515</c:v>
+                  <c:v>101.97002577194077</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>89.928466218194515</c:v>
+                  <c:v>101.97002577194077</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5157,10 +5157,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6220</c:v>
+                  <c:v>8500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5039.2138063278999</c:v>
+                  <c:v>6461.7148097203117</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5204,10 +5204,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>111.53583385525893</c:v>
+                  <c:v>134.13548022231774</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>111.53583385525893</c:v>
+                  <c:v>134.13548022231774</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5219,10 +5219,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6250</c:v>
+                  <c:v>8500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5110.9467455621307</c:v>
+                  <c:v>6782.5693606755131</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12298,7 +12298,7 @@
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="B2" dT="2026-10-27T03:19:09.83" personId="{4B51B63F-135D-471B-AFAA-1BEB5D1B10EA}" id="{61577C78-3AE9-40FE-BEAD-1A1561E5C31C}">
-    <text>Source: docs/astral_engine_curve_rally2.json, astral_engine_curve_wrc.json, astral_engine_curve_wrc17.json, astral_engine_curve_25r1.json, astral_engine_curve_rally1.json and astral_engine_curve_rx1.json, current configured driveline. Game-exported torque is Nm and power is PS; displayed power is hp = PS * 735.49875 / 745.6998715822702. Samples retain 500 rpm spacing, peak points and the final point. Shift thresholds are recorded calibration inputs calculated from the full-resolution curves and configured rotational inertia; this workbook does not rerun that solver. 25R1 uses the 2025 game export. Rally1 uses the 2022 measured game export, at measured running mass 1460 kg. RX3 remains an RX1 five-speed placeholder.</text>
+    <text>Source: docs/astral_engine_curve_rally2.json, astral_engine_curve_wrc.json, astral_engine_curve_wrc17.json, astral_engine_curve_25r1.json, astral_engine_curve_rally1.json astral_engine_curve_rx1.json and astral_engine_curve_rx3.json, current configured driveline. Game-exported torque is Nm and power is PS; displayed power is hp = PS * 735.49875 / 745.6998715822702. Samples retain 500 rpm spacing, peak points and the final point. Shift thresholds are recorded calibration inputs calculated from the full-resolution curves and configured rotational inertia; this workbook does not rerun that solver. 25R1 uses the 2025 game export. Rally1 uses the 2022 measured game export, at measured running mass 1460 kg. RX3 uses its measured NA curve and five-speed driveline, at measured running mass 1009 kg.</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -24159,8 +24159,8 @@
     <row r="3" spans="1:17" ht="22.5" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="35" t="str">
-        <f>VLOOKUP("note.rx1FiveSpeedPlaceholder",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>RX1 占位 · 五挡</v>
+        <f>""</f>
+        <v/>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -24234,7 +24234,7 @@
       <c r="C6" s="30"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$157:$D$171)</f>
-        <v>595.02816984475828</v>
+        <v>224.50763333936891</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="30" t="str">
@@ -24243,8 +24243,8 @@
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
-      <c r="I6" s="7">
-        <v>1306</v>
+      <c r="I6" s="7" t="n">
+        <v>1009</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="30" t="str">
@@ -24254,7 +24254,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="O6" s="31" t="n">
         <v>3000</v>
       </c>
       <c r="P6" s="31"/>
@@ -24269,7 +24269,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$157:$B$171,MATCH(D6,Samples!$D$157:$D$171,0))</f>
-        <v>5690</v>
+        <v>8355</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="32" t="str">
@@ -24278,8 +24278,8 @@
       </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="8">
-        <v>0.128</v>
+      <c r="I7" s="8" t="n">
+        <v>0.121716</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="32" t="str">
@@ -24289,7 +24289,7 @@
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="O7" s="32" t="n">
         <v>8500</v>
       </c>
       <c r="P7" s="32"/>
@@ -24304,7 +24304,7 @@
       <c r="C8" s="30"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$157:$C$171)</f>
-        <v>849.65874099113</v>
+        <v>204.07922467170999</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="30" t="str">
@@ -24313,8 +24313,8 @@
       </c>
       <c r="G8" s="30"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="9">
-        <v>4</v>
+      <c r="I8" s="9" t="n">
+        <v>4.466666666666667</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="30" t="str">
@@ -24324,8 +24324,8 @@
       <c r="L8" s="30"/>
       <c r="M8" s="30"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="31">
-        <v>800</v>
+      <c r="O8" s="31" t="n">
+        <v>500</v>
       </c>
       <c r="P8" s="31"/>
       <c r="Q8" s="1"/>
@@ -24339,7 +24339,7 @@
       <c r="C9" s="32"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$157:$B$171,MATCH(D8,Samples!$C$157:$C$171,0))</f>
-        <v>4141</v>
+        <v>6292</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="32" t="str">
@@ -24348,8 +24348,8 @@
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="10">
-        <v>1.2E-2</v>
+      <c r="I9" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="32" t="str">
@@ -24428,8 +24428,8 @@
     <row r="13" spans="1:17" ht="32" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="29" t="str">
-        <f>VLOOKUP("label.groupOneRx1",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>第 1 组 · RX1</v>
+        <f>SUBSTITUTE(VLOOKUP("label.groupOneRx1",Locale!$A$2:$D$73,4,FALSE),"RX1","RX3")</f>
+        <v>第 1 组 · RX3</v>
       </c>
       <c r="C13" s="29"/>
       <c r="D13" s="29"/>
@@ -24496,23 +24496,23 @@
       <c r="B15" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="12">
-        <v>3.24</v>
-      </c>
-      <c r="D15" s="22">
-        <v>6000</v>
+      <c r="C15" s="12" t="n">
+        <v>4.024</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>8500</v>
       </c>
       <c r="E15" s="13">
         <f>D15*C16/C15</f>
-        <v>4812.9629629629635</v>
+        <v>6197.564612326044</v>
       </c>
       <c r="F15" s="14">
         <f>D15*2*PI()/60*$D$22/(C15*$I$8)*3.6</f>
-        <v>55.850536063818538</v>
+        <v>55.267551244682615</v>
       </c>
       <c r="G15" s="13">
         <f>MAX(0,D15-$O$8)</f>
-        <v>5200</v>
+        <v>8000</v>
       </c>
       <c r="H15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -24533,23 +24533,23 @@
       <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C16" s="12">
-        <v>2.5990000000000002</v>
-      </c>
-      <c r="D16" s="22">
-        <v>6170</v>
+      <c r="C16" s="12" t="n">
+        <v>2.934</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>8500</v>
       </c>
       <c r="E16" s="16">
         <f>D16*C17/C16</f>
-        <v>4952.1431319738349</v>
+        <v>6318.5071574642125</v>
       </c>
       <c r="F16" s="17">
         <f>D16*2*PI()/60*$D$22/(C16*$I$8)*3.6</f>
-        <v>71.597851503436175</v>
+        <v>75.79980443374329</v>
       </c>
       <c r="G16" s="16">
         <f>MAX(0,D16-$O$8)</f>
-        <v>5370</v>
+        <v>8000</v>
       </c>
       <c r="H16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -24570,23 +24570,23 @@
       <c r="B17" s="11">
         <v>3</v>
       </c>
-      <c r="C17" s="12">
-        <v>2.0859999999999999</v>
-      </c>
-      <c r="D17" s="22">
-        <v>6220</v>
+      <c r="C17" s="12" t="n">
+        <v>2.181</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>8500</v>
       </c>
       <c r="E17" s="13">
         <f>D17*C18/C17</f>
-        <v>5039.2138063278999</v>
+        <v>6461.7148097203117</v>
       </c>
       <c r="F17" s="14">
         <f>D17*2*PI()/60*$D$22/(C17*$I$8)*3.6</f>
-        <v>89.928466218194515</v>
+        <v>101.97002577194077</v>
       </c>
       <c r="G17" s="13">
         <f>MAX(0,D17-$O$8)</f>
-        <v>5420</v>
+        <v>8000</v>
       </c>
       <c r="H17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -24607,23 +24607,23 @@
       <c r="B18" s="15">
         <v>4</v>
       </c>
-      <c r="C18" s="12">
-        <v>1.69</v>
-      </c>
-      <c r="D18" s="22">
-        <v>6250</v>
+      <c r="C18" s="12" t="n">
+        <v>1.658</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>8500</v>
       </c>
       <c r="E18" s="16">
         <f>D18*C19/C18</f>
-        <v>5110.9467455621307</v>
+        <v>6782.5693606755131</v>
       </c>
       <c r="F18" s="17">
         <f>D18*2*PI()/60*$D$22/(C18*$I$8)*3.6</f>
-        <v>111.53583385525893</v>
+        <v>134.13548022231774</v>
       </c>
       <c r="G18" s="16">
         <f>MAX(0,D18-$O$8)</f>
-        <v>5450</v>
+        <v>8000</v>
       </c>
       <c r="H18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -24644,8 +24644,8 @@
       <c r="B19" s="11">
         <v>5</v>
       </c>
-      <c r="C19" s="12">
-        <v>1.3819999999999999</v>
+      <c r="C19" s="12" t="n">
+        <v>1.323</v>
       </c>
       <c r="D19" s="13">
         <f>$O$7</f>
@@ -24656,11 +24656,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19*2*PI()/60*$D$22/(C19*$I$8)*3.6</f>
-        <v>185.49490631905005</v>
+        <v>168.1002465673491</v>
       </c>
       <c r="G19" s="13">
-        <f>MAX(0,D19-$O$8)</f>
-        <v>7700</v>
+        <f>MAX(0,D19-250)</f>
+        <v>8250</v>
       </c>
       <c r="H19" s="11" t="str">
         <f>VLOOKUP("label.limiter",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -24721,8 +24721,8 @@
         <v>轮胎半径 (m)</v>
       </c>
       <c r="C22" s="34"/>
-      <c r="D22" s="18">
-        <v>0.32</v>
+      <c r="D22" s="18" t="n">
+        <v>0.31</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="34" t="str">
@@ -24730,8 +24730,8 @@
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
       <c r="G22" s="34"/>
-      <c r="H22" s="19">
-        <v>5.2788544000000002</v>
+      <c r="H22" s="19" t="n">
+        <v>5.0655424</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -24750,8 +24750,8 @@
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
       <c r="C23" s="34"/>
-      <c r="D23" s="20">
-        <v>1.85</v>
+      <c r="D23" s="20" t="n">
+        <v>1.65</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="34" t="str">
@@ -24759,8 +24759,8 @@
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
       <c r="G23" s="34"/>
-      <c r="H23" s="21">
-        <v>9.7999999999999997E-4</v>
+      <c r="H23" s="21" t="n">
+        <v>0.00078</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -25334,8 +25334,8 @@
         <v>1</v>
       </c>
       <c r="E53" s="34" t="str">
-        <f>VLOOKUP("label.groupOneRx1Placeholder",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>第 1 组 · RX1 占位</v>
+        <f>SUBSTITUTE(VLOOKUP("label.groupOneRx1",Locale!$A$2:$D$73,4,FALSE),"RX1","RX3")</f>
+        <v>第 1 组 · RX3</v>
       </c>
       <c r="F53" s="34"/>
       <c r="G53" s="34"/>
@@ -29989,8 +29989,7 @@
     <row r="155" spans="1:13" ht="32" customHeight="1">
       <c r="A155" s="1"/>
       <c r="B155" s="29" t="str">
-        <f>VLOOKUP("note.rx3Rx1Placeholder",Locale!$A$2:$D$73,4,FALSE)</f>
-        <v>RX3 · RX1 占位</v>
+        <v>RX3</v>
       </c>
       <c r="C155" s="29"/>
       <c r="D155" s="29"/>
@@ -30029,15 +30028,15 @@
     </row>
     <row r="157" spans="1:13" ht="22.5" customHeight="1">
       <c r="A157" s="1"/>
-      <c r="B157" s="1">
+      <c r="B157" s="1" t="n">
         <v>2500</v>
       </c>
-      <c r="C157" s="3">
-        <v>781.33066149713</v>
+      <c r="C157" s="3" t="n">
+        <v>151.83930704375</v>
       </c>
       <c r="D157" s="4">
-        <f>274.31450970575*735.49875/745.69987158227</f>
-        <v>270.56190658493745</v>
+        <f>53.308704135529*735.49875/745.6998715822702</f>
+        <v>52.579444827590663</v>
       </c>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
@@ -30051,15 +30050,15 @@
     </row>
     <row r="158" spans="1:13" ht="22.5" customHeight="1">
       <c r="A158" s="1"/>
-      <c r="B158" s="1">
+      <c r="B158" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="C158" s="3">
-        <v>815.57037906490996</v>
+      <c r="C158" s="3" t="n">
+        <v>159.2371684525</v>
       </c>
       <c r="D158" s="4">
-        <f>343.60272753414*735.49875/745.69987158227</f>
-        <v>338.90226648653652</v>
+        <f>67.087190522816*735.49875/745.6998715822702</f>
+        <v>66.169442494129825</v>
       </c>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
@@ -30073,15 +30072,15 @@
     </row>
     <row r="159" spans="1:13" ht="22.5" customHeight="1">
       <c r="A159" s="1"/>
-      <c r="B159" s="1">
+      <c r="B159" s="1" t="n">
         <v>3500</v>
       </c>
-      <c r="C159" s="3">
-        <v>839.31014412132004</v>
+      <c r="C159" s="3" t="n">
+        <v>165.63502986125</v>
       </c>
       <c r="D159" s="4">
-        <f>412.53843837174*735.49875/745.69987158227</f>
-        <v>406.89494166808578</v>
+        <f>81.413071243352*735.49875/745.6998715822702</f>
+        <v>80.299346178095874</v>
       </c>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
@@ -30095,15 +30094,15 @@
     </row>
     <row r="160" spans="1:13" ht="22.5" customHeight="1">
       <c r="A160" s="1"/>
-      <c r="B160" s="1">
+      <c r="B160" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="C160" s="3">
-        <v>849.15980634939001</v>
+      <c r="C160" s="3" t="n">
+        <v>172.03289127</v>
       </c>
       <c r="D160" s="4">
-        <f>477.00543172178*735.49875/745.69987158227</f>
-        <v>470.48003110172607</v>
+        <f>96.637432621049*735.49875/745.6998715822702</f>
+        <v>95.315439367283247</v>
       </c>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
@@ -30117,15 +30116,15 @@
     </row>
     <row r="161" spans="1:13" ht="22.5" customHeight="1">
       <c r="A161" s="1"/>
-      <c r="B161" s="1">
-        <v>4141</v>
-      </c>
-      <c r="C161" s="3">
-        <v>849.65874099113</v>
+      <c r="B161" s="1" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>181.43075267875</v>
       </c>
       <c r="D161" s="4">
-        <f>494.11002333565*735.49875/745.69987158227</f>
-        <v>487.35063311023652</v>
+        <f>114.65614080504*735.49875/745.6998715822702</f>
+        <v>113.08765289578997</v>
       </c>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
@@ -30139,15 +30138,15 @@
     </row>
     <row r="162" spans="1:13" ht="22.5" customHeight="1">
       <c r="A162" s="1"/>
-      <c r="B162" s="1">
-        <v>4500</v>
-      </c>
-      <c r="C162" s="3">
-        <v>846.29453700936006</v>
+      <c r="B162" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>191.8286140875</v>
       </c>
       <c r="D162" s="4">
-        <f>534.8203883037*735.49875/745.69987158227</f>
-        <v>527.5040831604706</v>
+        <f>134.69680588272*735.49875/745.6998715822702</f>
+        <v>132.85416309046971</v>
       </c>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
@@ -30161,15 +30160,15 @@
     </row>
     <row r="163" spans="1:13" ht="22.5" customHeight="1">
       <c r="A163" s="1"/>
-      <c r="B163" s="1">
-        <v>5000</v>
-      </c>
-      <c r="C163" s="3">
-        <v>830.31349066587995</v>
+      <c r="B163" s="1" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>200.22647549625</v>
       </c>
       <c r="D163" s="4">
-        <f>583.02342226696*735.49875/745.69987158227</f>
-        <v>575.04770302318877</v>
+        <f>154.6529099106*735.49875/745.6998715822702</f>
+        <v>152.537269024539</v>
       </c>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
@@ -30183,15 +30182,15 @@
     </row>
     <row r="164" spans="1:13" ht="22.5" customHeight="1">
       <c r="A164" s="1"/>
-      <c r="B164" s="1">
-        <v>5500</v>
-      </c>
-      <c r="C164" s="3">
-        <v>778.94554556110995</v>
+      <c r="B164" s="1" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>203.624336905</v>
       </c>
       <c r="D164" s="4">
-        <f>601.64968186327*735.49875/745.69987158227</f>
-        <v>593.4191567035989</v>
+        <f>171.57532776781*735.49875/745.6998715822702</f>
+        <v>169.22818940051559</v>
       </c>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
@@ -30205,15 +30204,15 @@
     </row>
     <row r="165" spans="1:13" ht="22.5" customHeight="1">
       <c r="A165" s="1"/>
-      <c r="B165" s="1">
-        <v>5690</v>
-      </c>
-      <c r="C165" s="3">
-        <v>754.97659059928003</v>
+      <c r="B165" s="1" t="n">
+        <v>6292</v>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>204.07922467171</v>
       </c>
       <c r="D165" s="4">
-        <f>603.28101147836*735.49875/745.69987158227</f>
-        <v>595.02816984475828</v>
+        <f>180.32727227891*735.49875/745.6998715822702</f>
+        <v>177.86040792876196</v>
       </c>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
@@ -30227,15 +30226,15 @@
     </row>
     <row r="166" spans="1:13" ht="22.5" customHeight="1">
       <c r="A166" s="1"/>
-      <c r="B166" s="1">
-        <v>6000</v>
-      </c>
-      <c r="C166" s="3">
-        <v>713.52169310327997</v>
+      <c r="B166" s="1" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>204.02219831375</v>
       </c>
       <c r="D166" s="4">
-        <f>601.21849983361*735.49875/745.69987158227</f>
-        <v>592.99387321365498</v>
+        <f>186.23644936697*735.49875/745.6998715822702</f>
+        <v>183.68874789156061</v>
       </c>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
@@ -30249,15 +30248,15 @@
     </row>
     <row r="167" spans="1:13" ht="22.5" customHeight="1">
       <c r="A167" s="1"/>
-      <c r="B167" s="1">
-        <v>6500</v>
-      </c>
-      <c r="C167" s="3">
-        <v>650.00523948523005</v>
+      <c r="B167" s="1" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>203.4200597225</v>
       </c>
       <c r="D167" s="4">
-        <f>593.34067014361*735.49875/745.69987158227</f>
-        <v>585.22381167748551</v>
+        <f>199.97040273893*735.49875/745.6998715822702</f>
+        <v>197.23482175127756</v>
       </c>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
@@ -30271,15 +30270,15 @@
     </row>
     <row r="168" spans="1:13" ht="22.5" customHeight="1">
       <c r="A168" s="1"/>
-      <c r="B168" s="1">
-        <v>7000</v>
-      </c>
-      <c r="C168" s="3">
-        <v>590.16354933322998</v>
+      <c r="B168" s="1" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>201.81792113125</v>
       </c>
       <c r="D168" s="4">
-        <f>580.15538292043*735.49875/745.69987158227</f>
-        <v>572.21889825237974</v>
+        <f>212.56653608937*735.49875/745.6998715822702</f>
+        <v>209.65864088701659</v>
       </c>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
@@ -30293,15 +30292,15 @@
     </row>
     <row r="169" spans="1:13" ht="22.5" customHeight="1">
       <c r="A169" s="1"/>
-      <c r="B169" s="1">
-        <v>7500</v>
-      </c>
-      <c r="C169" s="3">
-        <v>529.20441413318997</v>
+      <c r="B169" s="1" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>199.21578254</v>
       </c>
       <c r="D169" s="4">
-        <f>557.3892970701*735.49875/745.69987158227</f>
-        <v>549.764250848752</v>
+        <f>223.81419762392*735.49875/745.6998715822702</f>
+        <v>220.75243520607853</v>
       </c>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
@@ -30315,15 +30314,15 @@
     </row>
     <row r="170" spans="1:13" ht="22.5" customHeight="1">
       <c r="A170" s="1"/>
-      <c r="B170" s="1">
-        <v>8000</v>
-      </c>
-      <c r="C170" s="3">
-        <v>466.5003138289</v>
+      <c r="B170" s="1" t="n">
+        <v>8355</v>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>193.99604814021</v>
       </c>
       <c r="D170" s="4">
-        <f>524.10201691704*735.49875/745.69987158227</f>
-        <v>516.93233833745376</v>
+        <f>227.62147909892*735.49875/745.6998715822702</f>
+        <v>224.50763333936891</v>
       </c>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
@@ -30337,15 +30336,15 @@
     </row>
     <row r="171" spans="1:13" ht="22.5" customHeight="1">
       <c r="A171" s="1"/>
-      <c r="B171" s="1">
+      <c r="B171" s="1" t="n">
         <v>8499</v>
       </c>
-      <c r="C171" s="3">
-        <v>397.788442868</v>
+      <c r="C171" s="3" t="n">
+        <v>189.65178627393</v>
       </c>
       <c r="D171" s="4">
-        <f>474.78161591297*735.49875/745.69987158227</f>
-        <v>468.28663693613572</v>
+        <f>226.35947112671*735.49875/745.6998715822702</f>
+        <v>223.26288954709636</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -35054,23 +35053,23 @@
       </c>
       <c r="C392" s="20">
         <f>'RX3'!C15</f>
-        <v>3.24</v>
+        <v>4.024</v>
       </c>
       <c r="D392" s="20">
         <f>'RX3'!D15</f>
-        <v>6000</v>
+        <v>8500</v>
       </c>
       <c r="E392" s="20">
         <f>'RX3'!F15</f>
-        <v>55.850536063818538</v>
+        <v>55.267551244682615</v>
       </c>
       <c r="F392" s="20">
         <f>'RX3'!E15</f>
-        <v>4812.9629629629635</v>
+        <v>6197.564612326044</v>
       </c>
       <c r="G392" s="20">
         <f>E392*'RX3'!$O$7/D392</f>
-        <v>79.121592757076257</v>
+        <v>55.267551244682615</v>
       </c>
       <c r="H392" s="1"/>
       <c r="I392" s="1"/>
@@ -35086,23 +35085,23 @@
       </c>
       <c r="C393" s="20">
         <f>'RX3'!C16</f>
-        <v>2.5990000000000002</v>
+        <v>2.9340000000000002</v>
       </c>
       <c r="D393" s="20">
         <f>'RX3'!D16</f>
-        <v>6170</v>
+        <v>8500</v>
       </c>
       <c r="E393" s="20">
         <f>'RX3'!F16</f>
-        <v>71.597851503436175</v>
+        <v>75.79980443374329</v>
       </c>
       <c r="F393" s="20">
         <f>'RX3'!E16</f>
-        <v>4952.1431319738349</v>
+        <v>6318.5071574642125</v>
       </c>
       <c r="G393" s="20">
         <f>E393*'RX3'!$O$7/D393</f>
-        <v>98.635613902626829</v>
+        <v>75.79980443374329</v>
       </c>
       <c r="H393" s="1"/>
       <c r="I393" s="1"/>
@@ -35118,23 +35117,23 @@
       </c>
       <c r="C394" s="20">
         <f>'RX3'!C17</f>
-        <v>2.0859999999999999</v>
+        <v>2.181</v>
       </c>
       <c r="D394" s="20">
         <f>'RX3'!D17</f>
-        <v>6220</v>
+        <v>8500</v>
       </c>
       <c r="E394" s="20">
         <f>'RX3'!F17</f>
-        <v>89.928466218194515</v>
+        <v>101.97002577194077</v>
       </c>
       <c r="F394" s="20">
         <f>'RX3'!E17</f>
-        <v>5039.2138063278999</v>
+        <v>6461.7148097203117</v>
       </c>
       <c r="G394" s="20">
         <f>E394*'RX3'!$O$7/D394</f>
-        <v>122.89259852968704</v>
+        <v>101.97002577194077</v>
       </c>
       <c r="H394" s="1"/>
       <c r="I394" s="1"/>
@@ -35150,23 +35149,23 @@
       </c>
       <c r="C395" s="20">
         <f>'RX3'!C18</f>
-        <v>1.69</v>
+        <v>1.6579999999999999</v>
       </c>
       <c r="D395" s="20">
         <f>'RX3'!D18</f>
-        <v>6250</v>
+        <v>8500</v>
       </c>
       <c r="E395" s="20">
         <f>'RX3'!F18</f>
-        <v>111.53583385525893</v>
+        <v>134.13548022231774</v>
       </c>
       <c r="F395" s="20">
         <f>'RX3'!E18</f>
-        <v>5110.9467455621307</v>
+        <v>6782.5693606755131</v>
       </c>
       <c r="G395" s="20">
         <f>E395*'RX3'!$O$7/D395</f>
-        <v>151.68873404315215</v>
+        <v>134.13548022231774</v>
       </c>
       <c r="H395" s="1"/>
       <c r="I395" s="1"/>
@@ -35182,7 +35181,7 @@
       </c>
       <c r="C396" s="20">
         <f>'RX3'!C19</f>
-        <v>1.3819999999999999</v>
+        <v>1.323</v>
       </c>
       <c r="D396" s="20">
         <f>'RX3'!D19</f>
@@ -35190,7 +35189,7 @@
       </c>
       <c r="E396" s="20">
         <f>'RX3'!F19</f>
-        <v>185.49490631905005</v>
+        <v>168.1002465673491</v>
       </c>
       <c r="F396" s="20" t="str">
         <f>""</f>
@@ -35198,7 +35197,7 @@
       </c>
       <c r="G396" s="20">
         <f>E396*'RX3'!$O$7/D396</f>
-        <v>185.49490631905005</v>
+        <v>168.1002465673491</v>
       </c>
       <c r="H396" s="1"/>
       <c r="I396" s="1"/>
@@ -35346,7 +35345,7 @@
       <c r="A403" s="1"/>
       <c r="B403" s="1">
         <f>G392</f>
-        <v>79.121592757076257</v>
+        <v>55.267551244682615</v>
       </c>
       <c r="C403" s="1">
         <f>'RX3'!$O$7</f>
@@ -35354,7 +35353,7 @@
       </c>
       <c r="D403" s="1">
         <f>G393</f>
-        <v>98.635613902626829</v>
+        <v>75.79980443374329</v>
       </c>
       <c r="E403" s="1">
         <f>'RX3'!$O$7</f>
@@ -35362,7 +35361,7 @@
       </c>
       <c r="F403" s="1">
         <f>G394</f>
-        <v>122.89259852968704</v>
+        <v>101.97002577194077</v>
       </c>
       <c r="G403" s="1">
         <f>'RX3'!$O$7</f>
@@ -35370,7 +35369,7 @@
       </c>
       <c r="H403" s="1">
         <f>G395</f>
-        <v>151.68873404315215</v>
+        <v>134.13548022231774</v>
       </c>
       <c r="I403" s="1">
         <f>'RX3'!$O$7</f>
@@ -35378,7 +35377,7 @@
       </c>
       <c r="J403" s="1">
         <f>G396</f>
-        <v>185.49490631905005</v>
+        <v>168.1002465673491</v>
       </c>
       <c r="K403" s="1">
         <f>'RX3'!$O$7</f>
@@ -35467,35 +35466,35 @@
       <c r="A408" s="1"/>
       <c r="B408" s="1">
         <f>E392</f>
-        <v>55.850536063818538</v>
+        <v>55.267551244682615</v>
       </c>
       <c r="C408" s="1">
         <f>D392</f>
-        <v>6000</v>
+        <v>8500</v>
       </c>
       <c r="D408" s="1">
         <f>E393</f>
-        <v>71.597851503436175</v>
+        <v>75.79980443374329</v>
       </c>
       <c r="E408" s="1">
         <f>D393</f>
-        <v>6170</v>
+        <v>8500</v>
       </c>
       <c r="F408" s="1">
         <f>E394</f>
-        <v>89.928466218194515</v>
+        <v>101.97002577194077</v>
       </c>
       <c r="G408" s="1">
         <f>D394</f>
-        <v>6220</v>
+        <v>8500</v>
       </c>
       <c r="H408" s="1">
         <f>E395</f>
-        <v>111.53583385525893</v>
+        <v>134.13548022231774</v>
       </c>
       <c r="I408" s="1">
         <f>D395</f>
-        <v>6250</v>
+        <v>8500</v>
       </c>
       <c r="J408" s="1"/>
       <c r="K408" s="1"/>
@@ -35506,35 +35505,35 @@
       <c r="A409" s="1"/>
       <c r="B409" s="1">
         <f>E392</f>
-        <v>55.850536063818538</v>
+        <v>55.267551244682615</v>
       </c>
       <c r="C409" s="1">
         <f>F392</f>
-        <v>4812.9629629629635</v>
+        <v>6197.564612326044</v>
       </c>
       <c r="D409" s="1">
         <f>E393</f>
-        <v>71.597851503436175</v>
+        <v>75.79980443374329</v>
       </c>
       <c r="E409" s="1">
         <f>F393</f>
-        <v>4952.1431319738349</v>
+        <v>6318.5071574642125</v>
       </c>
       <c r="F409" s="1">
         <f>E394</f>
-        <v>89.928466218194515</v>
+        <v>101.97002577194077</v>
       </c>
       <c r="G409" s="1">
         <f>F394</f>
-        <v>5039.2138063278999</v>
+        <v>6461.7148097203117</v>
       </c>
       <c r="H409" s="1">
         <f>E395</f>
-        <v>111.53583385525893</v>
+        <v>134.13548022231774</v>
       </c>
       <c r="I409" s="1">
         <f>F395</f>
-        <v>5110.9467455621307</v>
+        <v>6782.5693606755131</v>
       </c>
       <c r="J409" s="1"/>
       <c r="K409" s="1"/>

--- a/docs/gearing_shiftlights.xlsx
+++ b/docs/gearing_shiftlights.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\@Games\Steam_Library\steamapps\common\BeamNG_Userdata\.tmp_codex\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\@Games\Steam_Library\steamapps\common\BeamNG_Userdata\.tmp_codex\kit_taper_stage\after\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3440912B-1EE1-4F4A-9CE2-BD32E4DCD6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42012E4E-E652-49E2-9A61-D1EA48AEE78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1123,22 +1123,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1148,6 +1136,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7880,10 +7880,10 @@
                   <c:v>5500</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>5661</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>6349</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6500</c:v>
@@ -7922,25 +7922,25 @@
                   <c:v>430.39128070018899</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>424.58118536320899</c:v>
+                  <c:v>424.57951548356601</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>395.32862481182298</c:v>
+                  <c:v>396.96215971206198</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>363.78841837355799</c:v>
+                  <c:v>386.44662220812</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>344.35163115915401</c:v>
+                  <c:v>363.39536816149899</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>336.08948400981501</c:v>
+                  <c:v>333.37064286517</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>308.42095837166801</c:v>
+                  <c:v>305.80692930985703</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>281.83133697955299</c:v>
+                  <c:v>278.62052763536002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8022,10 +8022,10 @@
                   <c:v>5500</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>5661</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>6349</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6500</c:v>
@@ -8064,25 +8064,25 @@
                   <c:v>268.26730883588647</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>294.05090743999966</c:v>
+                  <c:v>294.0497509365062</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>301.17070505568455</c:v>
+                  <c:v>302.41517061360446</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>302.33741360177493</c:v>
+                  <c:v>303.02219862871982</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>302.83024370590675</c:v>
+                  <c:v>302.01075728582975</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>302.59382070936732</c:v>
+                  <c:v>300.14594724410972</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>299.04303848784434</c:v>
+                  <c:v>296.50849220581864</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>292.74157760286937</c:v>
+                  <c:v>289.40647156790982</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8454,7 +8454,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>59.09578710545707</c:v>
+                  <c:v>59.095787105457084</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8516,7 +8516,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>82.646227171274901</c:v>
+                  <c:v>82.64622717127493</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8640,7 +8640,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>149.20694704075808</c:v>
+                  <c:v>149.20694704075805</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8761,10 +8761,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>51.216348824729458</c:v>
+                  <c:v>50.822376910693087</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>51.216348824729458</c:v>
+                  <c:v>50.822376910693087</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8776,10 +8776,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6500</c:v>
+                  <c:v>6450</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4647.7937267410953</c:v>
+                  <c:v>4612.0414673046253</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8823,10 +8823,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>73.610239667215509</c:v>
+                  <c:v>72.94906984984533</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73.610239667215509</c:v>
+                  <c:v>72.94906984984533</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8838,10 +8838,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6680</c:v>
+                  <c:v>6620</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4869.695167286246</c:v>
+                  <c:v>4825.9553903345723</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8885,10 +8885,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>100.21898131779952</c:v>
+                  <c:v>99.009702508534971</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100.21898131779952</c:v>
+                  <c:v>99.009702508534971</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8900,10 +8900,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6630</c:v>
+                  <c:v>6550</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5037.5828658847531</c:v>
+                  <c:v>4976.7975522692504</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8947,10 +8947,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>129.90951522348669</c:v>
+                  <c:v>127.12431887872586</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>129.90951522348669</c:v>
+                  <c:v>127.12431887872586</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8962,10 +8962,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6530</c:v>
+                  <c:v>6390</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5210.8523489932886</c:v>
+                  <c:v>5099.1342281879197</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9284,7 +9284,7 @@
                   <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6067</c:v>
+                  <c:v>6057</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6500</c:v>
@@ -9326,28 +9326,28 @@
                   <c:v>409.84192825957501</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>406.29929522419002</c:v>
+                  <c:v>406.29769456235601</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>393.25124246449298</c:v>
+                  <c:v>392.66405833404798</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>368.15627132977102</c:v>
+                  <c:v>367.75892548697999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>364.22134188911002</c:v>
+                  <c:v>364.40324741955197</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>336.32016241731498</c:v>
+                  <c:v>335.57662363556898</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>302.96067217525803</c:v>
+                  <c:v>302.291480294015</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>269.15737544566502</c:v>
+                  <c:v>269.745814160583</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>257.62128362460498</c:v>
+                  <c:v>258.17684992210201</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9432,7 +9432,7 @@
                   <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6067</c:v>
+                  <c:v>6057</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6500</c:v>
@@ -9474,28 +9474,28 @@
                   <c:v>255.45868625274488</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>281.38947407832535</c:v>
+                  <c:v>281.38836551280031</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>299.58810600530364</c:v>
+                  <c:v>299.14077523423327</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>305.96745045583043</c:v>
+                  <c:v>305.63722412550322</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>306.07732665842246</c:v>
+                  <c:v>305.72544561979919</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>302.80150903048889</c:v>
+                  <c:v>302.13207350358789</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>293.74877903216935</c:v>
+                  <c:v>293.09993475597344</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>279.61426420577601</c:v>
+                  <c:v>280.22556403744301</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>272.94690567057808</c:v>
+                  <c:v>273.53552202891285</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13720,6 +13720,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70CDAD8D-2DEB-9946-E007-95FFE6642571}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6350000" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -13945,22 +13999,22 @@
   <sheetData>
     <row r="1" spans="1:17" ht="22" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="30" t="s">
         <v>75</v>
       </c>
       <c r="H1" s="1"/>
@@ -13976,24 +14030,24 @@
     </row>
     <row r="2" spans="1:17" ht="34" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="35" t="str">
+      <c r="B2" s="31" t="str">
         <f>VLOOKUP("title.rally2GearingShiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>Rally2 · 齿比与换挡灯</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17" ht="22.5" customHeight="1">
@@ -14036,170 +14090,170 @@
     </row>
     <row r="5" spans="1:17" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="32" t="str">
         <f>VLOOKUP("chart.engineCurve",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机曲线</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="29" t="str">
+      <c r="F5" s="32" t="str">
         <f>VLOOKUP("label.calibrationBasis",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>标定依据</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="29" t="str">
+      <c r="K5" s="32" t="str">
         <f>VLOOKUP("label.shiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>换挡灯</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" ht="22.5" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="30" t="str">
+      <c r="B6" s="27" t="str">
         <f>VLOOKUP("label.peakPowerHp",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值功率 (hp)</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$7:$D$19)</f>
         <v>285.92508713620288</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="30" t="str">
+      <c r="F6" s="27" t="str">
         <f>VLOOKUP("label.runningMassKg",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>运行质量 (kg)</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="7">
         <v>1420.59</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="30" t="str">
+      <c r="K6" s="27" t="str">
         <f>VLOOKUP("label.neutralFlashRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>空挡闪烁 (rpm)</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28">
         <v>3000</v>
       </c>
-      <c r="P6" s="31"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="32" t="str">
+      <c r="B7" s="33" t="str">
         <f>VLOOKUP("label.powerPeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>功率峰值转速 (rpm)</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$7:$B$19,MATCH(D6,Samples!$D$7:$D$19,0))</f>
         <v>5275</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="33" t="str">
         <f>VLOOKUP("label.engineFlywheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机 + 飞轮转动惯量 (kg m²)</v>
       </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="8">
         <v>0.12343999999999999</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="32" t="str">
+      <c r="K7" s="33" t="str">
         <f>VLOOKUP("label.topGearLimiterRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>最高挡 / 限转 (rpm)</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33">
         <v>7500</v>
       </c>
-      <c r="P7" s="32"/>
+      <c r="P7" s="33"/>
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="30" t="str">
+      <c r="B8" s="27" t="str">
         <f>VLOOKUP("label.peakTorqueNm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩 (Nm)</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$7:$C$19)</f>
         <v>425.46588144156999</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="30" t="str">
+      <c r="F8" s="27" t="str">
         <f>VLOOKUP("label.finalDrive",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>主减速比</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
       <c r="I8" s="9">
         <v>4.1333333333333337</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="30" t="str">
+      <c r="K8" s="27" t="str">
         <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>普通档亮灯范围 (rpm)</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31">
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28">
         <v>500</v>
       </c>
-      <c r="P8" s="31"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="32" t="str">
+      <c r="B9" s="33" t="str">
         <f>VLOOKUP("label.torquePeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩转速 (rpm)</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$7:$B$19,MATCH(D8,Samples!$C$7:$C$19,0))</f>
         <v>4157</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="33" t="str">
         <f>VLOOKUP("label.gearboxTorqueLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱扭矩损失</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="10">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="32" t="str">
+      <c r="K9" s="33" t="str">
         <f>VLOOKUP("label.roundingRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>取整步长 (rpm)</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32">
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>10</v>
       </c>
-      <c r="P9" s="32"/>
+      <c r="P9" s="33"/>
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
@@ -14213,44 +14267,44 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="30" t="str">
+      <c r="K10" s="27" t="str">
         <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>最高档亮灯范围 (rpm)</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="31">
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="28">
         <v>250</v>
       </c>
-      <c r="P10" s="31"/>
+      <c r="P10" s="28"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="34" t="str">
         <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>黄色单元格为手动输入。</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
-      <c r="K11" s="30" t="str">
+      <c r="K11" s="27" t="str">
         <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>空档亮灯范围 (rpm)</v>
       </c>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="31">
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28">
         <v>0</v>
       </c>
-      <c r="P11" s="31"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -14274,27 +14328,27 @@
     </row>
     <row r="13" spans="1:17" ht="32" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="32" t="str">
         <f>VLOOKUP("label.groupOneTypeATarmac",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 1 组 · Type-A / 柏油</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="29" t="str">
+      <c r="J13" s="32" t="str">
         <f>VLOOKUP("label.groupTwoTypeBGravel",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 2 组 · Type-B / 砂石</v>
       </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:17" ht="32" customHeight="1">
@@ -14681,38 +14735,38 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="18">
         <v>0.32500000000000001</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="28" t="str">
+      <c r="F22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="G22" s="28"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="19">
         <v>5.4748128000000005</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="28" t="str">
+      <c r="J22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="K22" s="28"/>
+      <c r="K22" s="35"/>
       <c r="L22" s="18">
         <v>0.32400000000000001</v>
       </c>
       <c r="M22" s="1"/>
-      <c r="N22" s="28" t="str">
+      <c r="N22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="O22" s="28"/>
+      <c r="O22" s="35"/>
       <c r="P22" s="19">
         <v>5.7898434559999998</v>
       </c>
@@ -14720,39 +14774,39 @@
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="C23" s="28"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="20">
         <v>1.65</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="28" t="str">
+      <c r="F23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="G23" s="28"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="21">
         <v>7.7999999999999999E-4</v>
       </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="28" t="str">
+      <c r="J23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="K23" s="28"/>
+      <c r="K23" s="35"/>
       <c r="L23" s="20">
         <f>$D$23</f>
         <v>1.65</v>
       </c>
       <c r="M23" s="1"/>
-      <c r="N23" s="28" t="str">
+      <c r="N23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="O23" s="28"/>
+      <c r="O23" s="35"/>
       <c r="P23" s="21">
         <f>$H$23</f>
         <v>7.7999999999999999E-4</v>
@@ -15312,29 +15366,29 @@
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="28" t="str">
+      <c r="B53" s="35" t="str">
         <f>VLOOKUP("label.gearGroup",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>齿轮组</v>
       </c>
-      <c r="C53" s="28"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="23">
         <v>1</v>
       </c>
-      <c r="E53" s="28" t="str">
+      <c r="E53" s="35" t="str">
         <f>IF(D53=1,VLOOKUP("label.groupOneTypeATarmac",Locale!$A$2:$D$73,4,FALSE),VLOOKUP("label.groupTwoTypeBGravel",Locale!$A$2:$D$73,4,FALSE))</f>
         <v>第 1 组 · Type-A / 柏油</v>
       </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
       <c r="Q53" s="1"/>
     </row>
     <row r="54" spans="1:17" ht="22.5" customHeight="1">
@@ -15852,6 +15906,29 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="E53:P53"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:P8"/>
     <mergeCell ref="K10:N10"/>
     <mergeCell ref="O10:P10"/>
     <mergeCell ref="K11:N11"/>
@@ -15868,29 +15945,6 @@
     <mergeCell ref="O6:P6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="E53:P53"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:G23"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="5">
@@ -16000,12 +16054,12 @@
     </row>
     <row r="5" spans="1:13" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -16551,12 +16605,12 @@
     </row>
     <row r="35" spans="1:13" ht="32" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -16727,11 +16781,11 @@
         <v>5000</v>
       </c>
       <c r="C43" s="3">
-        <v>406.29929522419002</v>
+        <v>406.29769456235601</v>
       </c>
       <c r="D43" s="4">
-        <f>285.292251937627*735.49875/745.69987158227</f>
-        <v>281.38947407832535</v>
+        <f>285.291127996669*735.49875/745.69987158227</f>
+        <v>281.38836551280031</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -16749,11 +16803,11 @@
         <v>5500</v>
       </c>
       <c r="C44" s="3">
-        <v>393.25124246449298</v>
+        <v>392.66405833404798</v>
       </c>
       <c r="D44" s="4">
-        <f>303.743292800607*735.49875/745.69987158227</f>
-        <v>299.58810600530364</v>
+        <f>303.289757701408*735.49875/745.69987158227</f>
+        <v>299.14077523423327</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -16771,11 +16825,11 @@
         <v>6000</v>
       </c>
       <c r="C45" s="3">
-        <v>368.15627132977102</v>
+        <v>367.75892548697999</v>
       </c>
       <c r="D45" s="4">
-        <f>310.211116624287*735.49875/745.69987158227</f>
-        <v>305.96745045583043</v>
+        <f>309.876310165244*735.49875/745.69987158227</f>
+        <v>305.63722412550322</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -16790,14 +16844,14 @@
     <row r="46" spans="1:13" ht="22.5" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
-        <v>6067</v>
+        <v>6057</v>
       </c>
       <c r="C46" s="3">
-        <v>364.22134188911002</v>
+        <v>364.40324741955197</v>
       </c>
       <c r="D46" s="4">
-        <f>310.322516773047*735.49875/745.69987158227</f>
-        <v>306.07732665842246</v>
+        <f>309.965755262149*735.49875/745.69987158227</f>
+        <v>305.72544561979919</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -16815,11 +16869,11 @@
         <v>6500</v>
       </c>
       <c r="C47" s="3">
-        <v>336.32016241731498</v>
+        <v>335.57662363556898</v>
       </c>
       <c r="D47" s="4">
-        <f>307.001264650624*735.49875/745.69987158227</f>
-        <v>302.80150903048889</v>
+        <f>306.322544276942*735.49875/745.69987158227</f>
+        <v>302.13207350358789</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -16837,11 +16891,11 @@
         <v>7000</v>
       </c>
       <c r="C48" s="3">
-        <v>302.96067217525803</v>
+        <v>302.291480294015</v>
       </c>
       <c r="D48" s="4">
-        <f>297.822976316054*735.49875/745.69987158227</f>
-        <v>293.74877903216935</v>
+        <f>297.165132786835*735.49875/745.69987158227</f>
+        <v>293.09993475597344</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -16859,11 +16913,11 @@
         <v>7500</v>
       </c>
       <c r="C49" s="3">
-        <v>269.15737544566502</v>
+        <v>269.745814160583</v>
       </c>
       <c r="D49" s="4">
-        <f>283.492420498088*735.49875/745.69987158227</f>
-        <v>279.61426420577601</v>
+        <f>284.112198853894*735.49875/745.69987158227</f>
+        <v>280.22556403744301</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -16881,11 +16935,11 @@
         <v>7649</v>
       </c>
       <c r="C50" s="3">
-        <v>257.62128362460498</v>
+        <v>258.17684992210201</v>
       </c>
       <c r="D50" s="4">
-        <f>276.732587930745*735.49875/745.69987158227</f>
-        <v>272.94690567057808</v>
+        <f>277.329368201033*735.49875/745.69987158227</f>
+        <v>273.53552202891285</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -17109,12 +17163,12 @@
     </row>
     <row r="65" spans="1:13" ht="32" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="29" t="s">
+      <c r="B65" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="32"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -17674,12 +17728,12 @@
     </row>
     <row r="95" spans="1:13" ht="32" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="29" t="s">
+      <c r="B95" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="C95" s="29"/>
-      <c r="D95" s="29"/>
-      <c r="E95" s="29"/>
+      <c r="C95" s="32"/>
+      <c r="D95" s="32"/>
+      <c r="E95" s="32"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
@@ -18239,12 +18293,12 @@
     </row>
     <row r="125" spans="1:13" ht="32" customHeight="1">
       <c r="A125" s="1"/>
-      <c r="B125" s="29" t="s">
+      <c r="B125" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="C125" s="29"/>
-      <c r="D125" s="29"/>
-      <c r="E125" s="29"/>
+      <c r="C125" s="32"/>
+      <c r="D125" s="32"/>
+      <c r="E125" s="32"/>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
@@ -18804,12 +18858,12 @@
     </row>
     <row r="155" spans="1:13" ht="32" customHeight="1">
       <c r="A155" s="1"/>
-      <c r="B155" s="29" t="s">
+      <c r="B155" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="C155" s="29"/>
-      <c r="D155" s="29"/>
-      <c r="E155" s="29"/>
+      <c r="C155" s="32"/>
+      <c r="D155" s="32"/>
+      <c r="E155" s="32"/>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
@@ -19594,15 +19648,15 @@
     </row>
     <row r="200" spans="1:13" ht="32" customHeight="1">
       <c r="A200" s="1"/>
-      <c r="B200" s="29" t="str">
+      <c r="B200" s="32" t="str">
         <f>VLOOKUP("chart.rally2GearPositions",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>Rally2 · 挡位图</v>
       </c>
-      <c r="C200" s="29"/>
-      <c r="D200" s="29"/>
-      <c r="E200" s="29"/>
-      <c r="F200" s="29"/>
-      <c r="G200" s="29"/>
+      <c r="C200" s="32"/>
+      <c r="D200" s="32"/>
+      <c r="E200" s="32"/>
+      <c r="F200" s="32"/>
+      <c r="G200" s="32"/>
       <c r="H200" s="1"/>
       <c r="I200" s="1"/>
       <c r="J200" s="1"/>
@@ -20409,15 +20463,15 @@
     </row>
     <row r="238" spans="1:13" ht="32" customHeight="1">
       <c r="A238" s="1"/>
-      <c r="B238" s="29" t="str">
+      <c r="B238" s="32" t="str">
         <f>VLOOKUP("chart.wrc16GearPositions",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>WRC16 · 挡位图</v>
       </c>
-      <c r="C238" s="29"/>
-      <c r="D238" s="29"/>
-      <c r="E238" s="29"/>
-      <c r="F238" s="29"/>
-      <c r="G238" s="29"/>
+      <c r="C238" s="32"/>
+      <c r="D238" s="32"/>
+      <c r="E238" s="32"/>
+      <c r="F238" s="32"/>
+      <c r="G238" s="32"/>
       <c r="H238" s="1"/>
       <c r="I238" s="1"/>
       <c r="J238" s="1"/>
@@ -21272,15 +21326,15 @@
     </row>
     <row r="276" spans="1:13" ht="32" customHeight="1">
       <c r="A276" s="1"/>
-      <c r="B276" s="29" t="str">
+      <c r="B276" s="32" t="str">
         <f>VLOOKUP("chart.wrc17GearPositions",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>WRC17 · 挡位图</v>
       </c>
-      <c r="C276" s="29"/>
-      <c r="D276" s="29"/>
-      <c r="E276" s="29"/>
-      <c r="F276" s="29"/>
-      <c r="G276" s="29"/>
+      <c r="C276" s="32"/>
+      <c r="D276" s="32"/>
+      <c r="E276" s="32"/>
+      <c r="F276" s="32"/>
+      <c r="G276" s="32"/>
       <c r="H276" s="1"/>
       <c r="I276" s="1"/>
       <c r="J276" s="1"/>
@@ -22135,15 +22189,15 @@
     </row>
     <row r="314" spans="1:13" ht="32" customHeight="1">
       <c r="A314" s="1"/>
-      <c r="B314" s="29" t="str">
+      <c r="B314" s="32" t="str">
         <f>VLOOKUP("chart.25r1GearPositions",Locale!$A$2:$D$75,4,FALSE)</f>
         <v>25R1 · 档位图</v>
       </c>
-      <c r="C314" s="29"/>
-      <c r="D314" s="29"/>
-      <c r="E314" s="29"/>
-      <c r="F314" s="29"/>
-      <c r="G314" s="29"/>
+      <c r="C314" s="32"/>
+      <c r="D314" s="32"/>
+      <c r="E314" s="32"/>
+      <c r="F314" s="32"/>
+      <c r="G314" s="32"/>
       <c r="H314" s="1"/>
       <c r="I314" s="1"/>
       <c r="J314" s="1"/>
@@ -22950,15 +23004,15 @@
     </row>
     <row r="352" spans="1:13" ht="32" customHeight="1">
       <c r="A352" s="1"/>
-      <c r="B352" s="29" t="str">
+      <c r="B352" s="32" t="str">
         <f>VLOOKUP("chart.rx1GearPositions",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>RX1 · 挡位图</v>
       </c>
-      <c r="C352" s="29"/>
-      <c r="D352" s="29"/>
-      <c r="E352" s="29"/>
-      <c r="F352" s="29"/>
-      <c r="G352" s="29"/>
+      <c r="C352" s="32"/>
+      <c r="D352" s="32"/>
+      <c r="E352" s="32"/>
+      <c r="F352" s="32"/>
+      <c r="G352" s="32"/>
       <c r="H352" s="1"/>
       <c r="I352" s="1"/>
       <c r="J352" s="1"/>
@@ -23813,15 +23867,15 @@
     </row>
     <row r="390" spans="1:13" ht="32" customHeight="1">
       <c r="A390" s="1"/>
-      <c r="B390" s="29" t="str">
+      <c r="B390" s="32" t="str">
         <f>VLOOKUP("chart.rx3GearPositions",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>RX3 · 挡位图</v>
       </c>
-      <c r="C390" s="29"/>
-      <c r="D390" s="29"/>
-      <c r="E390" s="29"/>
-      <c r="F390" s="29"/>
-      <c r="G390" s="29"/>
+      <c r="C390" s="32"/>
+      <c r="D390" s="32"/>
+      <c r="E390" s="32"/>
+      <c r="F390" s="32"/>
+      <c r="G390" s="32"/>
       <c r="H390" s="1"/>
       <c r="I390" s="1"/>
       <c r="J390" s="1"/>
@@ -24673,12 +24727,12 @@
     </row>
     <row r="435" spans="1:13" ht="32" customHeight="1">
       <c r="A435" s="1"/>
-      <c r="B435" s="29" t="s">
+      <c r="B435" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C435" s="29"/>
-      <c r="D435" s="29"/>
-      <c r="E435" s="29"/>
+      <c r="C435" s="32"/>
+      <c r="D435" s="32"/>
+      <c r="E435" s="32"/>
       <c r="F435" s="1"/>
       <c r="G435" s="1"/>
       <c r="H435" s="1"/>
@@ -25043,15 +25097,15 @@
     </row>
     <row r="474" spans="1:13" ht="32" customHeight="1">
       <c r="A474" s="1"/>
-      <c r="B474" s="29" t="str">
+      <c r="B474" s="32" t="str">
         <f>VLOOKUP("chart.rally1GearPositions",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>Rally1 · 挡位图</v>
       </c>
-      <c r="C474" s="29"/>
-      <c r="D474" s="29"/>
-      <c r="E474" s="29"/>
-      <c r="F474" s="29"/>
-      <c r="G474" s="29"/>
+      <c r="C474" s="32"/>
+      <c r="D474" s="32"/>
+      <c r="E474" s="32"/>
+      <c r="F474" s="32"/>
+      <c r="G474" s="32"/>
       <c r="H474" s="1"/>
       <c r="I474" s="1"/>
       <c r="J474" s="1"/>
@@ -25587,12 +25641,12 @@
       <c r="M493" s="1"/>
     </row>
     <row r="500" spans="2:4" ht="15.5">
-      <c r="B500" s="29" t="str">
+      <c r="B500" s="32" t="str">
         <f>Locale!D83</f>
         <v>Rally2 WRC套件</v>
       </c>
-      <c r="C500" s="29"/>
-      <c r="D500" s="29"/>
+      <c r="C500" s="32"/>
+      <c r="D500" s="32"/>
     </row>
     <row r="501" spans="2:4" ht="15.5">
       <c r="B501" s="2" t="s">
@@ -25684,11 +25738,11 @@
         <v>5000</v>
       </c>
       <c r="C508" s="3">
-        <v>424.58118536320899</v>
+        <v>424.57951548356601</v>
       </c>
       <c r="D508" s="4">
-        <f>298.129295143816*735.49875/745.69987158227</f>
-        <v>294.05090743999966</v>
+        <f>298.128122600006*735.49875/745.69987158227</f>
+        <v>294.0497509365062</v>
       </c>
     </row>
     <row r="509" spans="2:4">
@@ -25696,35 +25750,35 @@
         <v>5500</v>
       </c>
       <c r="C509" s="3">
-        <v>395.32862481182298</v>
+        <v>396.96215971206198</v>
       </c>
       <c r="D509" s="4">
-        <f>305.347841970317*735.49875/745.69987158227</f>
-        <v>301.17070505568455</v>
+        <f>306.609567849157*735.49875/745.69987158227</f>
+        <v>302.41517061360446</v>
       </c>
     </row>
     <row r="510" spans="2:4">
       <c r="B510" s="1">
-        <v>6000</v>
+        <v>5661</v>
       </c>
       <c r="C510" s="3">
-        <v>363.78841837355799</v>
+        <v>386.44662220812</v>
       </c>
       <c r="D510" s="4">
-        <f>306.530732373589*735.49875/745.69987158227</f>
-        <v>302.33741360177493</v>
+        <f>307.225015139745*735.49875/745.69987158227</f>
+        <v>303.02219862871982</v>
       </c>
     </row>
     <row r="511" spans="2:4">
       <c r="B511" s="1">
-        <v>6349</v>
+        <v>6000</v>
       </c>
       <c r="C511" s="3">
-        <v>344.35163115915401</v>
+        <v>363.39536816149899</v>
       </c>
       <c r="D511" s="4">
-        <f>307.030397866376*735.49875/745.69987158227</f>
-        <v>302.83024370590675</v>
+        <f>306.199545443833*735.49875/745.69987158227</f>
+        <v>302.01075728582975</v>
       </c>
     </row>
     <row r="512" spans="2:4">
@@ -25732,11 +25786,11 @@
         <v>6500</v>
       </c>
       <c r="C512" s="3">
-        <v>336.08948400981501</v>
+        <v>333.37064286517</v>
       </c>
       <c r="D512" s="4">
-        <f>306.790695761976*735.49875/745.69987158227</f>
-        <v>302.59382070936732</v>
+        <f>304.308871110755*735.49875/745.69987158227</f>
+        <v>300.14594724410972</v>
       </c>
     </row>
     <row r="513" spans="2:13">
@@ -25744,11 +25798,11 @@
         <v>7000</v>
       </c>
       <c r="C513" s="3">
-        <v>308.42095837166801</v>
+        <v>305.80692930985703</v>
       </c>
       <c r="D513" s="4">
-        <f>303.190665379047*735.49875/745.69987158227</f>
-        <v>299.04303848784434</v>
+        <f>300.620965788088*735.49875/745.69987158227</f>
+        <v>296.50849220581864</v>
       </c>
     </row>
     <row r="514" spans="2:13">
@@ -25756,23 +25810,23 @@
         <v>7499</v>
       </c>
       <c r="C514" s="3">
-        <v>281.83133697955299</v>
+        <v>278.62052763536002</v>
       </c>
       <c r="D514" s="4">
-        <f>296.801805339915*735.49875/745.69987158227</f>
-        <v>292.74157760286937</v>
+        <f>293.420442500097*735.49875/745.69987158227</f>
+        <v>289.40647156790982</v>
       </c>
     </row>
     <row r="519" spans="2:13" ht="15.5">
-      <c r="B519" s="29" t="str">
+      <c r="B519" s="32" t="str">
         <f>Locale!D81</f>
         <v>Rally2 WRC套件 · 档位图</v>
       </c>
-      <c r="C519" s="29"/>
-      <c r="D519" s="29"/>
-      <c r="E519" s="29"/>
-      <c r="F519" s="29"/>
-      <c r="G519" s="29"/>
+      <c r="C519" s="32"/>
+      <c r="D519" s="32"/>
+      <c r="E519" s="32"/>
+      <c r="F519" s="32"/>
+      <c r="G519" s="32"/>
       <c r="H519" s="1"/>
       <c r="I519" s="1"/>
       <c r="J519" s="1"/>
@@ -25822,19 +25876,19 @@
       </c>
       <c r="D521" s="20">
         <f>'Rally2 WRC Kit'!D15</f>
-        <v>6500</v>
+        <v>6450</v>
       </c>
       <c r="E521" s="20">
         <f>'Rally2 WRC Kit'!F15</f>
-        <v>51.216348824729458</v>
+        <v>50.822376910693087</v>
       </c>
       <c r="F521" s="20">
         <f>'Rally2 WRC Kit'!E15</f>
-        <v>4647.7937267410953</v>
+        <v>4612.0414673046253</v>
       </c>
       <c r="G521" s="20">
         <f>E521*'Rally2 WRC Kit'!$O$7/D521</f>
-        <v>59.09578710545707</v>
+        <v>59.095787105457084</v>
       </c>
       <c r="H521" s="1"/>
       <c r="I521" s="1"/>
@@ -25853,19 +25907,19 @@
       </c>
       <c r="D522" s="20">
         <f>'Rally2 WRC Kit'!D16</f>
-        <v>6680</v>
+        <v>6620</v>
       </c>
       <c r="E522" s="20">
         <f>'Rally2 WRC Kit'!F16</f>
-        <v>73.610239667215509</v>
+        <v>72.94906984984533</v>
       </c>
       <c r="F522" s="20">
         <f>'Rally2 WRC Kit'!E16</f>
-        <v>4869.695167286246</v>
+        <v>4825.9553903345723</v>
       </c>
       <c r="G522" s="20">
         <f>E522*'Rally2 WRC Kit'!$O$7/D522</f>
-        <v>82.646227171274901</v>
+        <v>82.64622717127493</v>
       </c>
       <c r="H522" s="1"/>
       <c r="I522" s="1"/>
@@ -25884,15 +25938,15 @@
       </c>
       <c r="D523" s="20">
         <f>'Rally2 WRC Kit'!D17</f>
-        <v>6630</v>
+        <v>6550</v>
       </c>
       <c r="E523" s="20">
         <f>'Rally2 WRC Kit'!F17</f>
-        <v>100.21898131779952</v>
+        <v>99.009702508534971</v>
       </c>
       <c r="F523" s="20">
         <f>'Rally2 WRC Kit'!E17</f>
-        <v>5037.5828658847531</v>
+        <v>4976.7975522692504</v>
       </c>
       <c r="G523" s="20">
         <f>E523*'Rally2 WRC Kit'!$O$7/D523</f>
@@ -25915,19 +25969,19 @@
       </c>
       <c r="D524" s="20">
         <f>'Rally2 WRC Kit'!D18</f>
-        <v>6530</v>
+        <v>6390</v>
       </c>
       <c r="E524" s="20">
         <f>'Rally2 WRC Kit'!F18</f>
-        <v>129.90951522348669</v>
+        <v>127.12431887872586</v>
       </c>
       <c r="F524" s="20">
         <f>'Rally2 WRC Kit'!E18</f>
-        <v>5210.8523489932886</v>
+        <v>5099.1342281879197</v>
       </c>
       <c r="G524" s="20">
         <f>E524*'Rally2 WRC Kit'!$O$7/D524</f>
-        <v>149.20694704075808</v>
+        <v>149.20694704075805</v>
       </c>
       <c r="H524" s="1"/>
       <c r="I524" s="1"/>
@@ -26099,7 +26153,7 @@
     <row r="532" spans="2:13">
       <c r="B532" s="1">
         <f>G521</f>
-        <v>59.09578710545707</v>
+        <v>59.095787105457084</v>
       </c>
       <c r="C532" s="1">
         <f>'Rally2 WRC Kit'!$O$7</f>
@@ -26107,7 +26161,7 @@
       </c>
       <c r="D532" s="1">
         <f>G522</f>
-        <v>82.646227171274901</v>
+        <v>82.64622717127493</v>
       </c>
       <c r="E532" s="1">
         <f>'Rally2 WRC Kit'!$O$7</f>
@@ -26123,7 +26177,7 @@
       </c>
       <c r="H532" s="1">
         <f>G524</f>
-        <v>149.20694704075808</v>
+        <v>149.20694704075805</v>
       </c>
       <c r="I532" s="1">
         <f>'Rally2 WRC Kit'!$O$7</f>
@@ -26215,35 +26269,35 @@
     <row r="537" spans="2:13">
       <c r="B537" s="1">
         <f>E521</f>
-        <v>51.216348824729458</v>
+        <v>50.822376910693087</v>
       </c>
       <c r="C537" s="1">
         <f>D521</f>
-        <v>6500</v>
+        <v>6450</v>
       </c>
       <c r="D537" s="1">
         <f>E522</f>
-        <v>73.610239667215509</v>
+        <v>72.94906984984533</v>
       </c>
       <c r="E537" s="1">
         <f>D522</f>
-        <v>6680</v>
+        <v>6620</v>
       </c>
       <c r="F537" s="1">
         <f>E523</f>
-        <v>100.21898131779952</v>
+        <v>99.009702508534971</v>
       </c>
       <c r="G537" s="1">
         <f>D523</f>
-        <v>6630</v>
+        <v>6550</v>
       </c>
       <c r="H537" s="1">
         <f>E524</f>
-        <v>129.90951522348669</v>
+        <v>127.12431887872586</v>
       </c>
       <c r="I537" s="1">
         <f>D524</f>
-        <v>6530</v>
+        <v>6390</v>
       </c>
       <c r="J537" s="1"/>
       <c r="K537" s="1"/>
@@ -26253,35 +26307,35 @@
     <row r="538" spans="2:13">
       <c r="B538" s="1">
         <f>E521</f>
-        <v>51.216348824729458</v>
+        <v>50.822376910693087</v>
       </c>
       <c r="C538" s="1">
         <f>F521</f>
-        <v>4647.7937267410953</v>
+        <v>4612.0414673046253</v>
       </c>
       <c r="D538" s="1">
         <f>E522</f>
-        <v>73.610239667215509</v>
+        <v>72.94906984984533</v>
       </c>
       <c r="E538" s="1">
         <f>F522</f>
-        <v>4869.695167286246</v>
+        <v>4825.9553903345723</v>
       </c>
       <c r="F538" s="1">
         <f>E523</f>
-        <v>100.21898131779952</v>
+        <v>99.009702508534971</v>
       </c>
       <c r="G538" s="1">
         <f>F523</f>
-        <v>5037.5828658847531</v>
+        <v>4976.7975522692504</v>
       </c>
       <c r="H538" s="1">
         <f>E524</f>
-        <v>129.90951522348669</v>
+        <v>127.12431887872586</v>
       </c>
       <c r="I538" s="1">
         <f>F524</f>
-        <v>5210.8523489932886</v>
+        <v>5099.1342281879197</v>
       </c>
       <c r="J538" s="1"/>
       <c r="K538" s="1"/>
@@ -26290,6 +26344,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B390:G390"/>
+    <mergeCell ref="B238:G238"/>
     <mergeCell ref="B500:D500"/>
     <mergeCell ref="B519:G519"/>
     <mergeCell ref="B1:E1"/>
@@ -26306,8 +26362,6 @@
     <mergeCell ref="B474:G474"/>
     <mergeCell ref="B352:G352"/>
     <mergeCell ref="B155:E155"/>
-    <mergeCell ref="B390:G390"/>
-    <mergeCell ref="B238:G238"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26351,24 +26405,24 @@
     </row>
     <row r="2" spans="1:17" ht="34" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="35" t="str">
+      <c r="B2" s="31" t="str">
         <f>Locale!D79</f>
         <v>Rally2 WRC套件 · 齿比与换挡灯</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17" ht="22.5" customHeight="1">
@@ -26414,170 +26468,170 @@
     </row>
     <row r="5" spans="1:17" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="32" t="str">
         <f>VLOOKUP("chart.engineCurve",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机曲线</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="29" t="str">
+      <c r="F5" s="32" t="str">
         <f>VLOOKUP("label.calibrationBasis",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>标定依据</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="29" t="str">
+      <c r="K5" s="32" t="str">
         <f>VLOOKUP("label.shiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>换挡灯</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" ht="22.5" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="30" t="str">
+      <c r="B6" s="27" t="str">
         <f>VLOOKUP("label.peakPowerHp",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值功率 (hp)</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$502:$D$514)</f>
-        <v>302.83024370590675</v>
+        <v>303.02219862871982</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="30" t="str">
+      <c r="F6" s="27" t="str">
         <f>Locale!D82</f>
         <v>估算运行质量 (kg)</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="7">
         <v>1410.59</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="30" t="str">
+      <c r="K6" s="27" t="str">
         <f>VLOOKUP("label.neutralFlashRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>空挡闪烁 (rpm)</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28">
         <v>3000</v>
       </c>
-      <c r="P6" s="31"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="32" t="str">
+      <c r="B7" s="33" t="str">
         <f>VLOOKUP("label.powerPeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>功率峰值转速 (rpm)</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$502:$B$514,MATCH(D6,Samples!$D$502:$D$514,0))</f>
-        <v>6349</v>
+        <v>5661</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="33" t="str">
         <f>VLOOKUP("label.engineFlywheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机 + 飞轮转动惯量 (kg m²)</v>
       </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="8">
         <v>0.12343999999999999</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="32" t="str">
+      <c r="K7" s="33" t="str">
         <f>VLOOKUP("label.topGearLimiterRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>最高挡 / 限转 (rpm)</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33">
         <v>7500</v>
       </c>
-      <c r="P7" s="32"/>
+      <c r="P7" s="33"/>
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="30" t="str">
+      <c r="B8" s="27" t="str">
         <f>VLOOKUP("label.peakTorqueNm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩 (Nm)</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$502:$C$514)</f>
         <v>430.54138302481402</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="30" t="str">
+      <c r="F8" s="27" t="str">
         <f>VLOOKUP("label.finalDrive",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>主减速比</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
       <c r="I8" s="9">
         <v>4.1333333333333302</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="30" t="str">
+      <c r="K8" s="27" t="str">
         <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>普通档亮灯范围 (rpm)</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31">
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28">
         <v>500</v>
       </c>
-      <c r="P8" s="31"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="32" t="str">
+      <c r="B9" s="33" t="str">
         <f>VLOOKUP("label.torquePeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩转速 (rpm)</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$502:$B$514,MATCH(D8,Samples!$C$502:$C$514,0))</f>
         <v>4417</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="33" t="str">
         <f>VLOOKUP("label.gearboxTorqueLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱扭矩损失</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="10">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="32" t="str">
+      <c r="K9" s="33" t="str">
         <f>VLOOKUP("label.roundingRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>取整步长 (rpm)</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32">
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>10</v>
       </c>
-      <c r="P9" s="32"/>
+      <c r="P9" s="33"/>
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
@@ -26591,44 +26645,44 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="30" t="str">
+      <c r="K10" s="27" t="str">
         <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>最高档亮灯范围 (rpm)</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="31">
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="28">
         <v>250</v>
       </c>
-      <c r="P10" s="31"/>
+      <c r="P10" s="28"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="34" t="str">
         <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>黄色单元格为手动输入。</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
-      <c r="K11" s="30" t="str">
+      <c r="K11" s="27" t="str">
         <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>空档亮灯范围 (rpm)</v>
       </c>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="31">
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28">
         <v>0</v>
       </c>
-      <c r="P11" s="31"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -26652,16 +26706,16 @@
     </row>
     <row r="13" spans="1:17" ht="32" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="32" t="str">
         <f>Locale!D80</f>
         <v>第 1 组 · Type-A / 柏油（参考）</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -26725,19 +26779,19 @@
         <v>3.762</v>
       </c>
       <c r="D15" s="22">
-        <v>6500</v>
+        <v>6450</v>
       </c>
       <c r="E15" s="13">
         <f>D15*C16/C15</f>
-        <v>4647.7937267410953</v>
+        <v>4612.0414673046253</v>
       </c>
       <c r="F15" s="14">
         <f>D15*2*PI()/60*$D$22/(C15*$I$8)*3.6</f>
-        <v>51.216348824729458</v>
+        <v>50.822376910693087</v>
       </c>
       <c r="G15" s="13">
         <f>MAX(0,D15-$O$8)</f>
-        <v>6000</v>
+        <v>5950</v>
       </c>
       <c r="H15" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -26762,19 +26816,19 @@
         <v>2.69</v>
       </c>
       <c r="D16" s="22">
-        <v>6680</v>
+        <v>6620</v>
       </c>
       <c r="E16" s="16">
         <f>D16*C17/C16</f>
-        <v>4869.695167286246</v>
+        <v>4825.9553903345723</v>
       </c>
       <c r="F16" s="17">
         <f>D16*2*PI()/60*$D$22/(C16*$I$8)*3.6</f>
-        <v>73.610239667215509</v>
+        <v>72.94906984984533</v>
       </c>
       <c r="G16" s="16">
         <f>MAX(0,D16-$O$8)</f>
-        <v>6180</v>
+        <v>6120</v>
       </c>
       <c r="H16" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -26799,19 +26853,19 @@
         <v>1.9610000000000001</v>
       </c>
       <c r="D17" s="22">
-        <v>6630</v>
+        <v>6550</v>
       </c>
       <c r="E17" s="13">
         <f>D17*C18/C17</f>
-        <v>5037.5828658847531</v>
+        <v>4976.7975522692504</v>
       </c>
       <c r="F17" s="14">
         <f>D17*2*PI()/60*$D$22/(C17*$I$8)*3.6</f>
-        <v>100.21898131779952</v>
+        <v>99.009702508534971</v>
       </c>
       <c r="G17" s="13">
         <f>MAX(0,D17-$O$8)</f>
-        <v>6130</v>
+        <v>6050</v>
       </c>
       <c r="H17" s="11" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -26836,19 +26890,19 @@
         <v>1.49</v>
       </c>
       <c r="D18" s="22">
-        <v>6530</v>
+        <v>6390</v>
       </c>
       <c r="E18" s="16">
         <f>D18*C19/C18</f>
-        <v>5210.8523489932886</v>
+        <v>5099.1342281879197</v>
       </c>
       <c r="F18" s="17">
         <f>D18*2*PI()/60*$D$22/(C18*$I$8)*3.6</f>
-        <v>129.90951522348669</v>
+        <v>127.12431887872586</v>
       </c>
       <c r="G18" s="16">
         <f>MAX(0,D18-$O$8)</f>
-        <v>6030</v>
+        <v>5890</v>
       </c>
       <c r="H18" s="15" t="str">
         <f>VLOOKUP("label.shift",Locale!$A$2:$D$73,4,FALSE)</f>
@@ -26941,20 +26995,20 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="18">
         <v>0.32500000000000001</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="28" t="str">
+      <c r="F22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="G22" s="28"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="19">
         <v>5.4748127999999996</v>
       </c>
@@ -26970,20 +27024,20 @@
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="C23" s="28"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="20">
         <v>1.65</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="28" t="str">
+      <c r="F23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="G23" s="28"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="21">
         <v>7.7999999999999999E-4</v>
       </c>
@@ -27550,29 +27604,29 @@
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="28" t="str">
+      <c r="B53" s="35" t="str">
         <f>VLOOKUP("label.gearGroup",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>齿轮组</v>
       </c>
-      <c r="C53" s="28"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="23">
         <v>1</v>
       </c>
-      <c r="E53" s="28" t="str">
+      <c r="E53" s="35" t="str">
         <f>Locale!D80</f>
         <v>第 1 组 · Type-A / 柏油（参考）</v>
       </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
       <c r="Q53" s="1"/>
     </row>
     <row r="54" spans="1:17" ht="22.5" customHeight="1">
@@ -28090,11 +28144,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:P8"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="E53:P53"/>
     <mergeCell ref="B9:C9"/>
@@ -28106,23 +28172,11 @@
     <mergeCell ref="K10:N10"/>
     <mergeCell ref="O10:P10"/>
     <mergeCell ref="K11:N11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B3:P3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="K5:P5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F23:G23"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -28182,24 +28236,24 @@
     </row>
     <row r="2" spans="1:17" ht="34" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="35" t="str">
+      <c r="B2" s="31" t="str">
         <f>VLOOKUP("title.wrc16GearingShiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>WRC16 · 齿比与换挡灯</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17" ht="22.5" customHeight="1">
@@ -28242,170 +28296,170 @@
     </row>
     <row r="5" spans="1:17" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="32" t="str">
         <f>VLOOKUP("chart.engineCurve",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机曲线</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="29" t="str">
+      <c r="F5" s="32" t="str">
         <f>VLOOKUP("label.calibrationBasis",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>标定依据</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="29" t="str">
+      <c r="K5" s="32" t="str">
         <f>VLOOKUP("label.shiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>换挡灯</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" ht="22.5" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="30" t="str">
+      <c r="B6" s="27" t="str">
         <f>VLOOKUP("label.peakPowerHp",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值功率 (hp)</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$37:$D$50)</f>
-        <v>306.07732665842246</v>
+        <v>305.72544561979919</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="30" t="str">
+      <c r="F6" s="27" t="str">
         <f>VLOOKUP("label.runningMassKg",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>运行质量 (kg)</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="7">
         <v>1390</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="30" t="str">
+      <c r="K6" s="27" t="str">
         <f>VLOOKUP("label.neutralFlashRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>空挡闪烁 (rpm)</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28">
         <v>3000</v>
       </c>
-      <c r="P6" s="31"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="32" t="str">
+      <c r="B7" s="33" t="str">
         <f>VLOOKUP("label.powerPeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>功率峰值转速 (rpm)</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$37:$B$50,MATCH(D6,Samples!$D$37:$D$50,0))</f>
-        <v>6067</v>
+        <v>6057</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="33" t="str">
         <f>VLOOKUP("label.engineFlywheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机 + 飞轮转动惯量 (kg m²)</v>
       </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="8">
         <v>0.12171599999999999</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="32" t="str">
+      <c r="K7" s="33" t="str">
         <f>VLOOKUP("label.topGearLimiterRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>最高挡 / 限转 (rpm)</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33">
         <v>7650</v>
       </c>
-      <c r="P7" s="32"/>
+      <c r="P7" s="33"/>
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="30" t="str">
+      <c r="B8" s="27" t="str">
         <f>VLOOKUP("label.peakTorqueNm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩 (Nm)</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$37:$C$50)</f>
         <v>409.897678258469</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="30" t="str">
+      <c r="F8" s="27" t="str">
         <f>VLOOKUP("label.finalDrive",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>主减速比</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
       <c r="I8" s="9">
         <v>4.1333333333333337</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="30" t="str">
+      <c r="K8" s="27" t="str">
         <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>普通档亮灯范围 (rpm)</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31">
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28">
         <v>500</v>
       </c>
-      <c r="P8" s="31"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="32" t="str">
+      <c r="B9" s="33" t="str">
         <f>VLOOKUP("label.torquePeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩转速 (rpm)</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$37:$B$50,MATCH(D8,Samples!$C$37:$C$50,0))</f>
         <v>4436</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="33" t="str">
         <f>VLOOKUP("label.gearboxTorqueLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱扭矩损失</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="10">
         <v>1.2E-2</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="32" t="str">
+      <c r="K9" s="33" t="str">
         <f>VLOOKUP("label.roundingRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>取整步长 (rpm)</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32">
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>10</v>
       </c>
-      <c r="P9" s="32"/>
+      <c r="P9" s="33"/>
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
@@ -28419,44 +28473,44 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="30" t="str">
+      <c r="K10" s="27" t="str">
         <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>最高档亮灯范围 (rpm)</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="31">
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="28">
         <v>250</v>
       </c>
-      <c r="P10" s="31"/>
+      <c r="P10" s="28"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="34" t="str">
         <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>黄色单元格为手动输入。</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
-      <c r="K11" s="30" t="str">
+      <c r="K11" s="27" t="str">
         <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>空档亮灯范围 (rpm)</v>
       </c>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="31">
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28">
         <v>0</v>
       </c>
-      <c r="P11" s="31"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -28480,27 +28534,27 @@
     </row>
     <row r="13" spans="1:17" ht="32" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="32" t="str">
         <f>VLOOKUP("label.groupOneTypeATarmac",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 1 组 · Type-A / 柏油</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="29" t="str">
+      <c r="J13" s="32" t="str">
         <f>VLOOKUP("label.groupTwoTypeBGravel",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 2 组 · Type-B / 砂石</v>
       </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:17" ht="32" customHeight="1">
@@ -28923,38 +28977,38 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="18">
         <v>0.32500000000000001</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="28" t="str">
+      <c r="F22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="G22" s="28"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="19">
         <v>5.4748128000000005</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="28" t="str">
+      <c r="J22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="K22" s="28"/>
+      <c r="K22" s="35"/>
       <c r="L22" s="18">
         <v>0.32400000000000001</v>
       </c>
       <c r="M22" s="1"/>
-      <c r="N22" s="28" t="str">
+      <c r="N22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="O22" s="28"/>
+      <c r="O22" s="35"/>
       <c r="P22" s="19">
         <v>5.7898434559999998</v>
       </c>
@@ -28962,39 +29016,39 @@
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="C23" s="28"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="20">
         <v>1.85</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="28" t="str">
+      <c r="F23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="G23" s="28"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="21">
         <v>9.7999999999999997E-4</v>
       </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="28" t="str">
+      <c r="J23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="K23" s="28"/>
+      <c r="K23" s="35"/>
       <c r="L23" s="20">
         <f>$D$23</f>
         <v>1.85</v>
       </c>
       <c r="M23" s="1"/>
-      <c r="N23" s="28" t="str">
+      <c r="N23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="O23" s="28"/>
+      <c r="O23" s="35"/>
       <c r="P23" s="21">
         <f>$H$23</f>
         <v>9.7999999999999997E-4</v>
@@ -29554,29 +29608,29 @@
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="28" t="str">
+      <c r="B53" s="35" t="str">
         <f>VLOOKUP("label.gearGroup",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>齿轮组</v>
       </c>
-      <c r="C53" s="28"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="23">
         <v>1</v>
       </c>
-      <c r="E53" s="28" t="str">
+      <c r="E53" s="35" t="str">
         <f>IF(D53=1,VLOOKUP("label.groupOneTypeATarmac",Locale!$A$2:$D$73,4,FALSE),VLOOKUP("label.groupTwoTypeBGravel",Locale!$A$2:$D$73,4,FALSE))</f>
         <v>第 1 组 · Type-A / 柏油</v>
       </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
       <c r="Q53" s="1"/>
     </row>
     <row r="54" spans="1:17" ht="22.5" customHeight="1">
@@ -30094,31 +30148,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="K5:P5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="O11:P11"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="E53:P53"/>
     <mergeCell ref="J13:P13"/>
@@ -30131,6 +30160,31 @@
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="O6:P6"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -30190,24 +30244,24 @@
     </row>
     <row r="2" spans="1:17" ht="34" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="35" t="str">
+      <c r="B2" s="31" t="str">
         <f>VLOOKUP("title.wrc17GearingShiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>WRC17 · 齿比与换挡灯</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17" ht="22.5" customHeight="1">
@@ -30250,170 +30304,170 @@
     </row>
     <row r="5" spans="1:17" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="32" t="str">
         <f>VLOOKUP("chart.engineCurve",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机曲线</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="29" t="str">
+      <c r="F5" s="32" t="str">
         <f>VLOOKUP("label.calibrationBasis",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>标定依据</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="29" t="str">
+      <c r="K5" s="32" t="str">
         <f>VLOOKUP("label.shiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>换挡灯</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" ht="22.5" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="30" t="str">
+      <c r="B6" s="27" t="str">
         <f>VLOOKUP("label.peakPowerHp",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值功率 (hp)</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$67:$D$81)</f>
         <v>379.38933991421766</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="30" t="str">
+      <c r="F6" s="27" t="str">
         <f>VLOOKUP("label.runningMassKg",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>运行质量 (kg)</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="7">
         <v>1391.01</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="30" t="str">
+      <c r="K6" s="27" t="str">
         <f>VLOOKUP("label.neutralFlashRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>空挡闪烁 (rpm)</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28">
         <v>3000</v>
       </c>
-      <c r="P6" s="31"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="32" t="str">
+      <c r="B7" s="33" t="str">
         <f>VLOOKUP("label.powerPeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>功率峰值转速 (rpm)</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$67:$B$81,MATCH(D6,Samples!$D$67:$D$81,0))</f>
         <v>6619</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="33" t="str">
         <f>VLOOKUP("label.engineFlywheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机 + 飞轮转动惯量 (kg m²)</v>
       </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="8">
         <v>0.12171599999999999</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="32" t="str">
+      <c r="K7" s="33" t="str">
         <f>VLOOKUP("label.topGearLimiterRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>最高挡 / 限转 (rpm)</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33">
         <v>8500</v>
       </c>
-      <c r="P7" s="32"/>
+      <c r="P7" s="33"/>
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="30" t="str">
+      <c r="B8" s="27" t="str">
         <f>VLOOKUP("label.peakTorqueNm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩 (Nm)</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$67:$C$81)</f>
         <v>451.20326615827997</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="30" t="str">
+      <c r="F8" s="27" t="str">
         <f>VLOOKUP("label.finalDrive",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>主减速比</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
       <c r="I8" s="9">
         <v>4.4666666666666668</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="30" t="str">
+      <c r="K8" s="27" t="str">
         <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>普通档亮灯范围 (rpm)</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31">
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28">
         <v>500</v>
       </c>
-      <c r="P8" s="31"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="32" t="str">
+      <c r="B9" s="33" t="str">
         <f>VLOOKUP("label.torquePeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩转速 (rpm)</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$67:$B$81,MATCH(D8,Samples!$C$67:$C$81,0))</f>
         <v>4719</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="33" t="str">
         <f>VLOOKUP("label.gearboxTorqueLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱扭矩损失</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="10">
         <v>1.2E-2</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="32" t="str">
+      <c r="K9" s="33" t="str">
         <f>VLOOKUP("label.roundingRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>取整步长 (rpm)</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32">
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>10</v>
       </c>
-      <c r="P9" s="32"/>
+      <c r="P9" s="33"/>
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
@@ -30427,44 +30481,44 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="30" t="str">
+      <c r="K10" s="27" t="str">
         <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>最高档亮灯范围 (rpm)</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="31">
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="28">
         <v>250</v>
       </c>
-      <c r="P10" s="31"/>
+      <c r="P10" s="28"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="34" t="str">
         <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>黄色单元格为手动输入。</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
-      <c r="K11" s="30" t="str">
+      <c r="K11" s="27" t="str">
         <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>空档亮灯范围 (rpm)</v>
       </c>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="31">
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28">
         <v>0</v>
       </c>
-      <c r="P11" s="31"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -30488,27 +30542,27 @@
     </row>
     <row r="13" spans="1:17" ht="32" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="32" t="str">
         <f>VLOOKUP("label.groupOneTypeATarmac",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 1 组 · Type-A / 柏油</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="29" t="str">
+      <c r="J13" s="32" t="str">
         <f>VLOOKUP("label.groupTwoTypeBGravel",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 2 组 · Type-B / 砂石</v>
       </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:17" ht="32" customHeight="1">
@@ -30931,38 +30985,38 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="18">
         <v>0.32500000000000001</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="28" t="str">
+      <c r="F22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="G22" s="28"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="19">
         <v>5.4748128000000005</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="28" t="str">
+      <c r="J22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="K22" s="28"/>
+      <c r="K22" s="35"/>
       <c r="L22" s="18">
         <v>0.32400000000000001</v>
       </c>
       <c r="M22" s="1"/>
-      <c r="N22" s="28" t="str">
+      <c r="N22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="O22" s="28"/>
+      <c r="O22" s="35"/>
       <c r="P22" s="19">
         <v>5.7898434559999998</v>
       </c>
@@ -30970,39 +31024,39 @@
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="C23" s="28"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="20">
         <v>1.85</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="28" t="str">
+      <c r="F23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="G23" s="28"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="21">
         <v>9.7999999999999997E-4</v>
       </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="28" t="str">
+      <c r="J23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="K23" s="28"/>
+      <c r="K23" s="35"/>
       <c r="L23" s="20">
         <f>$D$23</f>
         <v>1.85</v>
       </c>
       <c r="M23" s="1"/>
-      <c r="N23" s="28" t="str">
+      <c r="N23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="O23" s="28"/>
+      <c r="O23" s="35"/>
       <c r="P23" s="21">
         <f>$H$23</f>
         <v>9.7999999999999997E-4</v>
@@ -31562,29 +31616,29 @@
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="28" t="str">
+      <c r="B53" s="35" t="str">
         <f>VLOOKUP("label.gearGroup",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>齿轮组</v>
       </c>
-      <c r="C53" s="28"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="23">
         <v>1</v>
       </c>
-      <c r="E53" s="28" t="str">
+      <c r="E53" s="35" t="str">
         <f>IF(D53=1,VLOOKUP("label.groupOneTypeATarmac",Locale!$A$2:$D$73,4,FALSE),VLOOKUP("label.groupTwoTypeBGravel",Locale!$A$2:$D$73,4,FALSE))</f>
         <v>第 1 组 · Type-A / 柏油</v>
       </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
       <c r="Q53" s="1"/>
     </row>
     <row r="54" spans="1:17" ht="22.5" customHeight="1">
@@ -32102,31 +32156,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="K5:P5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="O11:P11"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="E53:P53"/>
     <mergeCell ref="J13:P13"/>
@@ -32139,6 +32168,31 @@
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="O6:P6"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -32198,24 +32252,24 @@
     </row>
     <row r="2" spans="1:17" ht="34" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="35" t="str">
+      <c r="B2" s="31" t="str">
         <f>VLOOKUP("title.25r1GearingShiftLights",Locale!$A$2:$D$75,4,FALSE)</f>
         <v>25R1 · 齿比与换挡灯</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17" ht="22.5" customHeight="1">
@@ -32258,170 +32312,170 @@
     </row>
     <row r="5" spans="1:17" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="32" t="str">
         <f>VLOOKUP("chart.engineCurve",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机曲线</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="29" t="str">
+      <c r="F5" s="32" t="str">
         <f>VLOOKUP("label.calibrationBasis",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>标定依据</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="29" t="str">
+      <c r="K5" s="32" t="str">
         <f>VLOOKUP("label.shiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>换挡灯</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" ht="22.5" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="30" t="str">
+      <c r="B6" s="27" t="str">
         <f>VLOOKUP("label.peakPowerHp",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值功率 (hp)</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$97:$D$111)</f>
         <v>369.05984338245162</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="30" t="str">
+      <c r="F6" s="27" t="str">
         <f>VLOOKUP("label.runningMassKg",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>运行质量 (kg)</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="7">
         <v>1380</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="30" t="str">
+      <c r="K6" s="27" t="str">
         <f>VLOOKUP("label.neutralFlashRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>空挡闪烁 (rpm)</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28">
         <v>3000</v>
       </c>
-      <c r="P6" s="31"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="32" t="str">
+      <c r="B7" s="33" t="str">
         <f>VLOOKUP("label.powerPeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>功率峰值转速 (rpm)</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$97:$B$111,MATCH(D6,Samples!$D$97:$D$111,0))</f>
         <v>6997</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="33" t="str">
         <f>VLOOKUP("label.engineFlywheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机 + 飞轮转动惯量 (kg m²)</v>
       </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="8">
         <v>0.12171599999999999</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="32" t="str">
+      <c r="K7" s="33" t="str">
         <f>VLOOKUP("label.topGearLimiterRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>最高挡 / 限转 (rpm)</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33">
         <v>8500</v>
       </c>
-      <c r="P7" s="32"/>
+      <c r="P7" s="33"/>
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="30" t="str">
+      <c r="B8" s="27" t="str">
         <f>VLOOKUP("label.peakTorqueNm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩 (Nm)</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$97:$C$111)</f>
         <v>440.77961570266001</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="30" t="str">
+      <c r="F8" s="27" t="str">
         <f>VLOOKUP("label.finalDrive",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>主减速比</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
       <c r="I8" s="9">
         <v>4.1333333333333337</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="30" t="str">
+      <c r="K8" s="27" t="str">
         <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>普通档亮灯范围 (rpm)</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31">
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28">
         <v>500</v>
       </c>
-      <c r="P8" s="31"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="32" t="str">
+      <c r="B9" s="33" t="str">
         <f>VLOOKUP("label.torquePeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩转速 (rpm)</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$97:$B$111,MATCH(D8,Samples!$C$97:$C$111,0))</f>
         <v>4910</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="33" t="str">
         <f>VLOOKUP("label.gearboxTorqueLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱扭矩损失</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="10">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="32" t="str">
+      <c r="K9" s="33" t="str">
         <f>VLOOKUP("label.roundingRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>取整步长 (rpm)</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32">
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>10</v>
       </c>
-      <c r="P9" s="32"/>
+      <c r="P9" s="33"/>
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
@@ -32435,44 +32489,44 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="30" t="str">
+      <c r="K10" s="27" t="str">
         <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>最高档亮灯范围 (rpm)</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="31">
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="28">
         <v>250</v>
       </c>
-      <c r="P10" s="31"/>
+      <c r="P10" s="28"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="34" t="str">
         <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>黄色单元格为手动输入。</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
-      <c r="K11" s="30" t="str">
+      <c r="K11" s="27" t="str">
         <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>空档亮灯范围 (rpm)</v>
       </c>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="31">
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28">
         <v>0</v>
       </c>
-      <c r="P11" s="31"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -32496,27 +32550,27 @@
     </row>
     <row r="13" spans="1:17" ht="32" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="32" t="str">
         <f>VLOOKUP("label.groupOneTypeATarmac",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 1 组 · Type-A / 柏油</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="29" t="str">
+      <c r="J13" s="32" t="str">
         <f>VLOOKUP("label.groupTwoTypeBGravel",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 2 组 · Type-B / 砂石</v>
       </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:17" ht="32" customHeight="1">
@@ -32903,38 +32957,38 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="18">
         <v>0.32500000000000001</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="28" t="str">
+      <c r="F22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="G22" s="28"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="19">
         <v>5.4748128000000005</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="28" t="str">
+      <c r="J22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="K22" s="28"/>
+      <c r="K22" s="35"/>
       <c r="L22" s="18">
         <v>0.32400000000000001</v>
       </c>
       <c r="M22" s="1"/>
-      <c r="N22" s="28" t="str">
+      <c r="N22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="O22" s="28"/>
+      <c r="O22" s="35"/>
       <c r="P22" s="19">
         <v>5.7898434559999998</v>
       </c>
@@ -32942,39 +32996,39 @@
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="C23" s="28"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="20">
         <v>1.65</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="28" t="str">
+      <c r="F23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="G23" s="28"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="21">
         <v>7.7999999999999999E-4</v>
       </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="28" t="str">
+      <c r="J23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="K23" s="28"/>
+      <c r="K23" s="35"/>
       <c r="L23" s="20">
         <f>$D$23</f>
         <v>1.65</v>
       </c>
       <c r="M23" s="1"/>
-      <c r="N23" s="28" t="str">
+      <c r="N23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="O23" s="28"/>
+      <c r="O23" s="35"/>
       <c r="P23" s="21">
         <f>$H$23</f>
         <v>7.7999999999999999E-4</v>
@@ -33534,29 +33588,29 @@
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="28" t="str">
+      <c r="B53" s="35" t="str">
         <f>VLOOKUP("label.gearGroup",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>齿轮组</v>
       </c>
-      <c r="C53" s="28"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="23">
         <v>1</v>
       </c>
-      <c r="E53" s="28" t="str">
+      <c r="E53" s="35" t="str">
         <f>IF(D53=1,VLOOKUP("label.groupOneTypeATarmac",Locale!$A$2:$D$73,4,FALSE),VLOOKUP("label.groupTwoTypeBGravel",Locale!$A$2:$D$73,4,FALSE))</f>
         <v>第 1 组 · Type-A / 柏油</v>
       </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
       <c r="Q53" s="1"/>
     </row>
     <row r="54" spans="1:17" ht="22.5" customHeight="1">
@@ -34074,6 +34128,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="E53:P53"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:P8"/>
     <mergeCell ref="K10:N10"/>
     <mergeCell ref="O10:P10"/>
     <mergeCell ref="K11:N11"/>
@@ -34090,28 +34166,6 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="E53:P53"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="N23:O23"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -34171,24 +34225,24 @@
     </row>
     <row r="2" spans="1:17" ht="34" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="35" t="str">
+      <c r="B2" s="31" t="str">
         <f>VLOOKUP("title.rally1GearingShiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>Rally1 · 齿比与换挡灯</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17" ht="22.5" customHeight="1">
@@ -34234,170 +34288,170 @@
     </row>
     <row r="5" spans="1:17" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="32" t="str">
         <f>VLOOKUP("chart.engineCurve",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机曲线</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="29" t="str">
+      <c r="F5" s="32" t="str">
         <f>VLOOKUP("label.calibrationBasis",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>标定依据</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="29" t="str">
+      <c r="K5" s="32" t="str">
         <f>VLOOKUP("label.shiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>换挡灯</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" ht="22.5" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="30" t="str">
+      <c r="B6" s="27" t="str">
         <f>VLOOKUP("label.peakPowerHp",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值功率 (hp)</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$437:$D$451)</f>
         <v>379.28148996854014</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="30" t="str">
+      <c r="F6" s="27" t="str">
         <f>VLOOKUP("label.runningMassKg",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>运行质量 (kg)</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="7">
         <v>1460</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="30" t="str">
+      <c r="K6" s="27" t="str">
         <f>VLOOKUP("label.neutralFlashRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>空挡闪烁 (rpm)</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28">
         <v>3000</v>
       </c>
-      <c r="P6" s="31"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="32" t="str">
+      <c r="B7" s="33" t="str">
         <f>VLOOKUP("label.powerPeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>功率峰值转速 (rpm)</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$437:$B$451,MATCH(D6,Samples!$D$437:$D$451,0))</f>
         <v>6951</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="33" t="str">
         <f>VLOOKUP("label.engineFlywheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机 + 飞轮转动惯量 (kg m²)</v>
       </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="8">
         <v>0.12171599999999999</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="32" t="str">
+      <c r="K7" s="33" t="str">
         <f>VLOOKUP("label.topGearLimiterRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>最高挡 / 限转 (rpm)</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33">
         <v>8500</v>
       </c>
-      <c r="P7" s="32"/>
+      <c r="P7" s="33"/>
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="30" t="str">
+      <c r="B8" s="27" t="str">
         <f>VLOOKUP("label.peakTorqueNm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩 (Nm)</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$437:$C$451)</f>
         <v>444.51603790308002</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="30" t="str">
+      <c r="F8" s="27" t="str">
         <f>VLOOKUP("label.finalDrive",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>主减速比</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
       <c r="I8" s="9">
         <v>4.1333333333333337</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="30" t="str">
+      <c r="K8" s="27" t="str">
         <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>普通档亮灯范围 (rpm)</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31">
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28">
         <v>500</v>
       </c>
-      <c r="P8" s="31"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="32" t="str">
+      <c r="B9" s="33" t="str">
         <f>VLOOKUP("label.torquePeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩转速 (rpm)</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$437:$B$451,MATCH(D8,Samples!$C$437:$C$451,0))</f>
         <v>5083</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="33" t="str">
         <f>VLOOKUP("label.gearboxTorqueLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱扭矩损失</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="10">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="32" t="str">
+      <c r="K9" s="33" t="str">
         <f>VLOOKUP("label.roundingRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>取整步长 (rpm)</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32">
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>10</v>
       </c>
-      <c r="P9" s="32"/>
+      <c r="P9" s="33"/>
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
@@ -34411,44 +34465,44 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="30" t="str">
+      <c r="K10" s="27" t="str">
         <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>最高档亮灯范围 (rpm)</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="31">
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="28">
         <v>250</v>
       </c>
-      <c r="P10" s="31"/>
+      <c r="P10" s="28"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="34" t="str">
         <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>黄色单元格为手动输入。</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
-      <c r="K11" s="30" t="str">
+      <c r="K11" s="27" t="str">
         <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>空档亮灯范围 (rpm)</v>
       </c>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="31">
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28">
         <v>0</v>
       </c>
-      <c r="P11" s="31"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -34472,27 +34526,27 @@
     </row>
     <row r="13" spans="1:17" ht="32" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="32" t="str">
         <f>VLOOKUP("label.groupOneTypeATarmac",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 1 组 · Type-A / 柏油</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="29" t="str">
+      <c r="J13" s="32" t="str">
         <f>VLOOKUP("label.groupTwoTypeBGravel",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 2 组 · Type-B / 砂石</v>
       </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:17" ht="32" customHeight="1">
@@ -34879,38 +34933,38 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="18">
         <v>0.32500000000000001</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="28" t="str">
+      <c r="F22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="G22" s="28"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="19">
         <v>5.4748128000000005</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="28" t="str">
+      <c r="J22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="K22" s="28"/>
+      <c r="K22" s="35"/>
       <c r="L22" s="18">
         <v>0.32400000000000001</v>
       </c>
       <c r="M22" s="1"/>
-      <c r="N22" s="28" t="str">
+      <c r="N22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="O22" s="28"/>
+      <c r="O22" s="35"/>
       <c r="P22" s="19">
         <v>5.7898434559999998</v>
       </c>
@@ -34918,39 +34972,39 @@
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="C23" s="28"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="20">
         <v>1.65</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="28" t="str">
+      <c r="F23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="G23" s="28"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="21">
         <v>7.7999999999999999E-4</v>
       </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="28" t="str">
+      <c r="J23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="K23" s="28"/>
+      <c r="K23" s="35"/>
       <c r="L23" s="20">
         <f>$D$23</f>
         <v>1.65</v>
       </c>
       <c r="M23" s="1"/>
-      <c r="N23" s="28" t="str">
+      <c r="N23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="O23" s="28"/>
+      <c r="O23" s="35"/>
       <c r="P23" s="21">
         <f>$H$23</f>
         <v>7.7999999999999999E-4</v>
@@ -35510,29 +35564,29 @@
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="28" t="str">
+      <c r="B53" s="35" t="str">
         <f>VLOOKUP("label.gearGroup",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>齿轮组</v>
       </c>
-      <c r="C53" s="28"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="23">
         <v>1</v>
       </c>
-      <c r="E53" s="28" t="str">
+      <c r="E53" s="35" t="str">
         <f>IF(D53=1,VLOOKUP("label.groupOneTypeATarmac",Locale!$A$2:$D$73,4,FALSE),VLOOKUP("label.groupTwoTypeBGravel",Locale!$A$2:$D$73,4,FALSE))</f>
         <v>第 1 组 · Type-A / 柏油</v>
       </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
       <c r="Q53" s="1"/>
     </row>
     <row r="54" spans="1:17" ht="22.5" customHeight="1">
@@ -36050,6 +36104,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="E53:P53"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:P8"/>
     <mergeCell ref="K10:N10"/>
     <mergeCell ref="O10:P10"/>
     <mergeCell ref="K11:N11"/>
@@ -36066,28 +36142,6 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="E53:P53"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="N23:O23"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -36147,24 +36201,24 @@
     </row>
     <row r="2" spans="1:17" ht="34" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="35" t="str">
+      <c r="B2" s="31" t="str">
         <f>VLOOKUP("title.rx1GearingShiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>RX1 · 齿比与换挡灯</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17" ht="22.5" customHeight="1">
@@ -36207,170 +36261,170 @@
     </row>
     <row r="5" spans="1:17" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="32" t="str">
         <f>VLOOKUP("chart.engineCurve",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机曲线</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="29" t="str">
+      <c r="F5" s="32" t="str">
         <f>VLOOKUP("label.calibrationBasis",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>标定依据</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="29" t="str">
+      <c r="K5" s="32" t="str">
         <f>VLOOKUP("label.shiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>换挡灯</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" ht="22.5" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="30" t="str">
+      <c r="B6" s="27" t="str">
         <f>VLOOKUP("label.peakPowerHp",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值功率 (hp)</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$127:$D$141)</f>
         <v>593.67797109433252</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="30" t="str">
+      <c r="F6" s="27" t="str">
         <f>VLOOKUP("label.runningMassKg",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>运行质量 (kg)</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="7">
         <v>1306</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="30" t="str">
+      <c r="K6" s="27" t="str">
         <f>VLOOKUP("label.neutralFlashRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>空挡闪烁 (rpm)</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28">
         <v>3000</v>
       </c>
-      <c r="P6" s="31"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="32" t="str">
+      <c r="B7" s="33" t="str">
         <f>VLOOKUP("label.powerPeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>功率峰值转速 (rpm)</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$127:$B$141,MATCH(D6,Samples!$D$127:$D$141,0))</f>
         <v>6026</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="33" t="str">
         <f>VLOOKUP("label.engineFlywheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机 + 飞轮转动惯量 (kg m²)</v>
       </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="8">
         <v>0.128</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="32" t="str">
+      <c r="K7" s="33" t="str">
         <f>VLOOKUP("label.topGearLimiterRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>最高挡 / 限转 (rpm)</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33">
         <v>8500</v>
       </c>
-      <c r="P7" s="32"/>
+      <c r="P7" s="33"/>
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="30" t="str">
+      <c r="B8" s="27" t="str">
         <f>VLOOKUP("label.peakTorqueNm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩 (Nm)</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$127:$C$141)</f>
         <v>842.02176826692005</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="30" t="str">
+      <c r="F8" s="27" t="str">
         <f>VLOOKUP("label.finalDrive",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>主减速比</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
       <c r="I8" s="9">
         <v>4</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="30" t="str">
+      <c r="K8" s="27" t="str">
         <f>VLOOKUP("label.normalGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>普通档亮灯范围 (rpm)</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31">
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28">
         <v>500</v>
       </c>
-      <c r="P8" s="31"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="32" t="str">
+      <c r="B9" s="33" t="str">
         <f>VLOOKUP("label.torquePeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩转速 (rpm)</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$127:$B$141,MATCH(D8,Samples!$C$127:$C$141,0))</f>
         <v>4202</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="33" t="str">
         <f>VLOOKUP("label.gearboxTorqueLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱扭矩损失</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="10">
         <v>1.2E-2</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="32" t="str">
+      <c r="K9" s="33" t="str">
         <f>VLOOKUP("label.roundingRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>取整步长 (rpm)</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32">
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>10</v>
       </c>
-      <c r="P9" s="32"/>
+      <c r="P9" s="33"/>
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
@@ -36384,44 +36438,44 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="30" t="str">
+      <c r="K10" s="27" t="str">
         <f>VLOOKUP("label.topGearLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>最高档亮灯范围 (rpm)</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="31">
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="28">
         <v>250</v>
       </c>
-      <c r="P10" s="31"/>
+      <c r="P10" s="28"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="34" t="str">
         <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>黄色单元格为手动输入。</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
-      <c r="K11" s="30" t="str">
+      <c r="K11" s="27" t="str">
         <f>VLOOKUP("label.neutralLightRangeRpm",Locale!$A$2:$D$78,4,FALSE)</f>
         <v>空档亮灯范围 (rpm)</v>
       </c>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="31">
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28">
         <v>0</v>
       </c>
-      <c r="P11" s="31"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -36445,16 +36499,16 @@
     </row>
     <row r="13" spans="1:17" ht="32" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="32" t="str">
         <f>VLOOKUP("label.groupOneRx1",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 1 组 · RX1</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -36752,20 +36806,20 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="18">
         <v>0.32</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="28" t="str">
+      <c r="F22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="G22" s="28"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="19">
         <v>5.2788544000000002</v>
       </c>
@@ -36781,20 +36835,20 @@
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="C23" s="28"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="20">
         <v>1.85</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="28" t="str">
+      <c r="F23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="G23" s="28"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="21">
         <v>9.7999999999999997E-4</v>
       </c>
@@ -37361,29 +37415,29 @@
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="28" t="str">
+      <c r="B53" s="35" t="str">
         <f>VLOOKUP("label.gearGroup",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>齿轮组</v>
       </c>
-      <c r="C53" s="28"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="23">
         <v>1</v>
       </c>
-      <c r="E53" s="28" t="str">
+      <c r="E53" s="35" t="str">
         <f>VLOOKUP("label.groupOneRx1",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>第 1 组 · RX1</v>
       </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
       <c r="Q53" s="1"/>
     </row>
     <row r="54" spans="1:17" ht="22.5" customHeight="1">
@@ -37901,22 +37955,13 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="K5:P5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="E53:P53"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F23:G23"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="K9:N9"/>
@@ -37926,13 +37971,22 @@
     <mergeCell ref="O10:P10"/>
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="O11:P11"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="E53:P53"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="O6:P6"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
@@ -37992,24 +38046,24 @@
     </row>
     <row r="2" spans="1:17" ht="34" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="35" t="str">
+      <c r="B2" s="31" t="str">
         <f>VLOOKUP("title.rx3GearingShiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>RX3 · 齿比与换挡灯</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17" ht="22.5" customHeight="1">
@@ -38055,170 +38109,170 @@
     </row>
     <row r="5" spans="1:17" ht="32" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="32" t="str">
         <f>VLOOKUP("chart.engineCurve",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机曲线</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="29" t="str">
+      <c r="F5" s="32" t="str">
         <f>VLOOKUP("label.calibrationBasis",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>标定依据</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="29" t="str">
+      <c r="K5" s="32" t="str">
         <f>VLOOKUP("label.shiftLights",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>换挡灯</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" ht="22.5" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="30" t="str">
+      <c r="B6" s="27" t="str">
         <f>VLOOKUP("label.peakPowerHp",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值功率 (hp)</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="6">
         <f>MAX(Samples!$D$157:$D$171)</f>
         <v>224.50763333936891</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="30" t="str">
+      <c r="F6" s="27" t="str">
         <f>VLOOKUP("label.runningMassKg",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>运行质量 (kg)</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="7">
         <v>1009</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="30" t="str">
+      <c r="K6" s="27" t="str">
         <f>VLOOKUP("label.neutralFlashRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>空挡闪烁 (rpm)</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31">
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28">
         <v>3000</v>
       </c>
-      <c r="P6" s="31"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="32" t="str">
+      <c r="B7" s="33" t="str">
         <f>VLOOKUP("label.powerPeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>功率峰值转速 (rpm)</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="5">
         <f>INDEX(Samples!$B$157:$B$171,MATCH(D6,Samples!$D$157:$D$171,0))</f>
         <v>8355</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="33" t="str">
         <f>VLOOKUP("label.engineFlywheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>发动机 + 飞轮转动惯量 (kg m²)</v>
       </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="8">
         <v>0.121716</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="32" t="str">
+      <c r="K7" s="33" t="str">
         <f>VLOOKUP("label.topGearLimiterRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>最高挡 / 限转 (rpm)</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32">
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33">
         <v>8500</v>
       </c>
-      <c r="P7" s="32"/>
+      <c r="P7" s="33"/>
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="30" t="str">
+      <c r="B8" s="27" t="str">
         <f>VLOOKUP("label.peakTorqueNm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩 (Nm)</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="6">
         <f>MAX(Samples!$C$157:$C$171)</f>
         <v>204.07922467170999</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="30" t="str">
+      <c r="F8" s="27" t="str">
         <f>VLOOKUP("label.finalDrive",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>主减速比</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
       <c r="I8" s="9">
         <v>4.4666666666666668</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="30" t="str">
+      <c r="K8" s="27" t="str">
         <f>VLOOKUP("label.lightRangeRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>亮灯范围 (rpm)</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31">
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28">
         <v>500</v>
       </c>
-      <c r="P8" s="31"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="32" t="str">
+      <c r="B9" s="33" t="str">
         <f>VLOOKUP("label.torquePeakRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>峰值扭矩转速 (rpm)</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="5">
         <f>INDEX(Samples!$B$157:$B$171,MATCH(D8,Samples!$C$157:$C$171,0))</f>
         <v>6292</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="33" t="str">
         <f>VLOOKUP("label.gearboxTorqueLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱扭矩损失</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="10">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="32" t="str">
+      <c r="K9" s="33" t="str">
         <f>VLOOKUP("label.roundingRpm",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>取整步长 (rpm)</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32">
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>10</v>
       </c>
-      <c r="P9" s="32"/>
+      <c r="P9" s="33"/>
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
@@ -38242,24 +38296,24 @@
     </row>
     <row r="11" spans="1:17" ht="22.5" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="34" t="str">
         <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>黄色单元格为手动输入。</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -38283,16 +38337,16 @@
     </row>
     <row r="13" spans="1:17" ht="32" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="32" t="str">
         <f>SUBSTITUTE(VLOOKUP("label.groupOneRx1",Locale!$A$2:$D$73,4,FALSE),"RX1","RX3")</f>
         <v>第 1 组 · RX3</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -38572,20 +38626,20 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="35" t="str">
         <f>VLOOKUP("label.tyreRadiusM",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>轮胎半径 (m)</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="18">
         <v>0.31</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="28" t="str">
+      <c r="F22" s="35" t="str">
         <f>VLOOKUP("label.wheelInertia",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>车轮转动惯量 I (kg m²)</v>
       </c>
-      <c r="G22" s="28"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="19">
         <v>5.0655424</v>
       </c>
@@ -38601,20 +38655,20 @@
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="35" t="str">
         <f>VLOOKUP("label.gearboxFriction",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱摩擦阻力 (Nm)</v>
       </c>
-      <c r="C23" s="28"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="20">
         <v>1.65</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="28" t="str">
+      <c r="F23" s="35" t="str">
         <f>VLOOKUP("label.gearboxDynamicLoss",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>变速箱动态阻力 (Nm s)</v>
       </c>
-      <c r="G23" s="28"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="21">
         <v>7.7999999999999999E-4</v>
       </c>
@@ -39181,29 +39235,29 @@
     </row>
     <row r="53" spans="1:17" ht="22.5" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="28" t="str">
+      <c r="B53" s="35" t="str">
         <f>VLOOKUP("label.gearGroup",Locale!$A$2:$D$73,4,FALSE)</f>
         <v>齿轮组</v>
       </c>
-      <c r="C53" s="28"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="23">
         <v>1</v>
       </c>
-      <c r="E53" s="28" t="str">
+      <c r="E53" s="35" t="str">
         <f>SUBSTITUTE(VLOOKUP("label.groupOneRx1",Locale!$A$2:$D$73,4,FALSE),"RX1","RX3")</f>
         <v>第 1 组 · RX3</v>
       </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
       <c r="Q53" s="1"/>
     </row>
     <row r="54" spans="1:17" ht="22.5" customHeight="1">
@@ -39721,11 +39775,22 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B3:P3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="E53:P53"/>
+    <mergeCell ref="B11:P11"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:P9"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="K6:N6"/>
@@ -39734,22 +39799,11 @@
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="K7:N7"/>
     <mergeCell ref="O7:P7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="E53:P53"/>
-    <mergeCell ref="B11:P11"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="K5:P5"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="4">
